--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\RU-Replacer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE52A571-127B-43FB-A66A-10D0279D84EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D649ED4A-C730-4430-A2B3-6538D8B71869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId3"/>
     <sheet name="Составные в 1 очередь" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,12 +31,177 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>инициации</t>
   </si>
   <si>
     <t>обряды</t>
+  </si>
+  <si>
+    <t>земной цивилизации</t>
+  </si>
+  <si>
+    <t>земного общества</t>
+  </si>
+  <si>
+    <t>некую свою гипотезу</t>
+  </si>
+  <si>
+    <t>некое своё предположение</t>
+  </si>
+  <si>
+    <t>в эзотерическую практику</t>
+  </si>
+  <si>
+    <t>в освоение тайного знания и его применения</t>
+  </si>
+  <si>
+    <t>коррекций</t>
+  </si>
+  <si>
+    <t>изменений</t>
+  </si>
+  <si>
+    <t>статистическую базу</t>
+  </si>
+  <si>
+    <t>достаточное количество знаний</t>
+  </si>
+  <si>
+    <t>новой парадигмы</t>
+  </si>
+  <si>
+    <t>нового подхода</t>
+  </si>
+  <si>
+    <t>инкарнации</t>
+  </si>
+  <si>
+    <t>воплощения</t>
+  </si>
+  <si>
+    <t>инкарнация</t>
+  </si>
+  <si>
+    <t>воплощение</t>
+  </si>
+  <si>
+    <t>великие эзотерики</t>
+  </si>
+  <si>
+    <t>великие тайноведы</t>
+  </si>
+  <si>
+    <t>была проведена оценка</t>
+  </si>
+  <si>
+    <t>был проведен анализ</t>
+  </si>
+  <si>
+    <t>профессия</t>
+  </si>
+  <si>
+    <t>вид трудовой деятельности</t>
+  </si>
+  <si>
+    <t>профессии</t>
+  </si>
+  <si>
+    <t>виды трудовой деятельности</t>
+  </si>
+  <si>
+    <t>профессию</t>
+  </si>
+  <si>
+    <t>этой энергоинформационной трансформации</t>
+  </si>
+  <si>
+    <t>этого энергоинформационного преобразования</t>
+  </si>
+  <si>
+    <t>реализовался</t>
+  </si>
+  <si>
+    <t>воплотился</t>
+  </si>
+  <si>
+    <t>реализовались</t>
+  </si>
+  <si>
+    <t>воплотились</t>
+  </si>
+  <si>
+    <t>реализовать</t>
+  </si>
+  <si>
+    <t>воплотить</t>
+  </si>
+  <si>
+    <t>реализовал</t>
+  </si>
+  <si>
+    <t>воплотил</t>
+  </si>
+  <si>
+    <t>реализовали</t>
+  </si>
+  <si>
+    <t>воплотили</t>
+  </si>
+  <si>
+    <t>реализовала</t>
+  </si>
+  <si>
+    <t>воплотила</t>
+  </si>
+  <si>
+    <t>экзотерик</t>
+  </si>
+  <si>
+    <t>тайновед</t>
+  </si>
+  <si>
+    <t>экзотериков</t>
+  </si>
+  <si>
+    <t>тайноведов</t>
+  </si>
+  <si>
+    <t>многоплановое</t>
+  </si>
+  <si>
+    <t>многомерное</t>
+  </si>
+  <si>
+    <t>норма жизни</t>
+  </si>
+  <si>
+    <t>обязательное условие жизни</t>
+  </si>
+  <si>
+    <t>благая весть</t>
+  </si>
+  <si>
+    <t>евангелие</t>
+  </si>
+  <si>
+    <t>инициируемого</t>
+  </si>
+  <si>
+    <t>обращённого</t>
+  </si>
+  <si>
+    <t>инициируемый</t>
+  </si>
+  <si>
+    <t>обращённый</t>
+  </si>
+  <si>
+    <t>инкарнационных воплощениях</t>
+  </si>
+  <si>
+    <t>предыдущих воплощениях</t>
   </si>
 </sst>
 </file>
@@ -354,10 +519,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.76953125" customWidth="1"/>
+    <col min="2" max="2" width="20.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.75">
@@ -366,6 +532,150 @@
       </c>
       <c r="B1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -375,9 +685,70 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="47.6328125" customWidth="1"/>
+    <col min="2" max="2" width="27.76953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -393,13 +764,38 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
     <col min="2" max="2" width="77.40625" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D649ED4A-C730-4430-A2B3-6538D8B71869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E514E06-A7BF-4C37-B7FD-F667BDA5FC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>инициации</t>
   </si>
@@ -130,12 +130,6 @@
   </si>
   <si>
     <t>воплотились</t>
-  </si>
-  <si>
-    <t>реализовать</t>
-  </si>
-  <si>
-    <t>воплотить</t>
   </si>
   <si>
     <t>реализовал</t>
@@ -598,84 +592,76 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-    </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -734,18 +720,18 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C94A2FB-EFBB-4649-9673-2DEA1B7068D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C03B4AC-98D6-439A-982D-3BE51985F6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>инициации</t>
   </si>
@@ -206,6 +206,18 @@
   </si>
   <si>
     <t>«третьего очи»,</t>
+  </si>
+  <si>
+    <t>магии черной или белой</t>
+  </si>
+  <si>
+    <t>колдовства черного или белого</t>
+  </si>
+  <si>
+    <t>нашей земной цивилизации</t>
+  </si>
+  <si>
+    <t>нашего земного общества</t>
   </si>
 </sst>
 </file>
@@ -681,7 +693,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
@@ -742,6 +754,22 @@
       </c>
       <c r="B7" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C03B4AC-98D6-439A-982D-3BE51985F6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24158595-B8E0-4B77-B9DF-5E4A1C158044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,13 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
-  <si>
-    <t>инициации</t>
-  </si>
-  <si>
-    <t>обряды</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>земной цивилизации</t>
   </si>
@@ -58,12 +52,6 @@
     <t>в освоение тайного знания и его применения</t>
   </si>
   <si>
-    <t>коррекций</t>
-  </si>
-  <si>
-    <t>изменений</t>
-  </si>
-  <si>
     <t>статистическую базу</t>
   </si>
   <si>
@@ -76,18 +64,6 @@
     <t>нового подхода</t>
   </si>
   <si>
-    <t>инкарнации</t>
-  </si>
-  <si>
-    <t>воплощения</t>
-  </si>
-  <si>
-    <t>инкарнация</t>
-  </si>
-  <si>
-    <t>воплощение</t>
-  </si>
-  <si>
     <t>великие эзотерики</t>
   </si>
   <si>
@@ -100,99 +76,18 @@
     <t>был проведен анализ</t>
   </si>
   <si>
-    <t>профессия</t>
-  </si>
-  <si>
-    <t>вид трудовой деятельности</t>
-  </si>
-  <si>
-    <t>профессии</t>
-  </si>
-  <si>
-    <t>виды трудовой деятельности</t>
-  </si>
-  <si>
-    <t>профессию</t>
-  </si>
-  <si>
     <t>этой энергоинформационной трансформации</t>
   </si>
   <si>
     <t>этого энергоинформационного преобразования</t>
   </si>
   <si>
-    <t>реализовался</t>
-  </si>
-  <si>
-    <t>воплотился</t>
-  </si>
-  <si>
-    <t>реализовались</t>
-  </si>
-  <si>
-    <t>воплотились</t>
-  </si>
-  <si>
-    <t>реализовал</t>
-  </si>
-  <si>
-    <t>воплотил</t>
-  </si>
-  <si>
-    <t>реализовали</t>
-  </si>
-  <si>
-    <t>воплотили</t>
-  </si>
-  <si>
-    <t>реализовала</t>
-  </si>
-  <si>
-    <t>воплотила</t>
-  </si>
-  <si>
-    <t>экзотерик</t>
-  </si>
-  <si>
-    <t>тайновед</t>
-  </si>
-  <si>
-    <t>экзотериков</t>
-  </si>
-  <si>
-    <t>тайноведов</t>
-  </si>
-  <si>
-    <t>многоплановое</t>
-  </si>
-  <si>
-    <t>многомерное</t>
-  </si>
-  <si>
     <t>норма жизни</t>
   </si>
   <si>
     <t>обязательное условие жизни</t>
   </si>
   <si>
-    <t>благая весть</t>
-  </si>
-  <si>
-    <t>евангелие</t>
-  </si>
-  <si>
-    <t>инициируемого</t>
-  </si>
-  <si>
-    <t>обращённого</t>
-  </si>
-  <si>
-    <t>инициируемый</t>
-  </si>
-  <si>
-    <t>обращённый</t>
-  </si>
-  <si>
     <t>инкарнационных воплощениях</t>
   </si>
   <si>
@@ -218,6 +113,24 @@
   </si>
   <si>
     <t>нашего земного общества</t>
+  </si>
+  <si>
+    <t>серьезную статистическую базу</t>
+  </si>
+  <si>
+    <t>важные достаточные знания</t>
+  </si>
+  <si>
+    <t>всю магическую литературу</t>
+  </si>
+  <si>
+    <t>все источники колдовства</t>
+  </si>
+  <si>
+    <t>знаниях сохранилась в</t>
+  </si>
+  <si>
+    <t>знаниях сохранились в</t>
   </si>
 </sst>
 </file>
@@ -535,165 +448,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.76953125" customWidth="1"/>
     <col min="2" max="2" width="20.08984375" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
@@ -702,74 +470,98 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -797,26 +589,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -831,17 +623,17 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24158595-B8E0-4B77-B9DF-5E4A1C158044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC76E95-689F-4F1D-A956-1EF9482CF240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>земной цивилизации</t>
   </si>
@@ -131,6 +131,18 @@
   </si>
   <si>
     <t>знаниях сохранились в</t>
+  </si>
+  <si>
+    <t>весь эгрегориальный этнос</t>
+  </si>
+  <si>
+    <t>вся эгрегориальная народность</t>
+  </si>
+  <si>
+    <t>деструктивной магии</t>
+  </si>
+  <si>
+    <t>разрушающем колдовстве</t>
   </si>
 </sst>
 </file>
@@ -461,7 +473,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
@@ -562,6 +574,22 @@
       </c>
       <c r="B12" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC76E95-689F-4F1D-A956-1EF9482CF240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41F5950-F76F-4FDB-A39C-17147DE317BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="20970" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -24,21 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
-  <si>
-    <t>земной цивилизации</t>
-  </si>
-  <si>
-    <t>земного общества</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -52,12 +43,6 @@
     <t>в освоение тайного знания и его применения</t>
   </si>
   <si>
-    <t>статистическую базу</t>
-  </si>
-  <si>
-    <t>достаточное количество знаний</t>
-  </si>
-  <si>
     <t>новой парадигмы</t>
   </si>
   <si>
@@ -142,7 +127,43 @@
     <t>деструктивной магии</t>
   </si>
   <si>
-    <t>разрушающем колдовстве</t>
+    <t>разрушающего колдовства</t>
+  </si>
+  <si>
+    <t>с массой</t>
+  </si>
+  <si>
+    <t>с весом</t>
+  </si>
+  <si>
+    <t>тройную массу</t>
+  </si>
+  <si>
+    <t>тройной вес</t>
+  </si>
+  <si>
+    <t>может быть осуществлена коррекция</t>
+  </si>
+  <si>
+    <t>могут быть осуществлены изменения</t>
+  </si>
+  <si>
+    <t>принял агрессивный характер</t>
+  </si>
+  <si>
+    <t>принял враждебную сторону</t>
+  </si>
+  <si>
+    <t>фридмановскую модель</t>
+  </si>
+  <si>
+    <t>фридмановский прообраз</t>
+  </si>
+  <si>
+    <t>информация в Мироздании распространяется</t>
+  </si>
+  <si>
+    <t>сведения в Мироздании распространяются</t>
   </si>
 </sst>
 </file>
@@ -461,9 +482,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.76953125" customWidth="1"/>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.08984375" customWidth="1"/>
   </cols>
   <sheetData/>
@@ -473,123 +494,123 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A3:B18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
-    <col min="2" max="2" width="27.76953125" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
       <c r="B8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A12" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A13" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A14" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>35</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -600,7 +621,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -608,35 +629,67 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
-    <col min="2" max="2" width="77.40625" customWidth="1"/>
+    <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -647,21 +700,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470922A9-554F-4171-817B-B4542805EF8E}">
   <dimension ref="A2:A4"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,28 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41F5950-F76F-4FDB-A39C-17147DE317BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36405C5E-9D6E-43D9-8F29-D74973C6556F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="20970" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
     <sheet name="Сложные слова" sheetId="3" r:id="rId2"/>
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId3"/>
     <sheet name="Составные в 1 очередь" sheetId="1" r:id="rId4"/>
-    <sheet name="Лист1" sheetId="5" r:id="rId5"/>
+    <sheet name="Лист2" sheetId="6" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -482,7 +486,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.08984375" customWidth="1"/>
@@ -495,13 +499,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
   <dimension ref="A3:B18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
     <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -509,7 +513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -517,7 +521,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -525,7 +529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -533,7 +537,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -541,7 +545,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -549,7 +553,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -557,7 +561,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -565,7 +569,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -573,7 +577,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -581,7 +585,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -589,7 +593,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -597,7 +601,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -605,7 +609,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -621,7 +625,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -630,13 +634,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
     <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -644,7 +648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -652,7 +656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -660,7 +664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -668,7 +672,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -676,7 +680,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -684,7 +688,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -698,21 +702,30 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470922A9-554F-4171-817B-B4542805EF8E}">
   <dimension ref="A2:A4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>18</v>
       </c>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36405C5E-9D6E-43D9-8F29-D74973C6556F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E3A2DD-993E-4107-B5D9-B6C3EB40A787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25510" yWindow="0" windowWidth="12980" windowHeight="20970" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
     <sheet name="Сложные слова" sheetId="3" r:id="rId2"/>
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId3"/>
-    <sheet name="Составные в 1 очередь" sheetId="1" r:id="rId4"/>
-    <sheet name="Лист2" sheetId="6" r:id="rId5"/>
+    <sheet name="составные важные" sheetId="1" r:id="rId4"/>
+    <sheet name="Неизменные" sheetId="6" r:id="rId5"/>
     <sheet name="Лист1" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -25,15 +25,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -168,6 +165,54 @@
   </si>
   <si>
     <t>сведения в Мироздании распространяются</t>
+  </si>
+  <si>
+    <t>фридмановской модели</t>
+  </si>
+  <si>
+    <t>фридмановского прообраза</t>
+  </si>
+  <si>
+    <t>знаменитый каталог</t>
+  </si>
+  <si>
+    <t>знаменитая папка</t>
+  </si>
+  <si>
+    <t>была выброшена всевозможная литература</t>
+  </si>
+  <si>
+    <t>были выброшены всевозможные источики</t>
+  </si>
+  <si>
+    <t>константа становится очень большой</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> постоянное значение становится очень большим</t>
+  </si>
+  <si>
+    <t>Клеткоподобная равновесная устройство</t>
+  </si>
+  <si>
+    <t>Клеткоподобное равновесное устройство</t>
+  </si>
+  <si>
+    <t>привычный нам объем</t>
+  </si>
+  <si>
+    <t>привычное нам количество</t>
+  </si>
+  <si>
+    <t>информация, записанная на объемной форме молекулы, способна перезаписываться</t>
+  </si>
+  <si>
+    <t>сведения, записанные на объемном виде молекулы, способны перезаписываться</t>
+  </si>
+  <si>
+    <t xml:space="preserve">эзотерический и физический аспект так называемой </t>
+  </si>
+  <si>
+    <t>тайную и физическую особенность,так называемую</t>
   </si>
 </sst>
 </file>
@@ -486,7 +531,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.08984375" customWidth="1"/>
@@ -498,14 +543,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B18"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A3:B25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
     <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -513,7 +558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -521,7 +566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -529,7 +574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -537,7 +582,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -545,7 +590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -553,7 +598,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -561,7 +606,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -569,7 +614,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -577,7 +622,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -585,7 +630,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -593,7 +638,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -601,7 +646,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -609,12 +654,68 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
       <c r="B18" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +726,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -633,14 +734,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
     <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -648,7 +749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -656,7 +757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -664,7 +765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -672,28 +773,20 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -703,9 +796,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
-  <sheetData/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="46.36328125" customWidth="1"/>
+    <col min="2" max="2" width="38.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -713,19 +827,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470922A9-554F-4171-817B-B4542805EF8E}">
   <dimension ref="A2:A4"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E3A2DD-993E-4107-B5D9-B6C3EB40A787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34BB8F7-9D16-4D29-BFDE-E4206AD4A92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25510" yWindow="0" windowWidth="12980" windowHeight="20970" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,31 @@
     <sheet name="Неизменные" sheetId="6" r:id="rId5"/>
     <sheet name="Лист1" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -213,6 +227,36 @@
   </si>
   <si>
     <t>тайную и физическую особенность,так называемую</t>
+  </si>
+  <si>
+    <t>информационная составляющая через воду оказывает</t>
+  </si>
+  <si>
+    <t>имеющиеся сведения через воду оказывают</t>
+  </si>
+  <si>
+    <t>в данный реальный момент времени</t>
+  </si>
+  <si>
+    <t>в данное мгновение времени</t>
+  </si>
+  <si>
+    <t>взглянуть на микро–</t>
+  </si>
+  <si>
+    <t>взглянуть на крошечные-</t>
+  </si>
+  <si>
+    <t>строении микро–</t>
+  </si>
+  <si>
+    <t>строении крошечных-</t>
+  </si>
+  <si>
+    <t>зафиксировали все</t>
+  </si>
+  <si>
+    <t>запомнили все</t>
   </si>
 </sst>
 </file>
@@ -531,7 +575,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.08984375" customWidth="1"/>
@@ -543,14 +587,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A3:B28"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
     <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -558,7 +602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -566,7 +610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -574,7 +618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -582,7 +626,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -590,7 +634,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -598,7 +642,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -606,7 +650,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -614,7 +658,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -622,7 +666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -630,7 +674,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -638,7 +682,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -646,7 +690,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -654,7 +698,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -662,7 +706,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -670,7 +714,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -678,7 +722,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -686,7 +730,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -694,7 +738,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -702,7 +746,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -710,12 +754,36 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>55</v>
       </c>
       <c r="B25" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -726,7 +794,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -734,14 +802,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
     <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -749,7 +817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -757,7 +825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -765,7 +833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -773,7 +841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -781,12 +849,28 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>59</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -797,13 +881,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="46.36328125" customWidth="1"/>
     <col min="2" max="2" width="38.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -811,7 +895,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -827,19 +911,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470922A9-554F-4171-817B-B4542805EF8E}">
   <dimension ref="A2:A4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>18</v>
       </c>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34BB8F7-9D16-4D29-BFDE-E4206AD4A92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358376C0-EF77-4EB7-8A7E-B30FE943E0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25690" yWindow="2220" windowWidth="12980" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -257,6 +257,18 @@
   </si>
   <si>
     <t>запомнили все</t>
+  </si>
+  <si>
+    <t>магии белой или черной.</t>
+  </si>
+  <si>
+    <t>колдовства белого или черного</t>
+  </si>
+  <si>
+    <t>силами – коллапсировать</t>
+  </si>
+  <si>
+    <t>силами - схлопнуться</t>
   </si>
 </sst>
 </file>
@@ -587,7 +599,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B28"/>
+  <dimension ref="A3:B30"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
@@ -784,6 +796,22 @@
       </c>
       <c r="B28" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A30" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358376C0-EF77-4EB7-8A7E-B30FE943E0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4760B5DA-3139-4848-8403-DFA05C1DED05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25690" yWindow="2220" windowWidth="12980" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25690" yWindow="0" windowWidth="12980" windowHeight="20970" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -36,15 +36,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -269,6 +266,72 @@
   </si>
   <si>
     <t>силами - схлопнуться</t>
+  </si>
+  <si>
+    <t>Своим мощнейшим потенциалом</t>
+  </si>
+  <si>
+    <t>Своими мощнейшими возможностями</t>
+  </si>
+  <si>
+    <t>апеллирует 11 законами</t>
+  </si>
+  <si>
+    <t>опирается на 11 законов</t>
+  </si>
+  <si>
+    <t>Эта техника претерпела</t>
+  </si>
+  <si>
+    <t>Эти средства претерпели</t>
+  </si>
+  <si>
+    <t>со спином протона</t>
+  </si>
+  <si>
+    <t>с вращением положительно заряженной частицы,</t>
+  </si>
+  <si>
+    <t>структурам КГБ</t>
+  </si>
+  <si>
+    <t>ведомству КГБ</t>
+  </si>
+  <si>
+    <t>Группа А. Солодилова проводила</t>
+  </si>
+  <si>
+    <t>Отдел А. Солодилова проводил</t>
+  </si>
+  <si>
+    <t>эта цивилизация могла</t>
+  </si>
+  <si>
+    <t>это общество могло</t>
+  </si>
+  <si>
+    <t>Тема применения психотронных генераторов вызвала</t>
+  </si>
+  <si>
+    <t>Вопрос применения психотронных преобразователей вызвал</t>
+  </si>
+  <si>
+    <t>весь мой изъятый потенциал</t>
+  </si>
+  <si>
+    <t>все мои изъятые возможности</t>
+  </si>
+  <si>
+    <t>живой разумный организм</t>
+  </si>
+  <si>
+    <t>живое разумное тело</t>
+  </si>
+  <si>
+    <t>эксплуатируемый всего</t>
+  </si>
+  <si>
+    <t>используемый всешл</t>
   </si>
 </sst>
 </file>
@@ -587,7 +650,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.08984375" customWidth="1"/>
@@ -599,14 +662,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B30"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A3:B33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
     <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -614,7 +677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -622,7 +685,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -630,7 +693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -638,7 +701,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -646,7 +709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -654,7 +717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -662,7 +725,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -670,7 +733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -678,7 +741,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -686,7 +749,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -694,7 +757,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -702,7 +765,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -710,7 +773,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -718,7 +781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -726,7 +789,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -734,7 +797,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -742,7 +805,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -750,7 +813,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -758,7 +821,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -766,7 +829,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -774,7 +837,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -782,7 +845,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -790,7 +853,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -798,7 +861,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -806,12 +869,36 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>73</v>
       </c>
       <c r="B30" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -822,7 +909,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -830,14 +917,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
     <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -845,7 +932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -853,7 +940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -861,7 +948,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -869,7 +956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -877,7 +964,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>59</v>
       </c>
@@ -885,7 +972,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -893,12 +980,20 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>61</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -908,14 +1003,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" customWidth="1"/>
     <col min="2" max="2" width="38.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -923,12 +1018,68 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -939,19 +1090,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470922A9-554F-4171-817B-B4542805EF8E}">
   <dimension ref="A2:A4"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4760B5DA-3139-4848-8403-DFA05C1DED05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EADCDC-3C8B-4DC3-8F2E-1EA261C5D478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25690" yWindow="0" windowWidth="12980" windowHeight="20970" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId3"/>
     <sheet name="составные важные" sheetId="1" r:id="rId4"/>
     <sheet name="Неизменные" sheetId="6" r:id="rId5"/>
-    <sheet name="Лист1" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,12 +35,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -89,15 +91,6 @@
   </si>
   <si>
     <t>предыдущих воплощениях</t>
-  </si>
-  <si>
-    <t>международной разряды,</t>
-  </si>
-  <si>
-    <t>гуру</t>
-  </si>
-  <si>
-    <t>«третьего очи»,</t>
   </si>
   <si>
     <t>магии черной или белой</t>
@@ -650,7 +643,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.08984375" customWidth="1"/>
@@ -663,13 +656,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
   <dimension ref="A3:B33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
     <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -677,7 +670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -685,7 +678,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -693,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -701,7 +694,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -709,196 +702,196 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B14" t="s">
         <v>29</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="B15" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B16" t="s">
         <v>33</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="B18" t="s">
         <v>37</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="B19" t="s">
         <v>39</v>
       </c>
-      <c r="B18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
         <v>45</v>
       </c>
-      <c r="B20" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="B22" t="s">
         <v>47</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="B23" t="s">
         <v>49</v>
       </c>
-      <c r="B22" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="B24" t="s">
         <v>51</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A25" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="B25" t="s">
         <v>53</v>
       </c>
-      <c r="B24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
         <v>65</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="B28" t="s">
         <v>67</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="B29" t="s">
         <v>69</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A30" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="B30" t="s">
         <v>71</v>
       </c>
-      <c r="B29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s">
         <v>91</v>
       </c>
-      <c r="B31" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A33" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="B33" t="s">
         <v>93</v>
-      </c>
-      <c r="B32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -909,7 +902,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -918,13 +911,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
     <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -932,7 +925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -940,7 +933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -948,52 +941,52 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
         <v>57</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B8" t="s">
         <v>59</v>
       </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1004,107 +997,82 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="46.36328125" customWidth="1"/>
     <col min="2" max="2" width="38.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
         <v>75</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
         <v>77</v>
       </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
         <v>83</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B8" t="s">
         <v>85</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
         <v>87</v>
-      </c>
-      <c r="B8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470922A9-554F-4171-817B-B4542805EF8E}">
-  <dimension ref="A2:A4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EADCDC-3C8B-4DC3-8F2E-1EA261C5D478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B4D300-5D20-44B9-BA8A-D69E9956A625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22570" yWindow="2220" windowWidth="15730" windowHeight="10140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -325,6 +325,24 @@
   </si>
   <si>
     <t>используемый всешл</t>
+  </si>
+  <si>
+    <t>создаваемый мыслеобраз должен быть полноценным и для его входа</t>
+  </si>
+  <si>
+    <t>генерируемая мыслеформа должна быть полноценна и для ее входа</t>
+  </si>
+  <si>
+    <t>брежневской эпохи</t>
+  </si>
+  <si>
+    <t>периода Брежнева</t>
+  </si>
+  <si>
+    <t>клиент-искуситель</t>
+  </si>
+  <si>
+    <t>заказчик-искуситель</t>
   </si>
 </sst>
 </file>
@@ -655,7 +673,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B33"/>
+  <dimension ref="A3:B34"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
@@ -892,6 +910,14 @@
       </c>
       <c r="B33" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="46.36328125" customWidth="1"/>
@@ -1075,6 +1101,22 @@
         <v>87</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B4D300-5D20-44B9-BA8A-D69E9956A625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E3A2DD-993E-4107-B5D9-B6C3EB40A787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22570" yWindow="2220" windowWidth="15730" windowHeight="10140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25510" yWindow="0" windowWidth="12980" windowHeight="20970" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -18,32 +18,19 @@
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId3"/>
     <sheet name="составные важные" sheetId="1" r:id="rId4"/>
     <sheet name="Неизменные" sheetId="6" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -93,6 +80,15 @@
     <t>предыдущих воплощениях</t>
   </si>
   <si>
+    <t>международной разряды,</t>
+  </si>
+  <si>
+    <t>гуру</t>
+  </si>
+  <si>
+    <t>«третьего очи»,</t>
+  </si>
+  <si>
     <t>магии черной или белой</t>
   </si>
   <si>
@@ -217,132 +213,6 @@
   </si>
   <si>
     <t>тайную и физическую особенность,так называемую</t>
-  </si>
-  <si>
-    <t>информационная составляющая через воду оказывает</t>
-  </si>
-  <si>
-    <t>имеющиеся сведения через воду оказывают</t>
-  </si>
-  <si>
-    <t>в данный реальный момент времени</t>
-  </si>
-  <si>
-    <t>в данное мгновение времени</t>
-  </si>
-  <si>
-    <t>взглянуть на микро–</t>
-  </si>
-  <si>
-    <t>взглянуть на крошечные-</t>
-  </si>
-  <si>
-    <t>строении микро–</t>
-  </si>
-  <si>
-    <t>строении крошечных-</t>
-  </si>
-  <si>
-    <t>зафиксировали все</t>
-  </si>
-  <si>
-    <t>запомнили все</t>
-  </si>
-  <si>
-    <t>магии белой или черной.</t>
-  </si>
-  <si>
-    <t>колдовства белого или черного</t>
-  </si>
-  <si>
-    <t>силами – коллапсировать</t>
-  </si>
-  <si>
-    <t>силами - схлопнуться</t>
-  </si>
-  <si>
-    <t>Своим мощнейшим потенциалом</t>
-  </si>
-  <si>
-    <t>Своими мощнейшими возможностями</t>
-  </si>
-  <si>
-    <t>апеллирует 11 законами</t>
-  </si>
-  <si>
-    <t>опирается на 11 законов</t>
-  </si>
-  <si>
-    <t>Эта техника претерпела</t>
-  </si>
-  <si>
-    <t>Эти средства претерпели</t>
-  </si>
-  <si>
-    <t>со спином протона</t>
-  </si>
-  <si>
-    <t>с вращением положительно заряженной частицы,</t>
-  </si>
-  <si>
-    <t>структурам КГБ</t>
-  </si>
-  <si>
-    <t>ведомству КГБ</t>
-  </si>
-  <si>
-    <t>Группа А. Солодилова проводила</t>
-  </si>
-  <si>
-    <t>Отдел А. Солодилова проводил</t>
-  </si>
-  <si>
-    <t>эта цивилизация могла</t>
-  </si>
-  <si>
-    <t>это общество могло</t>
-  </si>
-  <si>
-    <t>Тема применения психотронных генераторов вызвала</t>
-  </si>
-  <si>
-    <t>Вопрос применения психотронных преобразователей вызвал</t>
-  </si>
-  <si>
-    <t>весь мой изъятый потенциал</t>
-  </si>
-  <si>
-    <t>все мои изъятые возможности</t>
-  </si>
-  <si>
-    <t>живой разумный организм</t>
-  </si>
-  <si>
-    <t>живое разумное тело</t>
-  </si>
-  <si>
-    <t>эксплуатируемый всего</t>
-  </si>
-  <si>
-    <t>используемый всешл</t>
-  </si>
-  <si>
-    <t>создаваемый мыслеобраз должен быть полноценным и для его входа</t>
-  </si>
-  <si>
-    <t>генерируемая мыслеформа должна быть полноценна и для ее входа</t>
-  </si>
-  <si>
-    <t>брежневской эпохи</t>
-  </si>
-  <si>
-    <t>периода Брежнева</t>
-  </si>
-  <si>
-    <t>клиент-искуситель</t>
-  </si>
-  <si>
-    <t>заказчик-искуситель</t>
   </si>
 </sst>
 </file>
@@ -661,7 +531,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.08984375" customWidth="1"/>
@@ -673,14 +543,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B34"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A3:B25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
     <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -688,7 +558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -696,7 +566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -704,7 +574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -712,7 +582,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -720,204 +590,132 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A28" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A29" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A31" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A34" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -928,7 +726,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -936,14 +734,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
     <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -959,7 +757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -967,52 +765,28 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
         <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1022,99 +796,52 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" customWidth="1"/>
     <col min="2" max="2" width="38.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470922A9-554F-4171-817B-B4542805EF8E}">
+  <dimension ref="A2:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B4D300-5D20-44B9-BA8A-D69E9956A625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A18254-7CA5-4ABA-8780-E8F342F7143B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22570" yWindow="2220" windowWidth="15730" windowHeight="10140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>заказчик-искуситель</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> любая гипотеза становится теорией только тогда, когда у нее</t>
+  </si>
+  <si>
+    <t>любое предположение становится учением только тогда, когда у него</t>
   </si>
 </sst>
 </file>
@@ -661,7 +667,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.08984375" customWidth="1"/>
@@ -674,13 +680,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
   <dimension ref="A3:B34"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.6328125" customWidth="1"/>
     <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -688,7 +694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -696,7 +702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -704,7 +710,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -712,7 +718,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -720,7 +726,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -728,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -736,7 +742,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -744,7 +750,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -752,7 +758,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -760,7 +766,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -768,7 +774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -776,7 +782,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -784,7 +790,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -792,7 +798,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -800,7 +806,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -808,7 +814,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -816,7 +822,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -824,7 +830,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -832,7 +838,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -840,7 +846,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -848,7 +854,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -856,7 +862,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -864,7 +870,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -872,7 +878,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -880,7 +886,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -888,7 +894,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -896,7 +902,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -904,7 +910,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -912,7 +918,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -928,7 +934,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -937,13 +943,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
     <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -959,7 +965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -967,7 +973,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -975,7 +981,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -983,7 +989,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -991,7 +997,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -999,7 +1005,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1007,7 +1013,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -1022,14 +1028,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" customWidth="1"/>
     <col min="2" max="2" width="38.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1037,7 +1043,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1045,7 +1051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1053,7 +1059,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1061,7 +1067,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1069,7 +1075,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1077,7 +1083,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1085,7 +1091,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -1093,7 +1099,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -1101,7 +1107,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -1109,12 +1115,20 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>96</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A18254-7CA5-4ABA-8780-E8F342F7143B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7123F203-4E56-4328-9E9C-A6545D8EB8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -349,19 +349,174 @@
   </si>
   <si>
     <t>любое предположение становится учением только тогда, когда у него</t>
+  </si>
+  <si>
+    <t>Форма нашего тела не случайна</t>
+  </si>
+  <si>
+    <t>Вид нашего тела не случаен</t>
+  </si>
+  <si>
+    <t>наша цивилизация пока является лишь псевдоразумной</t>
+  </si>
+  <si>
+    <t>наше общество является пока лишь лжеразумным</t>
+  </si>
+  <si>
+    <t>серьезнейшим нарушением</t>
+  </si>
+  <si>
+    <t>серьезнейшим нарушениям</t>
+  </si>
+  <si>
+    <t>отправить писателю</t>
+  </si>
+  <si>
+    <t>Началась всеобщая профанация</t>
+  </si>
+  <si>
+    <t>началось всеобщее осквернение</t>
+  </si>
+  <si>
+    <t>собран неопровержимый фактический материал на эту тему.</t>
+  </si>
+  <si>
+    <t>собраны неопровержимые достоверные подтверждения на этот вопрос</t>
+  </si>
+  <si>
+    <t>наша цивилизация должна была задохнуться</t>
+  </si>
+  <si>
+    <t>наше общество должно было задохнуться</t>
+  </si>
+  <si>
+    <t>из этого, правильного на первый взгляд, текста.</t>
+  </si>
+  <si>
+    <t>из этого, правильного на первый взгляд, письменного источника</t>
+  </si>
+  <si>
+    <t>Любая информация из Информационных Полей должна восприниматься</t>
+  </si>
+  <si>
+    <t>Любые сведения из несущих сведения Полей должны восприниматься</t>
+  </si>
+  <si>
+    <t>была обнаружена правая поляризация</t>
+  </si>
+  <si>
+    <t>было обнаружено первое изменение</t>
+  </si>
+  <si>
+    <t>Создание единой планетарной цивилизации</t>
+  </si>
+  <si>
+    <t>Создание единого планетарного общества</t>
+  </si>
+  <si>
+    <t>нашей планетарной цивилизации</t>
+  </si>
+  <si>
+    <t>нашего планетарного общества</t>
+  </si>
+  <si>
+    <t>нанесший российскому генофонду сильнейшую деформацию</t>
+  </si>
+  <si>
+    <t>нанесший российской наследственности сильнейшее повреждение</t>
+  </si>
+  <si>
+    <t>форма власти не менялась</t>
+  </si>
+  <si>
+    <t>образ власти не менялся</t>
+  </si>
+  <si>
+    <t>Типичный пример такого контакта</t>
+  </si>
+  <si>
+    <t>Обычный пример такой связи</t>
+  </si>
+  <si>
+    <t>любой количественный образ неким способом создаёт вокруг себя пространство</t>
+  </si>
+  <si>
+    <t>любая объемная форма неким образом структурирует вокруг себя пространство</t>
+  </si>
+  <si>
+    <t>Нас пока интересует возможность</t>
+  </si>
+  <si>
+    <t>Нам пока необходима возможность</t>
+  </si>
+  <si>
+    <t>готическую архитектуру</t>
+  </si>
+  <si>
+    <t>готическое зодчество</t>
+  </si>
+  <si>
+    <t>прапорщик в армии</t>
+  </si>
+  <si>
+    <t>прапорщик в вооружённых силах</t>
+  </si>
+  <si>
+    <t>Принцип действия подобных мыслеформ вполне понятен</t>
+  </si>
+  <si>
+    <t>Правило действия подобных мыслеобразов вполне понятно</t>
+  </si>
+  <si>
+    <t>Этот книгопечатный “произведение искусства” В. Приваловой сразу же привлек</t>
+  </si>
+  <si>
+    <t>Это книгопечатное “произведение искусства” В. Приваловой сразу же привлекло</t>
+  </si>
+  <si>
+    <t>Новошахтинской научно-исследовательской исследовательские отделы</t>
+  </si>
+  <si>
+    <t>Новошахтинскгой научно-исследовательского отдела</t>
+  </si>
+  <si>
+    <t>Не бывает магии белой или черной.</t>
+  </si>
+  <si>
+    <t>Не бывает колдовства белого или черного</t>
+  </si>
+  <si>
+    <t>следовать люди с</t>
+  </si>
+  <si>
+    <t>следовать кадры с</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -384,8 +539,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -667,10 +827,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7265625" customWidth="1"/>
-    <col min="2" max="2" width="20.08984375" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -680,13 +840,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
   <dimension ref="A3:B34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.6328125" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" customWidth="1"/>
+    <col min="1" max="1" width="47.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -694,7 +854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -702,7 +862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -710,7 +870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -718,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -726,7 +886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -734,7 +894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -742,7 +902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -750,7 +910,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -758,7 +918,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -766,7 +926,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -774,7 +934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -782,7 +942,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -790,7 +950,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -798,7 +958,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -806,7 +966,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -814,7 +974,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -822,7 +982,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -830,7 +990,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -838,7 +998,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -846,7 +1006,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -854,7 +1014,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -862,7 +1022,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -870,7 +1030,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -878,7 +1038,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -886,7 +1046,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -894,7 +1054,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -902,7 +1062,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -910,7 +1070,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -918,7 +1078,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -934,7 +1094,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -942,14 +1102,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="65.453125" customWidth="1"/>
-    <col min="2" max="2" width="77.36328125" customWidth="1"/>
+    <col min="1" max="1" width="65.42578125" customWidth="1"/>
+    <col min="2" max="2" width="77.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -957,7 +1117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -965,7 +1125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -973,7 +1133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -981,7 +1141,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -989,7 +1149,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -997,7 +1157,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -1005,7 +1165,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1013,12 +1173,103 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>78</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1028,14 +1279,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.36328125" customWidth="1"/>
-    <col min="2" max="2" width="38.54296875" customWidth="1"/>
+    <col min="1" max="1" width="66.5703125" customWidth="1"/>
+    <col min="2" max="2" width="70.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1043,7 +1294,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1051,7 +1302,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1059,7 +1310,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1067,7 +1318,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1075,7 +1326,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1083,7 +1334,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1091,7 +1342,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -1099,7 +1350,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -1107,7 +1358,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -1115,7 +1366,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -1123,12 +1374,108 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>100</v>
       </c>
       <c r="B12" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7123F203-4E56-4328-9E9C-A6545D8EB8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5EB3FF-B90E-4D4B-87AE-FAF112BE4373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23340" yWindow="0" windowWidth="15150" windowHeight="20970" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -35,15 +35,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -490,6 +487,30 @@
   </si>
   <si>
     <t>следовать кадры с</t>
+  </si>
+  <si>
+    <t>торсионной астрономии</t>
+  </si>
+  <si>
+    <t>скрученного звёздоведения</t>
+  </si>
+  <si>
+    <t>Этот каталог можно получить</t>
+  </si>
+  <si>
+    <t>эту папку можно получить</t>
+  </si>
+  <si>
+    <t>Этот эффект был великолепно экспериментально доказан</t>
+  </si>
+  <si>
+    <t>это последствие было великолепноопытно доказано академиком</t>
+  </si>
+  <si>
+    <t>большой «скрытой массы»</t>
+  </si>
+  <si>
+    <t>большого «скрытого вещества»</t>
   </si>
 </sst>
 </file>
@@ -827,10 +848,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -839,14 +860,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:B35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="1" max="1" width="47.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -854,7 +875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -862,7 +883,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -870,7 +891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -878,7 +899,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -886,7 +907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -894,7 +915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -902,7 +923,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -910,7 +931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -918,7 +939,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -926,7 +947,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -934,7 +955,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -942,7 +963,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -950,7 +971,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -958,7 +979,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -966,7 +987,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -974,7 +995,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -982,7 +1003,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -990,7 +1011,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -998,7 +1019,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1006,7 +1027,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1014,7 +1035,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1022,7 +1043,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1030,7 +1051,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1038,7 +1059,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1046,7 +1067,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1054,7 +1075,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -1062,7 +1083,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -1070,7 +1091,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -1078,12 +1099,20 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>98</v>
       </c>
       <c r="B34" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1093,23 +1122,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.42578125" customWidth="1"/>
-    <col min="2" max="2" width="77.42578125" customWidth="1"/>
+    <col min="1" max="1" width="65.453125" customWidth="1"/>
+    <col min="2" max="2" width="77.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1117,7 +1158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1125,7 +1166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1133,7 +1174,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1141,7 +1182,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1149,7 +1190,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -1157,7 +1198,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -1165,7 +1206,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1214,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -1181,7 +1222,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>102</v>
       </c>
@@ -1189,7 +1230,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>104</v>
       </c>
@@ -1197,7 +1238,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>106</v>
       </c>
@@ -1208,7 +1249,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>109</v>
       </c>
@@ -1216,7 +1257,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>111</v>
       </c>
@@ -1224,7 +1265,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -1232,7 +1273,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -1240,7 +1281,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -1248,7 +1289,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -1256,7 +1297,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>135</v>
       </c>
@@ -1264,12 +1305,28 @@
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>137</v>
       </c>
       <c r="B20" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1280,13 +1337,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="66.5703125" customWidth="1"/>
-    <col min="2" max="2" width="70.140625" customWidth="1"/>
+    <col min="1" max="1" width="66.54296875" customWidth="1"/>
+    <col min="2" max="2" width="70.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1294,7 +1351,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1302,7 +1359,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1310,7 +1367,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1318,7 +1375,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1326,7 +1383,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1334,7 +1391,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1342,7 +1399,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -1350,7 +1407,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -1358,7 +1415,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -1366,7 +1423,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -1374,7 +1431,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -1382,7 +1439,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -1390,7 +1447,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -1398,7 +1455,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -1406,7 +1463,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>127</v>
       </c>
@@ -1414,7 +1471,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -1422,7 +1479,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
@@ -1430,7 +1487,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>133</v>
       </c>
@@ -1438,7 +1495,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -1446,7 +1503,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -1454,7 +1511,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -1462,7 +1519,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>145</v>
       </c>
@@ -1470,7 +1527,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>148</v>
       </c>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5EB3FF-B90E-4D4B-87AE-FAF112BE4373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7123F203-4E56-4328-9E9C-A6545D8EB8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23340" yWindow="0" windowWidth="15150" windowHeight="20970" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -35,12 +35,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -487,30 +490,6 @@
   </si>
   <si>
     <t>следовать кадры с</t>
-  </si>
-  <si>
-    <t>торсионной астрономии</t>
-  </si>
-  <si>
-    <t>скрученного звёздоведения</t>
-  </si>
-  <si>
-    <t>Этот каталог можно получить</t>
-  </si>
-  <si>
-    <t>эту папку можно получить</t>
-  </si>
-  <si>
-    <t>Этот эффект был великолепно экспериментально доказан</t>
-  </si>
-  <si>
-    <t>это последствие было великолепноопытно доказано академиком</t>
-  </si>
-  <si>
-    <t>большой «скрытой массы»</t>
-  </si>
-  <si>
-    <t>большого «скрытого вещества»</t>
   </si>
 </sst>
 </file>
@@ -848,10 +827,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7265625" customWidth="1"/>
-    <col min="2" max="2" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -860,14 +839,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A3:B34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" customWidth="1"/>
+    <col min="1" max="1" width="47.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -875,7 +854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -883,7 +862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -891,7 +870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -899,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -907,7 +886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -915,7 +894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -923,7 +902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -931,7 +910,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -939,7 +918,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -947,7 +926,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -955,7 +934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -963,7 +942,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -971,7 +950,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -979,7 +958,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -987,7 +966,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -995,7 +974,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1003,7 +982,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1011,7 +990,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -1019,7 +998,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1027,7 +1006,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1035,7 +1014,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1043,7 +1022,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1051,7 +1030,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1059,7 +1038,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1067,7 +1046,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1075,7 +1054,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -1083,7 +1062,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -1091,7 +1070,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -1099,20 +1078,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>98</v>
       </c>
       <c r="B34" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>149</v>
-      </c>
-      <c r="B35" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1122,35 +1093,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="32.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="65.453125" customWidth="1"/>
-    <col min="2" max="2" width="77.453125" customWidth="1"/>
+    <col min="1" max="1" width="65.42578125" customWidth="1"/>
+    <col min="2" max="2" width="77.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1158,7 +1117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1166,7 +1125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1174,7 +1133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1182,7 +1141,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1190,7 +1149,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -1198,7 +1157,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -1206,7 +1165,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1214,7 +1173,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -1222,7 +1181,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>102</v>
       </c>
@@ -1230,7 +1189,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>104</v>
       </c>
@@ -1238,7 +1197,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>106</v>
       </c>
@@ -1249,7 +1208,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>109</v>
       </c>
@@ -1257,7 +1216,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>111</v>
       </c>
@@ -1265,7 +1224,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -1273,7 +1232,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -1281,7 +1240,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -1289,7 +1248,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -1297,7 +1256,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>135</v>
       </c>
@@ -1305,28 +1264,12 @@
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>137</v>
       </c>
       <c r="B20" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B21" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>153</v>
-      </c>
-      <c r="B22" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1337,13 +1280,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.54296875" customWidth="1"/>
-    <col min="2" max="2" width="70.1796875" customWidth="1"/>
+    <col min="1" max="1" width="66.5703125" customWidth="1"/>
+    <col min="2" max="2" width="70.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1351,7 +1294,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1359,7 +1302,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1367,7 +1310,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1375,7 +1318,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1383,7 +1326,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1391,7 +1334,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1399,7 +1342,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -1407,7 +1350,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -1415,7 +1358,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -1423,7 +1366,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -1431,7 +1374,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -1439,7 +1382,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -1447,7 +1390,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -1455,7 +1398,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -1463,7 +1406,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>127</v>
       </c>
@@ -1471,7 +1414,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -1479,7 +1422,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
@@ -1487,7 +1430,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>133</v>
       </c>
@@ -1495,7 +1438,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -1503,7 +1446,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -1511,7 +1454,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -1519,7 +1462,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>145</v>
       </c>
@@ -1527,7 +1470,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>148</v>
       </c>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7123F203-4E56-4328-9E9C-A6545D8EB8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E45FCE-91DF-4C18-B03A-E72753A7A27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -490,6 +490,48 @@
   </si>
   <si>
     <t>следовать кадры с</t>
+  </si>
+  <si>
+    <t>торсионной астрономии</t>
+  </si>
+  <si>
+    <t>скрученного звёздоведения</t>
+  </si>
+  <si>
+    <t>Этот каталог можно получить</t>
+  </si>
+  <si>
+    <t>эту папку можно получить</t>
+  </si>
+  <si>
+    <t>Этот эффект был великолепно экспериментально доказан</t>
+  </si>
+  <si>
+    <t>это последствие было великолепноопытно доказано академиком</t>
+  </si>
+  <si>
+    <t>большой «скрытой массы»</t>
+  </si>
+  <si>
+    <t>большого «скрытого вещества»</t>
+  </si>
+  <si>
+    <t>Информация “считывается”</t>
+  </si>
+  <si>
+    <t>сведения считываются</t>
+  </si>
+  <si>
+    <t>«считывается» информация</t>
+  </si>
+  <si>
+    <t>«считываются» сведения</t>
+  </si>
+  <si>
+    <t>как и самой магии</t>
+  </si>
+  <si>
+    <t>как и самому колдовству</t>
   </si>
 </sst>
 </file>
@@ -839,7 +881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B34"/>
+  <dimension ref="A3:B35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.5703125" customWidth="1"/>
@@ -1086,6 +1128,14 @@
         <v>99</v>
       </c>
     </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1093,16 +1143,36 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.42578125" customWidth="1"/>
@@ -1272,6 +1342,22 @@
         <v>138</v>
       </c>
     </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" t="s">
+        <v>154</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1279,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" customWidth="1"/>
@@ -1478,6 +1564,22 @@
         <v>147</v>
       </c>
     </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>159</v>
+      </c>
+      <c r="B26" t="s">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E45FCE-91DF-4C18-B03A-E72753A7A27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CC1521-AA05-4631-B880-E61CAC27CF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -532,6 +532,60 @@
   </si>
   <si>
     <t>как и самому колдовству</t>
+  </si>
+  <si>
+    <t>выражение: “Лечим болезнь…” по крайней мере глупо</t>
+  </si>
+  <si>
+    <t>фраза: “Лечим болезнь…” по крайней мере глупа</t>
+  </si>
+  <si>
+    <t>сама медицина по уши погрязла</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> само целительство по уши погрязло</t>
+  </si>
+  <si>
+    <t>метастазную форму</t>
+  </si>
+  <si>
+    <t>охваченный очагом злокачественной опухли образ</t>
+  </si>
+  <si>
+    <t>на тот же географический меридиан</t>
+  </si>
+  <si>
+    <t>на ту же землераздельную ось</t>
+  </si>
+  <si>
+    <t>интересную статистику, которая по-новому позволила</t>
+  </si>
+  <si>
+    <t>увлекательный подсчёт, который по-новому позволил</t>
+  </si>
+  <si>
+    <t>Этот книгопечатный “шедевр”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это книгопечатное “произведение искусства” </t>
+  </si>
+  <si>
+    <t>начался грандиозный судебный процесс</t>
+  </si>
+  <si>
+    <t>началось непостижимое судебное разбирательство</t>
+  </si>
+  <si>
+    <t>международной медицинской мафиозной структурой</t>
+  </si>
+  <si>
+    <t>международным целительским преступным сообществом</t>
+  </si>
+  <si>
+    <t>Одесский филиал</t>
+  </si>
+  <si>
+    <t>Одесское подразделение</t>
   </si>
 </sst>
 </file>
@@ -869,10 +923,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="2" max="2" width="20.1328125" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -881,14 +935,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:B36"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="47.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="1" max="1" width="47.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -896,7 +950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -904,7 +958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -912,7 +966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -920,7 +974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -928,7 +982,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -936,7 +990,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -944,7 +998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -952,7 +1006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -960,7 +1014,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -968,7 +1022,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -976,7 +1030,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -984,7 +1038,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -992,7 +1046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1000,7 +1054,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1008,7 +1062,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1016,7 +1070,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1024,7 +1078,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1032,7 +1086,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -1040,7 +1094,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1048,7 +1102,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1056,7 +1110,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1064,7 +1118,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1072,7 +1126,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1080,7 +1134,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1088,7 +1142,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1096,7 +1150,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -1104,7 +1158,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -1112,7 +1166,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -1120,7 +1174,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -1128,12 +1182,20 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>149</v>
       </c>
       <c r="B35" t="s">
         <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A36" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1144,12 +1206,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+    <col min="1" max="1" width="32.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>155</v>
       </c>
@@ -1157,7 +1219,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>161</v>
       </c>
@@ -1173,13 +1235,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="65.42578125" customWidth="1"/>
-    <col min="2" max="2" width="77.42578125" customWidth="1"/>
+    <col min="1" max="1" width="65.40625" customWidth="1"/>
+    <col min="2" max="2" width="77.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1187,7 +1249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1195,7 +1257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1203,7 +1265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1211,7 +1273,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1219,7 +1281,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -1227,7 +1289,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -1235,7 +1297,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1243,7 +1305,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -1251,7 +1313,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>102</v>
       </c>
@@ -1259,7 +1321,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>104</v>
       </c>
@@ -1267,7 +1329,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>106</v>
       </c>
@@ -1278,7 +1340,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>109</v>
       </c>
@@ -1286,7 +1348,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>111</v>
       </c>
@@ -1294,7 +1356,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -1302,7 +1364,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -1310,7 +1372,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -1318,7 +1380,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -1326,7 +1388,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>135</v>
       </c>
@@ -1334,7 +1396,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>137</v>
       </c>
@@ -1342,7 +1404,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>151</v>
       </c>
@@ -1350,7 +1412,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>153</v>
       </c>
@@ -1365,14 +1427,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="66.5703125" customWidth="1"/>
-    <col min="2" max="2" width="70.140625" customWidth="1"/>
+    <col min="1" max="1" width="66.54296875" customWidth="1"/>
+    <col min="2" max="2" width="70.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1380,7 +1442,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1388,7 +1450,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1396,7 +1458,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1404,7 +1466,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1412,7 +1474,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1420,7 +1482,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1428,7 +1490,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -1436,7 +1498,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -1444,7 +1506,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -1452,7 +1514,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -1460,7 +1522,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -1468,7 +1530,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -1476,7 +1538,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -1484,7 +1546,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -1492,7 +1554,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>127</v>
       </c>
@@ -1500,7 +1562,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -1508,7 +1570,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
@@ -1516,7 +1578,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>133</v>
       </c>
@@ -1524,7 +1586,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -1532,7 +1594,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -1540,7 +1602,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -1548,7 +1610,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>145</v>
       </c>
@@ -1556,7 +1618,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>148</v>
       </c>
@@ -1564,7 +1626,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>157</v>
       </c>
@@ -1572,12 +1634,76 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>159</v>
       </c>
       <c r="B26" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A31" t="s">
+        <v>173</v>
+      </c>
+      <c r="B31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CC1521-AA05-4631-B880-E61CAC27CF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AF7309-E366-49A3-BD68-78D08628BBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,11 @@
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId3"/>
     <sheet name="составные важные" sheetId="1" r:id="rId4"/>
     <sheet name="Неизменные" sheetId="6" r:id="rId5"/>
+    <sheet name="создателю ошибки" sheetId="7" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'составные важные'!$A$1:$B$28</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="323">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -586,6 +590,432 @@
   </si>
   <si>
     <t>Одесское подразделение</t>
+  </si>
+  <si>
+    <t>При этом многолетний анализ причин тех или иных заболеваний показал</t>
+  </si>
+  <si>
+    <t>При этом многолетняя оценка причин тех или иных заболеваний показала</t>
+  </si>
+  <si>
+    <t>с точки зрения эниологии</t>
+  </si>
+  <si>
+    <t>был обнаружен сильнейший стресс, связанный</t>
+  </si>
+  <si>
+    <t>было обнаружено сильнейшее перенапряжение, связанное</t>
+  </si>
+  <si>
+    <t>В армянской магии</t>
+  </si>
+  <si>
+    <t>в армянском колдовстве</t>
+  </si>
+  <si>
+    <t>наилучший «целебный эффект»</t>
+  </si>
+  <si>
+    <t>наилучшее «целебное последствие»</t>
+  </si>
+  <si>
+    <t>магов, колдунов</t>
+  </si>
+  <si>
+    <t>чудотворцев, колдунов</t>
+  </si>
+  <si>
+    <t>в некий живой разумный потусторонне-мыслительный живая особь, для жизнеобеспечения которого</t>
+  </si>
+  <si>
+    <t>в некую живую разумную потусторонне-мыслительную сущность, для жизнеобеспечения которой</t>
+  </si>
+  <si>
+    <t>саморазвивающийся паразитирующий разумный организм</t>
+  </si>
+  <si>
+    <t>саморазвивающаяся порабощающая разумная живая особь</t>
+  </si>
+  <si>
+    <t>имярек</t>
+  </si>
+  <si>
+    <t>вербальная магия представлена</t>
+  </si>
+  <si>
+    <t>словесное колдовство представлено</t>
+  </si>
+  <si>
+    <t>современная медицина попыталась</t>
+  </si>
+  <si>
+    <t>современное целительство попыталось</t>
+  </si>
+  <si>
+    <t>сделав медицину своей служанкой</t>
+  </si>
+  <si>
+    <t>сделав целительство себе прислугой</t>
+  </si>
+  <si>
+    <t>В медицинской энциклопедии</t>
+  </si>
+  <si>
+    <t>В целительском справочнике</t>
+  </si>
+  <si>
+    <t>Донор, начав сдавать кровь, (рис. 105) вынужден был это делать потом постоянно, иначе у него</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Жертва, начав сдавать кровь, (рис. 105) вынуждена была это делать потом постоянно, иначе у неё</t>
+  </si>
+  <si>
+    <t>некий эгрегор, «замешанный на крови»</t>
+  </si>
+  <si>
+    <t>некое совместное сознание, «замешанное на крови»</t>
+  </si>
+  <si>
+    <t>мата в эволюции российского этноса</t>
+  </si>
+  <si>
+    <t>мата в развитии российской народности</t>
+  </si>
+  <si>
+    <t>мыслеформа и мыслеобраз являются категориями</t>
+  </si>
+  <si>
+    <t>мыслеобраз является понятием</t>
+  </si>
+  <si>
+    <t>в некий энергоинформационный «банк»</t>
+  </si>
+  <si>
+    <t>в некое вездесущее «хранилище»</t>
+  </si>
+  <si>
+    <t>с точки зрения вездесущности</t>
+  </si>
+  <si>
+    <t>“чистая энергия”, которая</t>
+  </si>
+  <si>
+    <t>“чистый заряд”, который</t>
+  </si>
+  <si>
+    <t>энергоинформационного потенциала</t>
+  </si>
+  <si>
+    <t>вездесущих возможностей</t>
+  </si>
+  <si>
+    <t>бабушка сказал</t>
+  </si>
+  <si>
+    <t>энергоинформационной коррекции</t>
+  </si>
+  <si>
+    <t>вездесущего изменения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">эниокорректора </t>
+  </si>
+  <si>
+    <t>вездесущего изменителя</t>
+  </si>
+  <si>
+    <t>эниокорректор</t>
+  </si>
+  <si>
+    <t>вездесущий изменитель</t>
+  </si>
+  <si>
+    <t>эниокорректорам</t>
+  </si>
+  <si>
+    <t>вездесущим изменителям</t>
+  </si>
+  <si>
+    <t>эниокорректорами</t>
+  </si>
+  <si>
+    <t>вездесущими изменителями</t>
+  </si>
+  <si>
+    <t>эниокорректорах</t>
+  </si>
+  <si>
+    <t>вездесущих изменителях</t>
+  </si>
+  <si>
+    <t>эниокорректоре</t>
+  </si>
+  <si>
+    <t>вездесущем изменителе</t>
+  </si>
+  <si>
+    <t>эниокорректору</t>
+  </si>
+  <si>
+    <t>вездесущему изменителю</t>
+  </si>
+  <si>
+    <t>эниокорректоры</t>
+  </si>
+  <si>
+    <t>вездесущие изменители</t>
+  </si>
+  <si>
+    <t>эниокорректором</t>
+  </si>
+  <si>
+    <t>вездесущим изменителем</t>
+  </si>
+  <si>
+    <t>эниокорректоров</t>
+  </si>
+  <si>
+    <t>вездесущих изменителей</t>
+  </si>
+  <si>
+    <t>колдовским и магическим</t>
+  </si>
+  <si>
+    <t>колдовским</t>
+  </si>
+  <si>
+    <t>свои пространство и время.</t>
+  </si>
+  <si>
+    <t>кто заинтересован в этом полтергейсте</t>
+  </si>
+  <si>
+    <t>кто нуждается в этом барабашке</t>
+  </si>
+  <si>
+    <t>Мыслеобраз преобразуется в мыслеформу</t>
+  </si>
+  <si>
+    <t>Мыслеобраз преобразуется</t>
+  </si>
+  <si>
+    <t>тот магический эгрегор, который в данном «спектакле» принимал</t>
+  </si>
+  <si>
+    <t>то колдовское совместное сознание, которое в данном «представлении» принимало</t>
+  </si>
+  <si>
+    <t>к обоим сущностям</t>
+  </si>
+  <si>
+    <t>её необходимо родиться</t>
+  </si>
+  <si>
+    <t>но с стой</t>
+  </si>
+  <si>
+    <t>насаждаемая правящей элитой</t>
+  </si>
+  <si>
+    <t>насаждаемое правящей знатью</t>
+  </si>
+  <si>
+    <t>всю необходимую для нормализации целого семейства информацию</t>
+  </si>
+  <si>
+    <t>все необходимые для налаживания целого семейства сведения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">энергоинформационную </t>
+  </si>
+  <si>
+    <t>вездесущную</t>
+  </si>
+  <si>
+    <t>энергоинформационную коррекцию</t>
+  </si>
+  <si>
+    <t>вездесущное изменение</t>
+  </si>
+  <si>
+    <t>трехмерного, природного колдовства</t>
+  </si>
+  <si>
+    <t>трехмерной, биологической магии</t>
+  </si>
+  <si>
+    <t>свой энергоинформационный потенциал</t>
+  </si>
+  <si>
+    <t>свои вездесущные возможности</t>
+  </si>
+  <si>
+    <t>на жителей европейских стран.</t>
+  </si>
+  <si>
+    <t>энергоинформационна</t>
+  </si>
+  <si>
+    <t>вездесущна</t>
+  </si>
+  <si>
+    <t>энергоинформационная</t>
+  </si>
+  <si>
+    <t>вездесущная</t>
+  </si>
+  <si>
+    <t>энергоинформационно</t>
+  </si>
+  <si>
+    <t>вездесущно</t>
+  </si>
+  <si>
+    <t>энергоинформационное</t>
+  </si>
+  <si>
+    <t>вездесущное</t>
+  </si>
+  <si>
+    <t>энергоинформационном</t>
+  </si>
+  <si>
+    <t>вездесущном</t>
+  </si>
+  <si>
+    <t>энергоинформационному</t>
+  </si>
+  <si>
+    <t>вездесущному</t>
+  </si>
+  <si>
+    <t>энергоинформационной</t>
+  </si>
+  <si>
+    <t>вездесущной</t>
+  </si>
+  <si>
+    <t>энергоинформационного</t>
+  </si>
+  <si>
+    <t>вездесущного</t>
+  </si>
+  <si>
+    <t>энергоинформационны</t>
+  </si>
+  <si>
+    <t>вездесущны</t>
+  </si>
+  <si>
+    <t>энергоинформационные</t>
+  </si>
+  <si>
+    <t>вездесущные</t>
+  </si>
+  <si>
+    <t>энергоинформационным</t>
+  </si>
+  <si>
+    <t>вездесущным</t>
+  </si>
+  <si>
+    <t>энергоинформационными</t>
+  </si>
+  <si>
+    <t>вездесущными</t>
+  </si>
+  <si>
+    <t>энергоинформационный</t>
+  </si>
+  <si>
+    <t>вездесущный</t>
+  </si>
+  <si>
+    <t>энергоинформационных</t>
+  </si>
+  <si>
+    <t>вездесущных</t>
+  </si>
+  <si>
+    <t>Энергоинформационностей</t>
+  </si>
+  <si>
+    <t>вездесущностей</t>
+  </si>
+  <si>
+    <t>Энергоинформационности</t>
+  </si>
+  <si>
+    <t>вездесущности</t>
+  </si>
+  <si>
+    <t>Энергоинформационность</t>
+  </si>
+  <si>
+    <t>вездесущность</t>
+  </si>
+  <si>
+    <t>Энергоинформационностью</t>
+  </si>
+  <si>
+    <t>вездесущностью</t>
+  </si>
+  <si>
+    <t>Энергоинформационностям</t>
+  </si>
+  <si>
+    <t>вездесущностям</t>
+  </si>
+  <si>
+    <t>Энергоинформационностями</t>
+  </si>
+  <si>
+    <t>вездесущностями</t>
+  </si>
+  <si>
+    <t>индийский магический клан был вынужден</t>
+  </si>
+  <si>
+    <t>индийская колдовская семья была вынуждена</t>
+  </si>
+  <si>
+    <t>Энергоинформационный анализ</t>
+  </si>
+  <si>
+    <t>вездесущная оценка</t>
+  </si>
+  <si>
+    <t>не хватает многих компонент</t>
+  </si>
+  <si>
+    <t>на этой «запрещенной» орбите</t>
+  </si>
+  <si>
+    <t>на этом «запрещенном» витке</t>
+  </si>
+  <si>
+    <t>Тестовая ситуация в автобусе произошла</t>
+  </si>
+  <si>
+    <t>Проверочный случай в автобусе произошёл</t>
+  </si>
+  <si>
+    <t>целый колдовской клан</t>
+  </si>
+  <si>
+    <t>целую колдовскую семью</t>
+  </si>
+  <si>
+    <t>весь грандиозный многомерный организм</t>
+  </si>
+  <si>
+    <t>вся выдающаяся многомерная живая особь</t>
+  </si>
+  <si>
+    <t>эзотерический клан, руководимый</t>
+  </si>
+  <si>
+    <t>тайное сообщество, руководимое</t>
   </si>
 </sst>
 </file>
@@ -922,27 +1352,383 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B57"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.7265625" customWidth="1"/>
-    <col min="2" max="2" width="20.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.921875" customWidth="1"/>
+    <col min="2" max="2" width="42.53515625" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>278</v>
+      </c>
+      <c r="B8" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B15" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>284</v>
+      </c>
+      <c r="B16" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>286</v>
+      </c>
+      <c r="B18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>288</v>
+      </c>
+      <c r="B20" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>290</v>
+      </c>
+      <c r="B21" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>294</v>
+      </c>
+      <c r="B22" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>225</v>
+      </c>
+      <c r="B23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>223</v>
+      </c>
+      <c r="B24" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>227</v>
+      </c>
+      <c r="B25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B26" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>231</v>
+      </c>
+      <c r="B27" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>233</v>
+      </c>
+      <c r="B28" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>241</v>
+      </c>
+      <c r="B29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>239</v>
+      </c>
+      <c r="B30" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B57">
+    <sortCondition ref="A1:A57"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B36"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A3:B41"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="47.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" customWidth="1"/>
+    <col min="1" max="1" width="47.53515625" customWidth="1"/>
+    <col min="2" max="2" width="27.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -950,7 +1736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -958,7 +1744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -966,7 +1752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -974,7 +1760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -982,7 +1768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -990,7 +1776,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -998,7 +1784,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1006,7 +1792,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1014,7 +1800,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1022,7 +1808,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1030,7 +1816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1038,7 +1824,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1046,7 +1832,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1054,7 +1840,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1062,7 +1848,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1070,7 +1856,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1078,7 +1864,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1086,7 +1872,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -1094,7 +1880,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1102,7 +1888,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1110,7 +1896,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1118,7 +1904,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1126,7 +1912,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1134,7 +1920,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1142,7 +1928,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1150,23 +1936,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A31" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -1174,7 +1944,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -1182,7 +1952,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -1190,12 +1960,52 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>167</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>218</v>
+      </c>
+      <c r="B37" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>221</v>
+      </c>
+      <c r="B38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>243</v>
+      </c>
+      <c r="B39" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>261</v>
+      </c>
+      <c r="B40" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>310</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -1206,12 +2016,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32.86328125" customWidth="1"/>
+    <col min="1" max="1" width="32.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>155</v>
       </c>
@@ -1219,7 +2029,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>161</v>
       </c>
@@ -1234,207 +2044,267 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="65.40625" customWidth="1"/>
-    <col min="2" max="2" width="77.40625" customWidth="1"/>
+    <col min="1" max="1" width="65.3828125" customWidth="1"/>
+    <col min="2" max="2" width="77.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A12" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>107</v>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" t="s">
+        <v>138</v>
       </c>
       <c r="C12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B24" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>246</v>
+      </c>
+      <c r="B25" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>264</v>
+      </c>
+      <c r="B26" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>265</v>
+      </c>
+      <c r="B28" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>321</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B28" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B28">
+    <sortCondition ref="A1:A28"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B63"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="66.54296875" customWidth="1"/>
-    <col min="2" max="2" width="70.1328125" customWidth="1"/>
+    <col min="1" max="1" width="66.53515625" customWidth="1"/>
+    <col min="2" max="2" width="70.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1442,7 +2312,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1450,7 +2320,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1458,7 +2328,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1466,7 +2336,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1474,7 +2344,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1482,7 +2352,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1490,7 +2360,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -1498,7 +2368,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -1506,7 +2376,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -1514,7 +2384,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -1522,7 +2392,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -1530,7 +2400,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -1538,7 +2408,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -1546,7 +2416,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -1554,7 +2424,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>127</v>
       </c>
@@ -1562,7 +2432,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -1570,7 +2440,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
@@ -1578,7 +2448,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>133</v>
       </c>
@@ -1586,7 +2456,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -1594,7 +2464,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -1602,7 +2472,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -1610,7 +2480,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>145</v>
       </c>
@@ -1618,7 +2488,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>148</v>
       </c>
@@ -1626,7 +2496,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>157</v>
       </c>
@@ -1634,7 +2504,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>159</v>
       </c>
@@ -1642,7 +2512,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>164</v>
       </c>
@@ -1650,7 +2520,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>165</v>
       </c>
@@ -1658,7 +2528,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>169</v>
       </c>
@@ -1666,7 +2536,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>171</v>
       </c>
@@ -1674,7 +2544,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>173</v>
       </c>
@@ -1682,7 +2552,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>175</v>
       </c>
@@ -1690,7 +2560,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>177</v>
       </c>
@@ -1698,12 +2568,297 @@
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>179</v>
       </c>
       <c r="B34" t="s">
         <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>184</v>
+      </c>
+      <c r="B46" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>188</v>
+      </c>
+      <c r="B47" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>192</v>
+      </c>
+      <c r="B48" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>194</v>
+      </c>
+      <c r="B49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>207</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>209</v>
+      </c>
+      <c r="B52" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>211</v>
+      </c>
+      <c r="B53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>213</v>
+      </c>
+      <c r="B54" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>216</v>
+      </c>
+      <c r="B55" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>250</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>255</v>
+      </c>
+      <c r="B57" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>257</v>
+      </c>
+      <c r="B58" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>308</v>
+      </c>
+      <c r="B59" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>313</v>
+      </c>
+      <c r="B60" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>315</v>
+      </c>
+      <c r="B61" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>317</v>
+      </c>
+      <c r="B62" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A63" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B63" t="s">
+        <v>320</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="40.84375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AF7309-E366-49A3-BD68-78D08628BBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E0E578-550E-4B8A-B00C-AF06096C7BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31620" yWindow="3150" windowWidth="28800" windowHeight="15370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
     <sheet name="Сложные слова" sheetId="3" r:id="rId2"/>
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId3"/>
     <sheet name="составные важные" sheetId="1" r:id="rId4"/>
-    <sheet name="Неизменные" sheetId="6" r:id="rId5"/>
-    <sheet name="создателю ошибки" sheetId="7" r:id="rId6"/>
+    <sheet name="перепсиать" sheetId="8" r:id="rId5"/>
+    <sheet name="Неизменные" sheetId="6" r:id="rId6"/>
+    <sheet name="создателю ошибки" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'составные важные'!$A$1:$B$28</definedName>
@@ -39,15 +40,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="347">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -1016,6 +1014,78 @@
   </si>
   <si>
     <t>тайное сообщество, руководимое</t>
+  </si>
+  <si>
+    <t>обычной черной магии</t>
+  </si>
+  <si>
+    <t>обычном чёрном колдовстве</t>
+  </si>
+  <si>
+    <t>этих же способности</t>
+  </si>
+  <si>
+    <t>весь изъятый потенциал</t>
+  </si>
+  <si>
+    <t>все изъятые возможности</t>
+  </si>
+  <si>
+    <t>«круглая» дата</t>
+  </si>
+  <si>
+    <t>«круглое» число днеисчеслителя</t>
+  </si>
+  <si>
+    <t>был объявлен очередной траур</t>
+  </si>
+  <si>
+    <t>было объявлено очередное горе</t>
+  </si>
+  <si>
+    <t>типичный технократический подход</t>
+  </si>
+  <si>
+    <t>обычный подход использования властью научных разработок и достижений</t>
+  </si>
+  <si>
+    <t>ваша мыслеформа вышла</t>
+  </si>
+  <si>
+    <t>ваш мыслеобраз вышел</t>
+  </si>
+  <si>
+    <t>целому магическому клану</t>
+  </si>
+  <si>
+    <t>целой колдовской семье</t>
+  </si>
+  <si>
+    <t>была создана следующая мыслеформа</t>
+  </si>
+  <si>
+    <t>был создан следующий мыслеобраз</t>
+  </si>
+  <si>
+    <t>дистанционной и при индивидуальной коррекции</t>
+  </si>
+  <si>
+    <t>удалённом и при личном изменении</t>
+  </si>
+  <si>
+    <t>видимая пациентами картина</t>
+  </si>
+  <si>
+    <t>видимое больными изображение</t>
+  </si>
+  <si>
+    <t>картина в разных случаях</t>
+  </si>
+  <si>
+    <t>документ там важный был</t>
+  </si>
+  <si>
+    <t>письменное свидетельство там важное было</t>
   </si>
 </sst>
 </file>
@@ -1353,13 +1423,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.921875" customWidth="1"/>
-    <col min="2" max="2" width="42.53515625" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="2" max="2" width="42.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>268</v>
       </c>
@@ -1367,7 +1437,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>270</v>
       </c>
@@ -1375,7 +1445,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>272</v>
       </c>
@@ -1383,7 +1453,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>282</v>
       </c>
@@ -1391,7 +1461,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>274</v>
       </c>
@@ -1399,7 +1469,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>280</v>
       </c>
@@ -1407,7 +1477,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>276</v>
       </c>
@@ -1415,7 +1485,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>278</v>
       </c>
@@ -1423,7 +1493,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>296</v>
       </c>
@@ -1431,7 +1501,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>298</v>
       </c>
@@ -1439,7 +1509,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>300</v>
       </c>
@@ -1447,7 +1517,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>302</v>
       </c>
@@ -1455,7 +1525,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>304</v>
       </c>
@@ -1463,7 +1533,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>306</v>
       </c>
@@ -1471,7 +1541,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>259</v>
       </c>
@@ -1479,7 +1549,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>284</v>
       </c>
@@ -1487,11 +1557,11 @@
         <v>285</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>286</v>
       </c>
@@ -1499,7 +1569,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>292</v>
       </c>
@@ -1507,7 +1577,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>288</v>
       </c>
@@ -1515,7 +1585,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>290</v>
       </c>
@@ -1523,7 +1593,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>294</v>
       </c>
@@ -1531,7 +1601,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>225</v>
       </c>
@@ -1539,7 +1609,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>223</v>
       </c>
@@ -1547,7 +1617,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>227</v>
       </c>
@@ -1555,7 +1625,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>229</v>
       </c>
@@ -1563,7 +1633,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>231</v>
       </c>
@@ -1571,7 +1641,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>233</v>
       </c>
@@ -1579,7 +1649,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>241</v>
       </c>
@@ -1587,7 +1657,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>239</v>
       </c>
@@ -1595,7 +1665,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>235</v>
       </c>
@@ -1603,7 +1673,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>237</v>
       </c>
@@ -1611,103 +1681,103 @@
         <v>238</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
     </row>
@@ -1722,13 +1792,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
   <dimension ref="A3:B41"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.53515625" customWidth="1"/>
-    <col min="2" max="2" width="27.69140625" customWidth="1"/>
+    <col min="1" max="1" width="47.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1736,7 +1806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1744,7 +1814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1752,7 +1822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1760,7 +1830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1768,7 +1838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1776,7 +1846,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1784,7 +1854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1792,7 +1862,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1800,7 +1870,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1808,7 +1878,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1816,7 +1886,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1824,7 +1894,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1832,7 +1902,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1840,7 +1910,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1848,7 +1918,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1856,7 +1926,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1864,7 +1934,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1872,7 +1942,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -1880,7 +1950,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1888,7 +1958,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1896,7 +1966,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1904,7 +1974,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1912,7 +1982,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1920,7 +1990,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1928,7 +1998,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1936,7 +2006,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -1944,7 +2014,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -1952,7 +2022,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -1960,7 +2030,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>167</v>
       </c>
@@ -1968,7 +2038,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>218</v>
       </c>
@@ -1976,7 +2046,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>221</v>
       </c>
@@ -1984,7 +2054,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>243</v>
       </c>
@@ -1992,7 +2062,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>261</v>
       </c>
@@ -2000,7 +2070,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>310</v>
       </c>
@@ -2016,12 +2086,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.84375" customWidth="1"/>
+    <col min="1" max="1" width="32.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>155</v>
       </c>
@@ -2029,7 +2099,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>161</v>
       </c>
@@ -2044,14 +2114,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.3828125" customWidth="1"/>
-    <col min="2" max="2" width="77.3828125" customWidth="1"/>
+    <col min="1" max="1" width="65.36328125" customWidth="1"/>
+    <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -2059,7 +2129,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -2067,7 +2137,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2075,7 +2145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>88</v>
       </c>
@@ -2083,7 +2153,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -2091,7 +2161,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>90</v>
       </c>
@@ -2099,7 +2169,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -2107,7 +2177,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -2115,7 +2185,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -2123,7 +2193,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -2131,7 +2201,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -2139,7 +2209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>137</v>
       </c>
@@ -2150,7 +2220,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>183</v>
       </c>
@@ -2158,7 +2228,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>106</v>
       </c>
@@ -2166,7 +2236,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2174,7 +2244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -2182,7 +2252,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>102</v>
       </c>
@@ -2190,7 +2260,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -2198,7 +2268,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>186</v>
       </c>
@@ -2206,7 +2276,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>190</v>
       </c>
@@ -2214,7 +2284,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>197</v>
       </c>
@@ -2222,7 +2292,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>199</v>
       </c>
@@ -2230,7 +2300,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>201</v>
       </c>
@@ -2238,7 +2308,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>203</v>
       </c>
@@ -2246,7 +2316,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>246</v>
       </c>
@@ -2254,7 +2324,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>264</v>
       </c>
@@ -2262,7 +2332,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>248</v>
       </c>
@@ -2270,7 +2340,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>265</v>
       </c>
@@ -2278,12 +2348,84 @@
         <v>266</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>321</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>322</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>326</v>
+      </c>
+      <c r="B31" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>330</v>
+      </c>
+      <c r="B33" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>334</v>
+      </c>
+      <c r="B34" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>336</v>
+      </c>
+      <c r="B35" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>340</v>
+      </c>
+      <c r="B36" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>342</v>
+      </c>
+      <c r="B37" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>345</v>
+      </c>
+      <c r="B38" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -2296,516 +2438,13 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B63"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="66.53515625" customWidth="1"/>
-    <col min="2" max="2" width="70.15234375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>129</v>
-      </c>
-      <c r="B17" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A18" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B19" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>164</v>
-      </c>
-      <c r="B27" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B28" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>169</v>
-      </c>
-      <c r="B29" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>171</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>173</v>
-      </c>
-      <c r="B31" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>175</v>
-      </c>
-      <c r="B32" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>177</v>
-      </c>
-      <c r="B33" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>179</v>
-      </c>
-      <c r="B34" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>181</v>
-      </c>
-      <c r="B35" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>153</v>
-      </c>
-      <c r="B36" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>111</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>184</v>
-      </c>
-      <c r="B46" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
-        <v>188</v>
-      </c>
-      <c r="B47" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
-        <v>192</v>
-      </c>
-      <c r="B48" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A49" t="s">
-        <v>194</v>
-      </c>
-      <c r="B49" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
-        <v>205</v>
-      </c>
-      <c r="B50" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
-        <v>207</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>209</v>
-      </c>
-      <c r="B52" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
-        <v>211</v>
-      </c>
-      <c r="B53" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>213</v>
-      </c>
-      <c r="B54" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A55" t="s">
-        <v>216</v>
-      </c>
-      <c r="B55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A56" t="s">
-        <v>250</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A57" t="s">
-        <v>255</v>
-      </c>
-      <c r="B57" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A58" t="s">
-        <v>257</v>
-      </c>
-      <c r="B58" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
-        <v>308</v>
-      </c>
-      <c r="B59" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
-        <v>313</v>
-      </c>
-      <c r="B60" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>315</v>
-      </c>
-      <c r="B61" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A62" t="s">
-        <v>317</v>
-      </c>
-      <c r="B62" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A63" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B63" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -2814,51 +2453,598 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
+  <dimension ref="A1:B66"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.84375" customWidth="1"/>
+    <col min="1" max="1" width="66.54296875" customWidth="1"/>
+    <col min="2" max="2" width="70.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>159</v>
+      </c>
+      <c r="B26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>173</v>
+      </c>
+      <c r="B31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>184</v>
+      </c>
+      <c r="B46" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>188</v>
+      </c>
+      <c r="B47" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>192</v>
+      </c>
+      <c r="B48" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>194</v>
+      </c>
+      <c r="B49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>207</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>209</v>
+      </c>
+      <c r="B52" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>211</v>
+      </c>
+      <c r="B53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>213</v>
+      </c>
+      <c r="B54" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>216</v>
+      </c>
+      <c r="B55" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>250</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>255</v>
+      </c>
+      <c r="B57" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>257</v>
+      </c>
+      <c r="B58" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>308</v>
+      </c>
+      <c r="B59" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>313</v>
+      </c>
+      <c r="B60" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>315</v>
+      </c>
+      <c r="B61" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>317</v>
+      </c>
+      <c r="B62" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B63" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>328</v>
+      </c>
+      <c r="B64" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>332</v>
+      </c>
+      <c r="B65" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>338</v>
+      </c>
+      <c r="B66" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E0E578-550E-4B8A-B00C-AF06096C7BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186BF400-CC0C-4174-A7B9-43A8F705741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31620" yWindow="3150" windowWidth="28800" windowHeight="15370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -40,12 +40,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="370">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -1086,6 +1089,75 @@
   </si>
   <si>
     <t>письменное свидетельство там важное было</t>
+  </si>
+  <si>
+    <t xml:space="preserve">эниокоррекции </t>
+  </si>
+  <si>
+    <t>эниокоррекций</t>
+  </si>
+  <si>
+    <t>вездесущих изменений</t>
+  </si>
+  <si>
+    <t>эниокоррекцией</t>
+  </si>
+  <si>
+    <t>вездесущим изменением</t>
+  </si>
+  <si>
+    <t>эниокоррекция</t>
+  </si>
+  <si>
+    <t>вездесущее изменение</t>
+  </si>
+  <si>
+    <t>эниокоррекциям</t>
+  </si>
+  <si>
+    <t>вездесущим изменениям</t>
+  </si>
+  <si>
+    <t>эниокоррекциями</t>
+  </si>
+  <si>
+    <t>вездесущими изменениями</t>
+  </si>
+  <si>
+    <t>эниокоррекциях</t>
+  </si>
+  <si>
+    <t>вездесущих изменениях</t>
+  </si>
+  <si>
+    <t>эниокоррекцию</t>
+  </si>
+  <si>
+    <t>эниологической теории</t>
+  </si>
+  <si>
+    <t>вездесущего учения</t>
+  </si>
+  <si>
+    <t>к практике</t>
+  </si>
+  <si>
+    <t>к применению</t>
+  </si>
+  <si>
+    <t>тонкие ручки и ножи.</t>
+  </si>
+  <si>
+    <t>Такой принцип работы просто вынуждал</t>
+  </si>
+  <si>
+    <t>Такой правило работы просто вынуждало</t>
+  </si>
+  <si>
+    <t>эзотериков прошлого и настоящего позволил сделать следующий вывод</t>
+  </si>
+  <si>
+    <t>тайноведов прошлого и настоящего позволило сделать следующий вывод</t>
   </si>
 </sst>
 </file>
@@ -1423,13 +1495,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="31.90625" customWidth="1"/>
-    <col min="2" max="2" width="42.54296875" customWidth="1"/>
+    <col min="1" max="1" width="31.921875" customWidth="1"/>
+    <col min="2" max="2" width="42.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>268</v>
       </c>
@@ -1437,7 +1509,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>270</v>
       </c>
@@ -1445,7 +1517,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>272</v>
       </c>
@@ -1453,7 +1525,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>282</v>
       </c>
@@ -1461,7 +1533,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>274</v>
       </c>
@@ -1469,7 +1541,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>280</v>
       </c>
@@ -1477,7 +1549,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>276</v>
       </c>
@@ -1485,7 +1557,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>278</v>
       </c>
@@ -1493,7 +1565,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>296</v>
       </c>
@@ -1501,7 +1573,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>298</v>
       </c>
@@ -1509,7 +1581,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>300</v>
       </c>
@@ -1517,7 +1589,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>302</v>
       </c>
@@ -1525,7 +1597,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>304</v>
       </c>
@@ -1533,7 +1605,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>306</v>
       </c>
@@ -1541,7 +1613,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>259</v>
       </c>
@@ -1549,7 +1621,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>284</v>
       </c>
@@ -1557,11 +1629,11 @@
         <v>285</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>286</v>
       </c>
@@ -1569,7 +1641,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>292</v>
       </c>
@@ -1577,7 +1649,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>288</v>
       </c>
@@ -1585,7 +1657,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>290</v>
       </c>
@@ -1593,7 +1665,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>294</v>
       </c>
@@ -1601,7 +1673,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>225</v>
       </c>
@@ -1609,7 +1681,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>223</v>
       </c>
@@ -1617,7 +1689,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>227</v>
       </c>
@@ -1625,7 +1697,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>229</v>
       </c>
@@ -1633,7 +1705,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>231</v>
       </c>
@@ -1641,7 +1713,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>233</v>
       </c>
@@ -1649,7 +1721,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>241</v>
       </c>
@@ -1657,7 +1729,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>239</v>
       </c>
@@ -1665,7 +1737,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>235</v>
       </c>
@@ -1673,7 +1745,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>237</v>
       </c>
@@ -1681,103 +1753,135 @@
         <v>238</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>347</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>348</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>350</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>352</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>354</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>356</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>358</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>360</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
     </row>
@@ -1792,13 +1896,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
   <dimension ref="A3:B41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="47.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" customWidth="1"/>
+    <col min="1" max="1" width="47.53515625" customWidth="1"/>
+    <col min="2" max="2" width="27.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1806,7 +1910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1814,7 +1918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1822,7 +1926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1830,7 +1934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1838,7 +1942,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1846,7 +1950,23 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>361</v>
+      </c>
+      <c r="B9" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>363</v>
+      </c>
+      <c r="B10" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1854,7 +1974,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1862,7 +1982,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1870,7 +1990,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1878,7 +1998,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1886,7 +2006,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1894,7 +2014,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1902,7 +2022,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1910,7 +2030,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1918,7 +2038,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1926,7 +2046,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1934,7 +2054,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1942,7 +2062,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -1950,7 +2070,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1958,7 +2078,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1966,7 +2086,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1974,7 +2094,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1982,7 +2102,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1990,7 +2110,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1998,7 +2118,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2006,7 +2126,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -2014,7 +2134,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -2022,7 +2142,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -2030,7 +2150,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>167</v>
       </c>
@@ -2038,7 +2158,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>218</v>
       </c>
@@ -2046,7 +2166,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>221</v>
       </c>
@@ -2054,7 +2174,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>243</v>
       </c>
@@ -2062,7 +2182,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>261</v>
       </c>
@@ -2070,7 +2190,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>310</v>
       </c>
@@ -2086,12 +2206,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32.81640625" customWidth="1"/>
+    <col min="1" max="1" width="32.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>155</v>
       </c>
@@ -2099,7 +2219,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>161</v>
       </c>
@@ -2115,13 +2235,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="65.36328125" customWidth="1"/>
-    <col min="2" max="2" width="77.36328125" customWidth="1"/>
+    <col min="1" max="1" width="65.3828125" customWidth="1"/>
+    <col min="2" max="2" width="77.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -2129,7 +2249,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -2137,7 +2257,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2145,15 +2265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -2161,7 +2273,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>90</v>
       </c>
@@ -2169,7 +2281,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -2177,7 +2289,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -2185,7 +2297,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -2193,7 +2305,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -2201,7 +2313,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -2209,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>137</v>
       </c>
@@ -2220,7 +2332,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>183</v>
       </c>
@@ -2228,7 +2340,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>106</v>
       </c>
@@ -2236,7 +2348,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2244,7 +2356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -2252,7 +2364,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>102</v>
       </c>
@@ -2260,7 +2372,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -2268,7 +2380,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>186</v>
       </c>
@@ -2276,7 +2388,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>190</v>
       </c>
@@ -2284,7 +2396,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>197</v>
       </c>
@@ -2292,7 +2404,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>199</v>
       </c>
@@ -2300,7 +2412,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>201</v>
       </c>
@@ -2308,7 +2420,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>203</v>
       </c>
@@ -2316,7 +2428,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>246</v>
       </c>
@@ -2324,7 +2436,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>264</v>
       </c>
@@ -2332,7 +2444,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>248</v>
       </c>
@@ -2340,7 +2452,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>265</v>
       </c>
@@ -2348,7 +2460,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>321</v>
       </c>
@@ -2356,7 +2468,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>323</v>
       </c>
@@ -2364,7 +2476,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>326</v>
       </c>
@@ -2372,7 +2484,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -2380,15 +2492,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>330</v>
-      </c>
-      <c r="B33" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>334</v>
       </c>
@@ -2396,7 +2500,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>336</v>
       </c>
@@ -2404,7 +2508,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>340</v>
       </c>
@@ -2412,7 +2516,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>342</v>
       </c>
@@ -2420,7 +2524,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>345</v>
       </c>
@@ -2440,9 +2544,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>344</v>
       </c>
@@ -2454,14 +2558,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B66"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B69"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="66.54296875" customWidth="1"/>
-    <col min="2" max="2" width="70.1796875" customWidth="1"/>
+    <col min="1" max="1" width="66.53515625" customWidth="1"/>
+    <col min="2" max="2" width="70.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -2469,7 +2573,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2477,7 +2581,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -2485,7 +2589,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -2493,7 +2597,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -2501,7 +2605,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -2509,7 +2613,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -2517,7 +2621,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -2525,7 +2629,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -2533,7 +2637,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -2541,7 +2645,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -2549,7 +2653,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -2557,7 +2661,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -2565,7 +2669,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -2573,7 +2677,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -2581,7 +2685,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>127</v>
       </c>
@@ -2589,7 +2693,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -2597,7 +2701,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
@@ -2605,7 +2709,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>133</v>
       </c>
@@ -2613,7 +2717,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -2621,7 +2725,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -2629,7 +2733,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -2637,7 +2741,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>145</v>
       </c>
@@ -2645,7 +2749,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>148</v>
       </c>
@@ -2653,7 +2757,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>157</v>
       </c>
@@ -2661,7 +2765,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>159</v>
       </c>
@@ -2669,7 +2773,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>164</v>
       </c>
@@ -2677,7 +2781,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>165</v>
       </c>
@@ -2685,7 +2789,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>169</v>
       </c>
@@ -2693,7 +2797,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>171</v>
       </c>
@@ -2701,7 +2805,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>173</v>
       </c>
@@ -2709,7 +2813,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>175</v>
       </c>
@@ -2717,7 +2821,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>177</v>
       </c>
@@ -2725,7 +2829,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>179</v>
       </c>
@@ -2733,7 +2837,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>181</v>
       </c>
@@ -2741,7 +2845,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>153</v>
       </c>
@@ -2749,7 +2853,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>117</v>
       </c>
@@ -2757,7 +2861,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -2765,7 +2869,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>113</v>
       </c>
@@ -2773,7 +2877,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -2781,7 +2885,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -2789,7 +2893,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -2797,7 +2901,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -2805,7 +2909,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -2813,7 +2917,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -2821,7 +2925,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>184</v>
       </c>
@@ -2829,7 +2933,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>188</v>
       </c>
@@ -2837,7 +2941,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>192</v>
       </c>
@@ -2845,7 +2949,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>194</v>
       </c>
@@ -2853,7 +2957,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>205</v>
       </c>
@@ -2861,7 +2965,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>207</v>
       </c>
@@ -2869,7 +2973,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>209</v>
       </c>
@@ -2877,7 +2981,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>211</v>
       </c>
@@ -2885,7 +2989,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>213</v>
       </c>
@@ -2893,7 +2997,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>216</v>
       </c>
@@ -2901,7 +3005,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>250</v>
       </c>
@@ -2909,7 +3013,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>255</v>
       </c>
@@ -2917,7 +3021,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>257</v>
       </c>
@@ -2925,7 +3029,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>308</v>
       </c>
@@ -2933,7 +3037,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>313</v>
       </c>
@@ -2941,7 +3045,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>315</v>
       </c>
@@ -2949,7 +3053,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>317</v>
       </c>
@@ -2957,7 +3061,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" s="2" t="s">
         <v>319</v>
       </c>
@@ -2965,7 +3069,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>328</v>
       </c>
@@ -2973,7 +3077,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>332</v>
       </c>
@@ -2981,12 +3085,36 @@
         <v>333</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>338</v>
       </c>
       <c r="B66" t="s">
         <v>339</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>330</v>
+      </c>
+      <c r="B67" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>366</v>
+      </c>
+      <c r="B68" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>368</v>
+      </c>
+      <c r="B69" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -2996,55 +3124,60 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="40.81640625" customWidth="1"/>
+    <col min="1" max="1" width="40.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186BF400-CC0C-4174-A7B9-43A8F705741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56639659-37A4-470B-9220-11B8DB33E27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32540" yWindow="1600" windowWidth="28800" windowHeight="15410" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -40,15 +40,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="379">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -638,9 +635,6 @@
     <t>саморазвивающаяся порабощающая разумная живая особь</t>
   </si>
   <si>
-    <t>имярек</t>
-  </si>
-  <si>
     <t>вербальная магия представлена</t>
   </si>
   <si>
@@ -785,9 +779,6 @@
     <t>колдовским</t>
   </si>
   <si>
-    <t>свои пространство и время.</t>
-  </si>
-  <si>
     <t>кто заинтересован в этом полтергейсте</t>
   </si>
   <si>
@@ -1158,6 +1149,39 @@
   </si>
   <si>
     <t>тайноведов прошлого и настоящего позволило сделать следующий вывод</t>
+  </si>
+  <si>
+    <t>своё пространство и время</t>
+  </si>
+  <si>
+    <t>свои пространство и время</t>
+  </si>
+  <si>
+    <t>бабушка сказала</t>
+  </si>
+  <si>
+    <t>к обеим сущностям</t>
+  </si>
+  <si>
+    <t>но с той</t>
+  </si>
+  <si>
+    <t>на жителях европейских стран.</t>
+  </si>
+  <si>
+    <t>не хватает многих компонентов</t>
+  </si>
+  <si>
+    <t>этих же способностей</t>
+  </si>
+  <si>
+    <t>тонкие ручки и ножки</t>
+  </si>
+  <si>
+    <t>менингитоподобным вирусом</t>
+  </si>
+  <si>
+    <t>минингитоподобной заразой</t>
   </si>
 </sst>
 </file>
@@ -1495,393 +1519,393 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.921875" customWidth="1"/>
-    <col min="2" max="2" width="42.53515625" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="2" max="2" width="42.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>268</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>270</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>272</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B15" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>282</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B16" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>276</v>
-      </c>
-      <c r="B7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>278</v>
-      </c>
-      <c r="B8" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>259</v>
-      </c>
-      <c r="B15" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>284</v>
-      </c>
-      <c r="B16" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>284</v>
+      </c>
+      <c r="B18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>290</v>
+      </c>
+      <c r="B19" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>286</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B20" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>288</v>
+      </c>
+      <c r="B21" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>292</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B22" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>288</v>
-      </c>
-      <c r="B20" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>290</v>
-      </c>
-      <c r="B21" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>294</v>
-      </c>
-      <c r="B22" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>224</v>
+      </c>
+      <c r="B23" t="s">
         <v>225</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>223</v>
-      </c>
-      <c r="B24" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>227</v>
       </c>
-      <c r="B25" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>229</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>231</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>233</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>238</v>
+      </c>
+      <c r="B30" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>241</v>
-      </c>
-      <c r="B29" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>239</v>
-      </c>
-      <c r="B30" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>235</v>
       </c>
-      <c r="B31" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>237</v>
       </c>
-      <c r="B32" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>345</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>346</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>348</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>350</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>352</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>354</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>356</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>358</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>360</v>
-      </c>
       <c r="B40" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
     </row>
@@ -1896,13 +1920,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
   <dimension ref="A3:B41"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.53515625" customWidth="1"/>
-    <col min="2" max="2" width="27.69140625" customWidth="1"/>
+    <col min="1" max="1" width="47.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1910,7 +1934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1918,7 +1942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1926,7 +1950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1934,7 +1958,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1942,7 +1966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1950,23 +1974,23 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>361</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>363</v>
-      </c>
-      <c r="B10" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1974,7 +1998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1982,7 +2006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1990,7 +2014,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1998,7 +2022,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2006,7 +2030,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2014,7 +2038,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2022,7 +2046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -2030,7 +2054,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -2038,7 +2062,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -2046,7 +2070,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -2054,7 +2078,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -2062,7 +2086,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -2070,7 +2094,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2078,7 +2102,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2086,7 +2110,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -2094,7 +2118,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -2102,7 +2126,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -2110,7 +2134,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2118,7 +2142,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2126,7 +2150,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -2134,7 +2158,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -2142,7 +2166,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -2150,7 +2174,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>167</v>
       </c>
@@ -2158,44 +2182,44 @@
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" t="s">
         <v>218</v>
       </c>
-      <c r="B37" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" t="s">
         <v>221</v>
       </c>
-      <c r="B38" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" t="s">
         <v>243</v>
       </c>
-      <c r="B39" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B40" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -2205,13 +2229,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.84375" customWidth="1"/>
+    <col min="1" max="1" width="32.81640625" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>155</v>
       </c>
@@ -2219,12 +2244,20 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>161</v>
       </c>
       <c r="B2" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B3" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -2235,13 +2268,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.3828125" customWidth="1"/>
-    <col min="2" max="2" width="77.3828125" customWidth="1"/>
+    <col min="1" max="1" width="65.36328125" customWidth="1"/>
+    <col min="2" max="2" width="77.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -2249,7 +2282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -2257,7 +2290,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2265,7 +2298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -2273,7 +2306,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>90</v>
       </c>
@@ -2281,7 +2314,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -2289,7 +2322,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -2297,7 +2330,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -2305,7 +2338,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -2313,7 +2346,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -2321,7 +2354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>137</v>
       </c>
@@ -2332,15 +2365,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>183</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>106</v>
       </c>
@@ -2348,7 +2381,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2356,7 +2389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -2364,7 +2397,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>102</v>
       </c>
@@ -2372,7 +2405,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -2380,7 +2413,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>186</v>
       </c>
@@ -2388,7 +2421,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>190</v>
       </c>
@@ -2396,95 +2429,95 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" t="s">
         <v>197</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>199</v>
       </c>
-      <c r="B22" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>201</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>203</v>
       </c>
-      <c r="B24" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>244</v>
+      </c>
+      <c r="B25" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B26" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>246</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B27" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>263</v>
+      </c>
+      <c r="B28" t="s">
         <v>264</v>
       </c>
-      <c r="B26" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>248</v>
-      </c>
-      <c r="B27" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>265</v>
-      </c>
-      <c r="B28" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>319</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>321</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B30" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>323</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>326</v>
-      </c>
       <c r="B31" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -2492,44 +2525,44 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>332</v>
+      </c>
+      <c r="B34" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>334</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>336</v>
-      </c>
-      <c r="B35" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>338</v>
+      </c>
+      <c r="B36" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>340</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>342</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>345</v>
-      </c>
       <c r="B38" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -2544,11 +2577,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -2559,13 +2592,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
   <dimension ref="A1:B69"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="66.53515625" customWidth="1"/>
-    <col min="2" max="2" width="70.15234375" customWidth="1"/>
+    <col min="1" max="1" width="66.54296875" customWidth="1"/>
+    <col min="2" max="2" width="70.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -2573,7 +2606,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2581,7 +2614,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -2589,7 +2622,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -2597,7 +2630,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -2605,7 +2638,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -2613,7 +2646,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -2621,7 +2654,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -2629,7 +2662,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -2637,7 +2670,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -2645,7 +2678,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -2653,7 +2686,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -2661,7 +2694,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -2669,7 +2702,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -2677,7 +2710,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -2685,7 +2718,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>127</v>
       </c>
@@ -2693,7 +2726,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -2701,7 +2734,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
@@ -2709,7 +2742,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>133</v>
       </c>
@@ -2717,7 +2750,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -2725,7 +2758,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -2733,7 +2766,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -2741,7 +2774,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>145</v>
       </c>
@@ -2749,7 +2782,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>148</v>
       </c>
@@ -2757,7 +2790,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>157</v>
       </c>
@@ -2765,7 +2798,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>159</v>
       </c>
@@ -2773,7 +2806,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>164</v>
       </c>
@@ -2781,7 +2814,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>165</v>
       </c>
@@ -2789,7 +2822,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>169</v>
       </c>
@@ -2797,7 +2830,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>171</v>
       </c>
@@ -2805,7 +2838,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>173</v>
       </c>
@@ -2813,7 +2846,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>175</v>
       </c>
@@ -2821,7 +2854,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>177</v>
       </c>
@@ -2829,7 +2862,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>179</v>
       </c>
@@ -2837,7 +2870,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>181</v>
       </c>
@@ -2845,7 +2878,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>153</v>
       </c>
@@ -2853,7 +2886,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>117</v>
       </c>
@@ -2861,7 +2894,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -2869,7 +2902,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>113</v>
       </c>
@@ -2877,7 +2910,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -2885,7 +2918,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -2893,7 +2926,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -2901,7 +2934,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -2909,7 +2942,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -2917,7 +2950,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -2925,7 +2958,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>184</v>
       </c>
@@ -2933,7 +2966,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>188</v>
       </c>
@@ -2941,7 +2974,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>192</v>
       </c>
@@ -2949,7 +2982,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>194</v>
       </c>
@@ -2957,164 +2990,164 @@
         <v>195</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>204</v>
+      </c>
+      <c r="B50" t="s">
         <v>205</v>
       </c>
-      <c r="B50" t="s">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
+      <c r="B51" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B51" s="2" t="s">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>209</v>
       </c>
-      <c r="B52" t="s">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>211</v>
       </c>
-      <c r="B53" t="s">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>213</v>
       </c>
-      <c r="B54" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" t="s">
         <v>216</v>
       </c>
-      <c r="B55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>253</v>
+      </c>
+      <c r="B57" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>255</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B58" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A58" t="s">
-        <v>257</v>
-      </c>
-      <c r="B58" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B59" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>311</v>
+      </c>
+      <c r="B60" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>313</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B61" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>315</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A62" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B63" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A63" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B63" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>326</v>
+      </c>
+      <c r="B64" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>330</v>
+      </c>
+      <c r="B65" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>336</v>
+      </c>
+      <c r="B66" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>328</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B67" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A65" t="s">
-        <v>332</v>
-      </c>
-      <c r="B65" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A66" t="s">
-        <v>338</v>
-      </c>
-      <c r="B66" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A67" t="s">
-        <v>330</v>
-      </c>
-      <c r="B67" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>364</v>
+      </c>
+      <c r="B68" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>366</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
         <v>367</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
-        <v>368</v>
-      </c>
-      <c r="B69" t="s">
-        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -3124,60 +3157,83 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A2:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.84375" customWidth="1"/>
+    <col min="1" max="1" width="40.81640625" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+        <v>219</v>
+      </c>
+      <c r="B2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+        <v>369</v>
+      </c>
+      <c r="B3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+        <v>265</v>
+      </c>
+      <c r="B7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+        <v>310</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+        <v>323</v>
+      </c>
+      <c r="B9" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>365</v>
+        <v>363</v>
+      </c>
+      <c r="B10" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56639659-37A4-470B-9220-11B8DB33E27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CA442F-1ED4-4598-B1C5-F9C91DE849D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32540" yWindow="1600" windowWidth="28800" windowHeight="15410" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1760" yWindow="2450" windowWidth="28800" windowHeight="15410" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="406">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -1182,6 +1182,87 @@
   </si>
   <si>
     <t>минингитоподобной заразой</t>
+  </si>
+  <si>
+    <t>первостепенность информации, воспринимаемой</t>
+  </si>
+  <si>
+    <t>первостепенность сведений, воспринимаемых</t>
+  </si>
+  <si>
+    <t>«считывание» информации</t>
+  </si>
+  <si>
+    <t>«считывание» сведения</t>
+  </si>
+  <si>
+    <t>Какой бы прекрасной ни была математическая модель</t>
+  </si>
+  <si>
+    <t>Каким бы прекрасным ни был расчётный прообраз</t>
+  </si>
+  <si>
+    <t>попадают в русло.</t>
+  </si>
+  <si>
+    <t>мой энергоинформационный банк</t>
+  </si>
+  <si>
+    <t>моё вездесущное хранилище</t>
+  </si>
+  <si>
+    <t>донорского организма человека</t>
+  </si>
+  <si>
+    <t>жертвенного человеческого тела</t>
+  </si>
+  <si>
+    <t>Интересная информация при этом была выявлена</t>
+  </si>
+  <si>
+    <t>Увлекательные сведения при этом были выявлены</t>
+  </si>
+  <si>
+    <t>“прорвалась” информация</t>
+  </si>
+  <si>
+    <t>“прорвались” сведения</t>
+  </si>
+  <si>
+    <t>энергоинформационной структуре</t>
+  </si>
+  <si>
+    <t>вездесущном устройстве</t>
+  </si>
+  <si>
+    <t>анализ жидкости выявил</t>
+  </si>
+  <si>
+    <t>оценка жидкости выявила</t>
+  </si>
+  <si>
+    <t>энергоинформационной структуре человека</t>
+  </si>
+  <si>
+    <t>вездесущном устройстве человека</t>
+  </si>
+  <si>
+    <t>нужна и непосредственная инициация</t>
+  </si>
+  <si>
+    <t>нужнен и непосредственный обряд</t>
+  </si>
+  <si>
+    <t>наша планета была превращена в некую донорскую плантацию</t>
+  </si>
+  <si>
+    <t>наше небесное тело было превращено в некое жертвенное посевное поле</t>
+  </si>
+  <si>
+    <t>конкретной эниологической практики</t>
+  </si>
+  <si>
+    <t>определённого вездесущего  опыта применения</t>
   </si>
 </sst>
 </file>
@@ -2150,6 +2231,14 @@
         <v>71</v>
       </c>
     </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>394</v>
+      </c>
+      <c r="B31" t="s">
+        <v>395</v>
+      </c>
+    </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>92</v>
@@ -2229,7 +2318,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.81640625" customWidth="1"/>
@@ -2260,6 +2349,14 @@
         <v>378</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B4" t="s">
+        <v>405</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2267,7 +2364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.36328125" customWidth="1"/>
@@ -2298,6 +2395,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B4" t="s">
+        <v>387</v>
+      </c>
+    </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>135</v>
@@ -2525,6 +2630,14 @@
         <v>89</v>
       </c>
     </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>379</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>332</v>
@@ -2563,6 +2676,38 @@
       </c>
       <c r="B38" t="s">
         <v>344</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>388</v>
+      </c>
+      <c r="B39" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>396</v>
+      </c>
+      <c r="B40" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>398</v>
+      </c>
+      <c r="B41" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>400</v>
+      </c>
+      <c r="B42" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -2591,7 +2736,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="66.54296875" customWidth="1"/>
@@ -3148,6 +3293,54 @@
       </c>
       <c r="B69" t="s">
         <v>367</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>381</v>
+      </c>
+      <c r="B70" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>383</v>
+      </c>
+      <c r="B71" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>385</v>
+      </c>
+      <c r="B72" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>390</v>
+      </c>
+      <c r="B73" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>392</v>
+      </c>
+      <c r="B74" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>402</v>
+      </c>
+      <c r="B75" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CA442F-1ED4-4598-B1C5-F9C91DE849D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2CE73D-1CF2-4BBF-8E69-5895E9D4D5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="2450" windowWidth="28800" windowHeight="15410" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
     <sheet name="Сложные слова" sheetId="3" r:id="rId2"/>
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId3"/>
     <sheet name="составные важные" sheetId="1" r:id="rId4"/>
-    <sheet name="перепсиать" sheetId="8" r:id="rId5"/>
-    <sheet name="Неизменные" sheetId="6" r:id="rId6"/>
+    <sheet name="Неизменные" sheetId="6" r:id="rId5"/>
+    <sheet name="перепсиать" sheetId="8" r:id="rId6"/>
     <sheet name="создателю ошибки" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
@@ -40,12 +40,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="416">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -1263,6 +1266,36 @@
   </si>
   <si>
     <t>определённого вездесущего  опыта применения</t>
+  </si>
+  <si>
+    <t>-го магического аркана</t>
+  </si>
+  <si>
+    <t>-ой колдовской тайны</t>
+  </si>
+  <si>
+    <t>-й магический аркан</t>
+  </si>
+  <si>
+    <t>-е тайное колдовство</t>
+  </si>
+  <si>
+    <t>военный 5-й магический аркан</t>
+  </si>
+  <si>
+    <t>военное 5-е тайное колдовство</t>
+  </si>
+  <si>
+    <t>пятого магического аркана</t>
+  </si>
+  <si>
+    <t>пятой колдовской тайны</t>
+  </si>
+  <si>
+    <t>так называемый «мидпойнт», или средняя точка</t>
+  </si>
+  <si>
+    <t>так называемая «средняя точка»</t>
   </si>
 </sst>
 </file>
@@ -1312,13 +1345,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1600,13 +1635,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="31.90625" customWidth="1"/>
-    <col min="2" max="2" width="42.54296875" customWidth="1"/>
+    <col min="1" max="1" width="31.921875" customWidth="1"/>
+    <col min="2" max="2" width="42.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>266</v>
       </c>
@@ -1614,7 +1649,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>268</v>
       </c>
@@ -1622,7 +1657,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>270</v>
       </c>
@@ -1630,7 +1665,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>280</v>
       </c>
@@ -1638,7 +1673,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>272</v>
       </c>
@@ -1646,7 +1681,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>278</v>
       </c>
@@ -1654,7 +1689,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>274</v>
       </c>
@@ -1662,7 +1697,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>276</v>
       </c>
@@ -1670,55 +1705,55 @@
         <v>277</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>257</v>
       </c>
@@ -1726,7 +1761,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>282</v>
       </c>
@@ -1734,11 +1769,11 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>284</v>
       </c>
@@ -1746,7 +1781,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>290</v>
       </c>
@@ -1754,7 +1789,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>286</v>
       </c>
@@ -1762,7 +1797,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>288</v>
       </c>
@@ -1770,7 +1805,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>292</v>
       </c>
@@ -1778,7 +1813,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>224</v>
       </c>
@@ -1786,7 +1821,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>222</v>
       </c>
@@ -1794,7 +1829,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>226</v>
       </c>
@@ -1802,7 +1837,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>228</v>
       </c>
@@ -1810,7 +1845,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>230</v>
       </c>
@@ -1818,7 +1853,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>232</v>
       </c>
@@ -1826,7 +1861,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>240</v>
       </c>
@@ -1834,7 +1869,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>238</v>
       </c>
@@ -1842,7 +1877,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>234</v>
       </c>
@@ -1850,7 +1885,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>236</v>
       </c>
@@ -1858,137 +1893,137 @@
         <v>237</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>345</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>346</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>348</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>350</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>352</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>354</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>356</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>358</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B57">
@@ -2001,13 +2036,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
   <dimension ref="A3:B41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="47.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" customWidth="1"/>
+    <col min="1" max="1" width="47.53515625" customWidth="1"/>
+    <col min="2" max="2" width="27.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2015,7 +2050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2023,7 +2058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2031,7 +2066,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2039,7 +2074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2047,7 +2082,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2055,7 +2090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>359</v>
       </c>
@@ -2063,7 +2098,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>361</v>
       </c>
@@ -2071,7 +2106,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2079,7 +2114,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2087,7 +2122,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2095,7 +2130,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2103,7 +2138,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2111,7 +2146,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2119,7 +2154,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2127,7 +2162,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -2135,7 +2170,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -2143,7 +2178,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -2151,7 +2186,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -2159,7 +2194,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -2167,7 +2202,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -2175,7 +2210,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2183,7 +2218,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2191,7 +2226,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -2199,7 +2234,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -2207,7 +2242,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -2215,7 +2250,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2223,7 +2258,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2231,7 +2266,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>394</v>
       </c>
@@ -2239,7 +2274,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -2247,7 +2282,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -2255,7 +2290,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -2263,15 +2298,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>167</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>217</v>
       </c>
@@ -2279,7 +2314,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>220</v>
       </c>
@@ -2287,7 +2322,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>242</v>
       </c>
@@ -2295,7 +2330,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>259</v>
       </c>
@@ -2303,11 +2338,11 @@
         <v>260</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>308</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>309</v>
       </c>
     </row>
@@ -2319,13 +2354,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32.81640625" customWidth="1"/>
-    <col min="2" max="2" width="28.6328125" customWidth="1"/>
+    <col min="1" max="1" width="32.84375" customWidth="1"/>
+    <col min="2" max="2" width="28.61328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>155</v>
       </c>
@@ -2333,7 +2368,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>161</v>
       </c>
@@ -2341,7 +2376,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>377</v>
       </c>
@@ -2349,7 +2384,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>404</v>
       </c>
@@ -2364,350 +2399,366 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C44"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="65.36328125" customWidth="1"/>
-    <col min="2" max="2" width="77.36328125" customWidth="1"/>
+    <col min="1" max="1" width="65.3828125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="77.3828125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="4" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>401</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -2720,13 +2771,636 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
+  <dimension ref="A1:B78"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="66.53515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="70.15234375" style="2" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>342</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A48" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A49" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A50" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A51" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A52" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A53" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A54" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A55" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A56" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A57" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A58" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A59" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A60" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A61" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A62" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A64" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A65" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A66" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A67" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A68" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A69" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A70" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A71" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A72" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A73" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A74" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A75" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A76" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A77" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A78" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -2735,612 +3409,13 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B75"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="66.54296875" customWidth="1"/>
-    <col min="2" max="2" width="70.1796875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>129</v>
-      </c>
-      <c r="B17" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B19" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>164</v>
-      </c>
-      <c r="B27" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B28" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>169</v>
-      </c>
-      <c r="B29" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>171</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>173</v>
-      </c>
-      <c r="B31" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>175</v>
-      </c>
-      <c r="B32" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>177</v>
-      </c>
-      <c r="B33" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>179</v>
-      </c>
-      <c r="B34" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>181</v>
-      </c>
-      <c r="B35" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>153</v>
-      </c>
-      <c r="B36" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>111</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>184</v>
-      </c>
-      <c r="B46" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>188</v>
-      </c>
-      <c r="B47" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>192</v>
-      </c>
-      <c r="B48" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>194</v>
-      </c>
-      <c r="B49" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>204</v>
-      </c>
-      <c r="B50" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>206</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>208</v>
-      </c>
-      <c r="B52" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>210</v>
-      </c>
-      <c r="B53" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>212</v>
-      </c>
-      <c r="B54" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>215</v>
-      </c>
-      <c r="B55" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>248</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>253</v>
-      </c>
-      <c r="B57" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>255</v>
-      </c>
-      <c r="B58" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>306</v>
-      </c>
-      <c r="B59" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>311</v>
-      </c>
-      <c r="B60" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>313</v>
-      </c>
-      <c r="B61" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>315</v>
-      </c>
-      <c r="B62" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B63" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>326</v>
-      </c>
-      <c r="B64" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>330</v>
-      </c>
-      <c r="B65" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>336</v>
-      </c>
-      <c r="B66" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>328</v>
-      </c>
-      <c r="B67" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>364</v>
-      </c>
-      <c r="B68" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>366</v>
-      </c>
-      <c r="B69" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>381</v>
-      </c>
-      <c r="B70" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>383</v>
-      </c>
-      <c r="B71" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>385</v>
-      </c>
-      <c r="B72" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>390</v>
-      </c>
-      <c r="B73" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>392</v>
-      </c>
-      <c r="B74" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>402</v>
-      </c>
-      <c r="B75" t="s">
-        <v>403</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -3351,13 +3426,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
   <dimension ref="A2:B10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="40.81640625" customWidth="1"/>
+    <col min="1" max="1" width="40.84375" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>219</v>
       </c>
@@ -3365,7 +3440,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>369</v>
       </c>
@@ -3373,7 +3448,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>250</v>
       </c>
@@ -3381,7 +3456,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>251</v>
       </c>
@@ -3389,7 +3464,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>252</v>
       </c>
@@ -3397,7 +3472,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>265</v>
       </c>
@@ -3405,7 +3480,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>310</v>
       </c>
@@ -3413,7 +3488,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>323</v>
       </c>
@@ -3421,7 +3496,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>363</v>
       </c>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2CE73D-1CF2-4BBF-8E69-5895E9D4D5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36B01B2-01E8-44B9-BF6E-2F73495A925E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="746" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
     <sheet name="Сложные слова" sheetId="3" r:id="rId2"/>
-    <sheet name="Вездесущие слова" sheetId="4" r:id="rId3"/>
-    <sheet name="составные важные" sheetId="1" r:id="rId4"/>
-    <sheet name="Неизменные" sheetId="6" r:id="rId5"/>
-    <sheet name="перепсиать" sheetId="8" r:id="rId6"/>
-    <sheet name="создателю ошибки" sheetId="7" r:id="rId7"/>
+    <sheet name="составные важные" sheetId="1" r:id="rId3"/>
+    <sheet name="Вездесущие слова" sheetId="4" r:id="rId4"/>
+    <sheet name="Неизменные_длинные" sheetId="6" r:id="rId5"/>
+    <sheet name="Неизменные_короткие" sheetId="9" r:id="rId6"/>
+    <sheet name="перепсиать" sheetId="8" r:id="rId7"/>
+    <sheet name="создателю ошибки" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'составные важные'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сложные слова'!$A$3:$B$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="555">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -548,9 +550,6 @@
     <t>сама медицина по уши погрязла</t>
   </si>
   <si>
-    <t xml:space="preserve"> само целительство по уши погрязло</t>
-  </si>
-  <si>
     <t>метастазную форму</t>
   </si>
   <si>
@@ -584,9 +583,6 @@
     <t>международной медицинской мафиозной структурой</t>
   </si>
   <si>
-    <t>международным целительским преступным сообществом</t>
-  </si>
-  <si>
     <t>Одесский филиал</t>
   </si>
   <si>
@@ -647,21 +643,12 @@
     <t>современная медицина попыталась</t>
   </si>
   <si>
-    <t>современное целительство попыталось</t>
-  </si>
-  <si>
     <t>сделав медицину своей служанкой</t>
   </si>
   <si>
-    <t>сделав целительство себе прислугой</t>
-  </si>
-  <si>
     <t>В медицинской энциклопедии</t>
   </si>
   <si>
-    <t>В целительском справочнике</t>
-  </si>
-  <si>
     <t>Донор, начав сдавать кровь, (рис. 105) вынужден был это делать потом постоянно, иначе у него</t>
   </si>
   <si>
@@ -1296,6 +1283,438 @@
   </si>
   <si>
     <t>так называемая «средняя точка»</t>
+  </si>
+  <si>
+    <t>мощного магического клана</t>
+  </si>
+  <si>
+    <t>мощной колдовской семьи</t>
+  </si>
+  <si>
+    <t>в магии при энвольтировании</t>
+  </si>
+  <si>
+    <t>при колдовском отождествлении человека с болванкой</t>
+  </si>
+  <si>
+    <t>тунгусскую инъекцию</t>
+  </si>
+  <si>
+    <t>тунгусскуое лекарственное средство, подлежащее введению через иглу</t>
+  </si>
+  <si>
+    <t>картина постепенно начала</t>
+  </si>
+  <si>
+    <t>обстановка постепенно начала</t>
+  </si>
+  <si>
+    <t>современное врачевание попыталось</t>
+  </si>
+  <si>
+    <t>сделав врачевание себе прислугой</t>
+  </si>
+  <si>
+    <t>В врачебном справочнике</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> само врачевание по уши погрязло</t>
+  </si>
+  <si>
+    <t>международным врачебным преступным сообществом</t>
+  </si>
+  <si>
+    <t>Этот астральный адрес</t>
+  </si>
+  <si>
+    <t>Это потустороннее местоположение</t>
+  </si>
+  <si>
+    <t>дней Центра</t>
+  </si>
+  <si>
+    <t>дней Учреждения</t>
+  </si>
+  <si>
+    <t>непрерывной энергоинформационной коррекции</t>
+  </si>
+  <si>
+    <t>непрерывного вездесущего изменения</t>
+  </si>
+  <si>
+    <t>в Центре</t>
+  </si>
+  <si>
+    <t>в Учреждении</t>
+  </si>
+  <si>
+    <t>на наших экранах</t>
+  </si>
+  <si>
+    <t>на наших быдлоящиках</t>
+  </si>
+  <si>
+    <t>стральном плане</t>
+  </si>
+  <si>
+    <t>астральном плане</t>
+  </si>
+  <si>
+    <t>контактантов</t>
+  </si>
+  <si>
+    <t>контактов</t>
+  </si>
+  <si>
+    <t>кагальницкой катастрофы</t>
+  </si>
+  <si>
+    <t>кагальницкого стихийного бедствия</t>
+  </si>
+  <si>
+    <t>астрологом Центра</t>
+  </si>
+  <si>
+    <t>звёздоведом Учреждения</t>
+  </si>
+  <si>
+    <t>американский Центр по исследованию мозга пришел</t>
+  </si>
+  <si>
+    <t>американское Учреждение по исследованию мозга пришло</t>
+  </si>
+  <si>
+    <t>В нашем Центре</t>
+  </si>
+  <si>
+    <t>В нашем Учреждении</t>
+  </si>
+  <si>
+    <t>в нашем Центре</t>
+  </si>
+  <si>
+    <t>в нашем Учреждении</t>
+  </si>
+  <si>
+    <t>В Центр «ЭНИО»</t>
+  </si>
+  <si>
+    <t>из практики Центра</t>
+  </si>
+  <si>
+    <t>из накопленного опыта Учреждения</t>
+  </si>
+  <si>
+    <t>посетители нашего Центра</t>
+  </si>
+  <si>
+    <t>посетители нашего Учреждения</t>
+  </si>
+  <si>
+    <t>пришедшего в Центр</t>
+  </si>
+  <si>
+    <t>пришедшего в Учреждение</t>
+  </si>
+  <si>
+    <t>когда в Центре</t>
+  </si>
+  <si>
+    <t>когда в Учреждении</t>
+  </si>
+  <si>
+    <t>содержание Центра</t>
+  </si>
+  <si>
+    <t>содержание Учреждения</t>
+  </si>
+  <si>
+    <t>канадского Центра</t>
+  </si>
+  <si>
+    <t>канадского Учреждения</t>
+  </si>
+  <si>
+    <t>нашего Центра</t>
+  </si>
+  <si>
+    <t>нашего Учреждения</t>
+  </si>
+  <si>
+    <t>выявленных в Центре</t>
+  </si>
+  <si>
+    <t>выявленных в Учреждении</t>
+  </si>
+  <si>
+    <t>В Центр на</t>
+  </si>
+  <si>
+    <t>В Учреждение на</t>
+  </si>
+  <si>
+    <t>В Учреждение «ЭНИО»</t>
+  </si>
+  <si>
+    <t>в Центре наблюдаются</t>
+  </si>
+  <si>
+    <t>в Учреждении наблюдаются</t>
+  </si>
+  <si>
+    <t>«зарядили» в Центре</t>
+  </si>
+  <si>
+    <t>«зарядили» в Учреждении</t>
+  </si>
+  <si>
+    <t>Центр потерял возможность</t>
+  </si>
+  <si>
+    <t>Учреждение потеряло возможность</t>
+  </si>
+  <si>
+    <t>к маме в Центр</t>
+  </si>
+  <si>
+    <t>к маме в Учреждение</t>
+  </si>
+  <si>
+    <t>в Центре постоянно</t>
+  </si>
+  <si>
+    <t>в Учреждении постоянно</t>
+  </si>
+  <si>
+    <t>в Центре имеются</t>
+  </si>
+  <si>
+    <t>в Учреждении имеются</t>
+  </si>
+  <si>
+    <t>впал наш Центр, постоянно вскрывающий эти “гнойные нарывы” и обнажающий</t>
+  </si>
+  <si>
+    <t>впало наше Учреждение, постоянно вскрывающее эти “гнойные нарывы” и обнажающее</t>
+  </si>
+  <si>
+    <t>в годы практики в Центре</t>
+  </si>
+  <si>
+    <t>в годы опытов в Учреждении</t>
+  </si>
+  <si>
+    <t>наш Центр предлагает</t>
+  </si>
+  <si>
+    <t>наше Учреждение предлагает</t>
+  </si>
+  <si>
+    <t>в Центре относят</t>
+  </si>
+  <si>
+    <t>в Учреждении относят</t>
+  </si>
+  <si>
+    <t>Эниокорректоры Центра</t>
+  </si>
+  <si>
+    <t>Вездесущие изменители</t>
+  </si>
+  <si>
+    <t>мы потом в Центре</t>
+  </si>
+  <si>
+    <t>мы потом в Учреждении</t>
+  </si>
+  <si>
+    <t>Центра «ЭНИО»</t>
+  </si>
+  <si>
+    <t>Учреждения «ЭНИО»</t>
+  </si>
+  <si>
+    <t>В Центр постоянно обращаются</t>
+  </si>
+  <si>
+    <t>В Учреждение постоянно обращаются</t>
+  </si>
+  <si>
+    <t>В Центр практически</t>
+  </si>
+  <si>
+    <t>В Учреждение в действительности</t>
+  </si>
+  <si>
+    <t>В Центре собран</t>
+  </si>
+  <si>
+    <t>В Учреждении собран</t>
+  </si>
+  <si>
+    <t>В Центре индивидуальная</t>
+  </si>
+  <si>
+    <t>В Центре личная</t>
+  </si>
+  <si>
+    <t>работу в Центре</t>
+  </si>
+  <si>
+    <t>работу в Учреждении</t>
+  </si>
+  <si>
+    <t>к организации в Центре</t>
+  </si>
+  <si>
+    <t>к открытию в Учреждении</t>
+  </si>
+  <si>
+    <t>по телефону в Центр</t>
+  </si>
+  <si>
+    <t>по телефону в Учреждение</t>
+  </si>
+  <si>
+    <t>В Центре приходилось</t>
+  </si>
+  <si>
+    <t>В Учреждении приходилось</t>
+  </si>
+  <si>
+    <t>Центра:</t>
+  </si>
+  <si>
+    <t>Учреждения:</t>
+  </si>
+  <si>
+    <t>в Центр за прогнозами</t>
+  </si>
+  <si>
+    <t>в Учреждение за предсказаниями</t>
+  </si>
+  <si>
+    <t>ростовской прессы</t>
+  </si>
+  <si>
+    <t>ростовских новостных изданий</t>
+  </si>
+  <si>
+    <t>дать вашему Центру</t>
+  </si>
+  <si>
+    <t>дать вашему Учреждению</t>
+  </si>
+  <si>
+    <t>Центре «ЭНИО»</t>
+  </si>
+  <si>
+    <t>Учреждении «ЭНИО»</t>
+  </si>
+  <si>
+    <t>энергоинформационной картине</t>
+  </si>
+  <si>
+    <t>вездесущному изображению</t>
+  </si>
+  <si>
+    <t>Компьютерная картинка</t>
+  </si>
+  <si>
+    <t>Компьютерное изображение</t>
+  </si>
+  <si>
+    <t>Компьютерная картинка четко показала</t>
+  </si>
+  <si>
+    <t>Компьютерное изображение четко показало</t>
+  </si>
+  <si>
+    <t>складываться увлекательное явление</t>
+  </si>
+  <si>
+    <t>складываться интересная картина</t>
+  </si>
+  <si>
+    <t>образ постепенно начал</t>
+  </si>
+  <si>
+    <t>астральную мыслеформу</t>
+  </si>
+  <si>
+    <t>потусторонний мыслеобраз</t>
+  </si>
+  <si>
+    <t>чем конкретнее создана мыслеформа, тем конкретнее пройдет ее материализация</t>
+  </si>
+  <si>
+    <t>чем чётче создан мыслеобраз, тем чётче пройдет его воплощение</t>
+  </si>
+  <si>
+    <t>создана мыслеформа</t>
+  </si>
+  <si>
+    <t>создан мыслеобраз</t>
+  </si>
+  <si>
+    <t>на информационную структуру воды</t>
+  </si>
+  <si>
+    <t>на несущее сведения устройство воды</t>
+  </si>
+  <si>
+    <t>тонкую деталировку</t>
+  </si>
+  <si>
+    <t>тонкое рассмотрение</t>
+  </si>
+  <si>
+    <t>Структура многомерного энергоинформационного каркаса справедлива</t>
+  </si>
+  <si>
+    <t>Вездесущное многомерное устройство   мироздания справедливо</t>
+  </si>
+  <si>
+    <t>проектируется в ментальный план</t>
+  </si>
+  <si>
+    <t>вкладывается в ментальный план</t>
+  </si>
+  <si>
+    <t>увлечение деталировкой</t>
+  </si>
+  <si>
+    <t>увлечение подробностями</t>
+  </si>
+  <si>
+    <t>переносится необходимая для постоянного сохранения информация</t>
+  </si>
+  <si>
+    <t>переносятся необходимые для постоянного сохранения сведения</t>
+  </si>
+  <si>
+    <t>Мыслеформа, запущенная</t>
+  </si>
+  <si>
+    <t>Мыслетело, запущенное</t>
+  </si>
+  <si>
+    <t>один из сложнейших моментов</t>
+  </si>
+  <si>
+    <t>одно из сложнейших особенностей</t>
+  </si>
+  <si>
+    <t>генерации мыслеобразов</t>
+  </si>
+  <si>
+    <t>создании мыслеобразов</t>
+  </si>
+  <si>
+    <t>Похожей была и ситуация</t>
+  </si>
+  <si>
+    <t>Похожим был и случай</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1354,6 +1773,12 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1635,393 +2060,393 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="31.921875" customWidth="1"/>
-    <col min="2" max="2" width="42.53515625" customWidth="1"/>
+    <col min="1" max="1" width="31.89453125" customWidth="1"/>
+    <col min="2" max="2" width="42.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B3" t="s">
         <v>266</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="B5" t="s">
         <v>268</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="B7" t="s">
         <v>270</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="B8" t="s">
         <v>272</v>
       </c>
-      <c r="B5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B16" t="s">
         <v>278</v>
       </c>
-      <c r="B6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>274</v>
-      </c>
-      <c r="B7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>257</v>
-      </c>
-      <c r="B15" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>282</v>
-      </c>
-      <c r="B16" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>285</v>
+      </c>
+      <c r="B19" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>283</v>
+      </c>
+      <c r="B21" t="s">
         <v>284</v>
       </c>
-      <c r="B18" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>290</v>
-      </c>
-      <c r="B19" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>286</v>
-      </c>
-      <c r="B20" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
+      <c r="B22" t="s">
         <v>288</v>
       </c>
-      <c r="B21" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>292</v>
-      </c>
-      <c r="B22" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>217</v>
+      </c>
+      <c r="B24" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>221</v>
+      </c>
+      <c r="B25" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" t="s">
         <v>224</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>222</v>
-      </c>
-      <c r="B24" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
+      <c r="B27" t="s">
         <v>226</v>
       </c>
-      <c r="B25" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
+      <c r="B28" t="s">
         <v>228</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>235</v>
+      </c>
+      <c r="B29" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>233</v>
+      </c>
+      <c r="B30" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
+      <c r="B31" t="s">
         <v>230</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
+      <c r="B32" t="s">
         <v>232</v>
       </c>
-      <c r="B28" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>240</v>
-      </c>
-      <c r="B29" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>238</v>
-      </c>
-      <c r="B30" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>234</v>
-      </c>
-      <c r="B31" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>236</v>
-      </c>
-      <c r="B32" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
+        <v>340</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>341</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>343</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
         <v>345</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
+      <c r="B36" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B34" s="1" t="s">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
+      <c r="B37" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B35" s="1" t="s">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
+      <c r="B38" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B36" s="1" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
+      <c r="B39" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B37" s="1" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>354</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
-        <v>356</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>358</v>
-      </c>
       <c r="B40" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
     </row>
@@ -2035,14 +2460,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B41"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A3:B50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="47.53515625" customWidth="1"/>
-    <col min="2" max="2" width="27.69140625" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="38.41796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2050,7 +2475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2058,7 +2483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2066,7 +2491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2074,7 +2499,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2082,7 +2507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2090,23 +2515,23 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B9" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B10" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2114,7 +2539,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2122,7 +2547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2130,7 +2555,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2138,7 +2563,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2146,7 +2571,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2154,7 +2579,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2162,7 +2587,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -2170,7 +2595,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -2178,7 +2603,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -2186,7 +2611,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -2194,7 +2619,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -2202,7 +2627,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -2210,7 +2635,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2218,7 +2643,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2226,7 +2651,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -2234,7 +2659,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -2242,7 +2667,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -2250,7 +2675,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2258,7 +2683,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2266,15 +2691,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B31" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -2282,7 +2707,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -2290,7 +2715,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -2298,115 +2723,142 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B40" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>438</v>
+      </c>
+      <c r="B42" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>520</v>
+      </c>
+      <c r="B43" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>522</v>
+      </c>
+      <c r="B44" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>529</v>
+      </c>
+      <c r="B45" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>533</v>
+      </c>
+      <c r="B46" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>537</v>
+      </c>
+      <c r="B47" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>543</v>
+      </c>
+      <c r="B48" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>547</v>
+      </c>
+      <c r="B49" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:B42" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="32.84375" customWidth="1"/>
-    <col min="2" max="2" width="28.61328125" customWidth="1"/>
+    <col min="1" max="1" width="65.3671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="77.3671875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>404</v>
-      </c>
-      <c r="B4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="65.3828125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="77.3828125" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2414,7 +2866,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>46</v>
       </c>
@@ -2422,7 +2874,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2430,15 +2882,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>135</v>
       </c>
@@ -2446,7 +2898,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>90</v>
       </c>
@@ -2454,7 +2906,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>50</v>
       </c>
@@ -2462,7 +2914,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
@@ -2470,7 +2922,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>109</v>
       </c>
@@ -2478,7 +2930,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>123</v>
       </c>
@@ -2486,7 +2938,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -2494,7 +2946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>137</v>
       </c>
@@ -2505,15 +2957,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>106</v>
       </c>
@@ -2521,7 +2973,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -2529,7 +2981,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>78</v>
       </c>
@@ -2537,7 +2989,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>102</v>
       </c>
@@ -2545,7 +2997,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>151</v>
       </c>
@@ -2553,111 +3005,111 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="B24" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
         <v>88</v>
       </c>
@@ -2665,100 +3117,140 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="2" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B35" s="2" t="s">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="2" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" s="2" t="s">
+      <c r="B37" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A41" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A42" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A44" s="2" t="s">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>413</v>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -2770,637 +3262,1115 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="32.83984375" customWidth="1"/>
+    <col min="2" max="2" width="28.62890625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B78"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B133"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="66.53515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="70.15234375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="43.20703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="39.734375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" s="2" t="s">
+      <c r="B28" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="2" t="s">
+    </row>
+    <row r="30" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" s="2" t="s">
+      <c r="B30" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B30" s="4" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="3" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B31" s="2" t="s">
+    </row>
+    <row r="32" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="3" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B32" s="2" t="s">
+    </row>
+    <row r="33" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33" s="2" t="s">
+      <c r="B33" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B35" s="2" t="s">
+    <row r="36" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A42" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A43" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A44" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A45" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A46" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A47" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A48" s="2" t="s">
+      <c r="B46" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A49" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="28.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B50" s="2" t="s">
+    </row>
+    <row r="53" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="3" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A51" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B51" s="4" t="s">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="3" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A52" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A53" s="2" t="s">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B55" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A54" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A55" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A57" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A58" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A59" s="2" t="s">
+    <row r="58" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B60" s="3" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A60" s="2" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B60" s="2" t="s">
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="6" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A61" s="2" t="s">
+      <c r="B63" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A62" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A63" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A64" s="2" t="s">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A65" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B65" s="2" t="s">
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="3" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A66" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A67" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A68" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A69" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A70" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A71" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A72" s="2" t="s">
+      <c r="B66" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A73" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A74" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A75" s="2" t="s">
+      <c r="B73" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A76" s="2" t="s">
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A77" s="2" t="s">
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A78" s="2" t="s">
+    </row>
+    <row r="79" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B78" s="2" t="s">
+    </row>
+    <row r="80" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="3" t="s">
         <v>415</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" t="s">
+        <v>524</v>
+      </c>
+      <c r="B125" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -3409,13 +4379,22 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C9E41E9-C4FF-4A2E-9387-ABCBB02BFCB3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -3423,85 +4402,101 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
-  <dimension ref="A2:B10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A2:B12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="40.84375" customWidth="1"/>
+    <col min="1" max="1" width="40.83984375" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B8" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>358</v>
+      </c>
+      <c r="B10" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>252</v>
-      </c>
-      <c r="B6" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>265</v>
-      </c>
-      <c r="B7" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>310</v>
-      </c>
-      <c r="B8" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>323</v>
-      </c>
-      <c r="B9" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>363</v>
-      </c>
-      <c r="B10" t="s">
-        <v>376</v>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>434</v>
+      </c>
+      <c r="B11" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>436</v>
+      </c>
+      <c r="B12" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36B01B2-01E8-44B9-BF6E-2F73495A925E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679797E2-620F-427D-B6D4-6E7159F45433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="746" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="746" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -42,15 +42,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="553">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -208,18 +205,9 @@
     <t>Клеткоподобное равновесное устройство</t>
   </si>
   <si>
-    <t>привычный нам объем</t>
-  </si>
-  <si>
-    <t>привычное нам количество</t>
-  </si>
-  <si>
     <t>информация, записанная на объемной форме молекулы, способна перезаписываться</t>
   </si>
   <si>
-    <t>сведения, записанные на объемном виде молекулы, способны перезаписываться</t>
-  </si>
-  <si>
     <t xml:space="preserve">эзотерический и физический аспект так называемой </t>
   </si>
   <si>
@@ -445,9 +433,6 @@
     <t>Обычный пример такой связи</t>
   </si>
   <si>
-    <t>любой количественный образ неким способом создаёт вокруг себя пространство</t>
-  </si>
-  <si>
     <t>любая объемная форма неким образом структурирует вокруг себя пространство</t>
   </si>
   <si>
@@ -1715,6 +1700,12 @@
   </si>
   <si>
     <t>Похожим был и случай</t>
+  </si>
+  <si>
+    <t>любой объёмный образ неким способом создаёт вокруг себя пространство</t>
+  </si>
+  <si>
+    <t>сведения, записанные на объёмном образе молекулы, способны перезаписываться</t>
   </si>
 </sst>
 </file>
@@ -2060,393 +2051,393 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.89453125" customWidth="1"/>
-    <col min="2" max="2" width="42.5234375" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="2" max="2" width="42.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>261</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>263</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>265</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>267</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B8" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B15" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>273</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B16" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B15" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>277</v>
-      </c>
-      <c r="B16" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B18" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>281</v>
+      </c>
+      <c r="B19" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>277</v>
+      </c>
+      <c r="B20" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>279</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B21" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>285</v>
-      </c>
-      <c r="B19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>281</v>
-      </c>
-      <c r="B20" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>283</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
-        <v>287</v>
-      </c>
-      <c r="B22" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>219</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B26" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" t="s">
-        <v>217</v>
-      </c>
-      <c r="B24" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>221</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B27" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>223</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B28" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>231</v>
+      </c>
+      <c r="B29" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>225</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B31" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>227</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B32" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>235</v>
-      </c>
-      <c r="B29" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>233</v>
-      </c>
-      <c r="B30" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
-        <v>229</v>
-      </c>
-      <c r="B31" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
-        <v>231</v>
-      </c>
-      <c r="B32" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>336</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>337</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>339</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>341</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>343</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>345</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>347</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>349</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
-        <v>351</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>353</v>
-      </c>
       <c r="B40" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
     </row>
@@ -2461,13 +2452,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
   <dimension ref="A3:B50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="38.41796875" customWidth="1"/>
+    <col min="2" max="2" width="38.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2475,7 +2466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2483,7 +2474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2491,7 +2482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2499,7 +2490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2507,7 +2498,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2515,23 +2506,23 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B10" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2539,7 +2530,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2547,7 +2538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2555,7 +2546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2563,7 +2554,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2571,7 +2562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2579,7 +2570,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2587,7 +2578,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -2595,7 +2586,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -2603,7 +2594,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -2611,7 +2602,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -2619,7 +2610,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -2627,7 +2618,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -2635,7 +2626,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2643,204 +2634,196 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
         <v>62</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
+      <c r="B28" t="s">
         <v>64</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
+      <c r="B29" t="s">
         <v>66</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
+      <c r="B30" t="s">
         <v>68</v>
       </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B31" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>208</v>
+      </c>
+      <c r="B37" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>211</v>
+      </c>
+      <c r="B38" t="s">
         <v>212</v>
       </c>
-      <c r="B37" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
-        <v>215</v>
-      </c>
-      <c r="B38" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B39" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B40" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B42" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B43" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B44" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>525</v>
+      </c>
+      <c r="B45" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>529</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>533</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
-        <v>537</v>
-      </c>
-      <c r="B47" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>539</v>
+      </c>
+      <c r="B48" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>543</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" s="1" t="s">
         <v>548</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -2852,13 +2835,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.3671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="77.3671875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="65.36328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="77.36328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2866,7 +2849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>46</v>
       </c>
@@ -2874,7 +2857,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2882,31 +2865,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>50</v>
       </c>
@@ -2914,7 +2897,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
@@ -2922,23 +2905,23 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -2946,34 +2929,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -2981,276 +2964,276 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="2" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -3265,42 +3248,42 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.83984375" customWidth="1"/>
-    <col min="2" max="2" width="28.62890625" customWidth="1"/>
+    <col min="1" max="1" width="32.81640625" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -3311,13 +3294,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
   <dimension ref="A1:B133"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.20703125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="39.734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="43.1796875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="39.7265625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>40</v>
       </c>
@@ -3325,7 +3308,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -3333,1044 +3316,1044 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B45" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A79" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="B81" s="3" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="28.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="3" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A105" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>520</v>
+      </c>
+      <c r="B125" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A110" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125" t="s">
+      <c r="B127" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B125" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" s="1" t="s">
+    </row>
+    <row r="128" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A128" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B127" s="3" t="s">
+      <c r="B128" s="3" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128" s="3" t="s">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B129" s="3" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129" s="3" t="s">
+    <row r="130" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A130" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B130" s="3" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A130" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B132" s="3" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132" s="3" t="s">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B133" s="3" t="s">
         <v>550</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A133" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -4381,7 +4364,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C9E41E9-C4FF-4A2E-9387-ABCBB02BFCB3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4390,11 +4373,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -4405,98 +4388,98 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
   <dimension ref="A2:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.83984375" customWidth="1"/>
+    <col min="1" max="1" width="40.81640625" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>354</v>
+      </c>
+      <c r="B10" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>260</v>
-      </c>
-      <c r="B7" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>305</v>
-      </c>
-      <c r="B8" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>318</v>
-      </c>
-      <c r="B9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>358</v>
-      </c>
-      <c r="B10" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B11" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B12" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679797E2-620F-427D-B6D4-6E7159F45433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A822E7C-A044-4072-AFEA-ACA6C45BDB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="746" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="746" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
     <sheet name="Сложные слова" sheetId="3" r:id="rId2"/>
-    <sheet name="составные важные" sheetId="1" r:id="rId3"/>
-    <sheet name="Вездесущие слова" sheetId="4" r:id="rId4"/>
-    <sheet name="Неизменные_длинные" sheetId="6" r:id="rId5"/>
-    <sheet name="Неизменные_короткие" sheetId="9" r:id="rId6"/>
-    <sheet name="перепсиать" sheetId="8" r:id="rId7"/>
-    <sheet name="создателю ошибки" sheetId="7" r:id="rId8"/>
+    <sheet name="неизменные" sheetId="10" r:id="rId3"/>
+    <sheet name="составные важные" sheetId="1" r:id="rId4"/>
+    <sheet name="Вездесущие слова" sheetId="4" r:id="rId5"/>
+    <sheet name="Неизменные_длинные" sheetId="6" r:id="rId6"/>
+    <sheet name="Неизменные_короткие" sheetId="9" r:id="rId7"/>
+    <sheet name="перепсиать" sheetId="8" r:id="rId8"/>
+    <sheet name="создателю ошибки" sheetId="7" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сложные слова'!$A$3:$B$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сложные слова'!$A$1:$B$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'составные важные'!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,12 +43,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="595">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -1706,6 +1710,132 @@
   </si>
   <si>
     <t>сведения, записанные на объёмном образе молекулы, способны перезаписываться</t>
+  </si>
+  <si>
+    <t>Космического Донорства</t>
+  </si>
+  <si>
+    <t>Межзвёздно-пространственной Жертвенности</t>
+  </si>
+  <si>
+    <t>христианский эгрегор</t>
+  </si>
+  <si>
+    <t>христианское совместное сознание</t>
+  </si>
+  <si>
+    <t>вся воспринимаемая информация адаптируется</t>
+  </si>
+  <si>
+    <t>все воспринимаемые сведения приспосабливаются</t>
+  </si>
+  <si>
+    <t>прикладной эниологии</t>
+  </si>
+  <si>
+    <t>прикладного вездесущеведения</t>
+  </si>
+  <si>
+    <t>энергоинформационная коррекция</t>
+  </si>
+  <si>
+    <t>энерговампиризм</t>
+  </si>
+  <si>
+    <t>энерговампиризма</t>
+  </si>
+  <si>
+    <t>энерговампиризмам</t>
+  </si>
+  <si>
+    <t>энерговампиризмами</t>
+  </si>
+  <si>
+    <t>энерговампиризмах</t>
+  </si>
+  <si>
+    <t>зарядо-высасывание</t>
+  </si>
+  <si>
+    <t>зарядо-высасывания</t>
+  </si>
+  <si>
+    <t>зарядо-высасываниям</t>
+  </si>
+  <si>
+    <t>зарядо-высасываниями</t>
+  </si>
+  <si>
+    <t>зарядо-высасываниях</t>
+  </si>
+  <si>
+    <t>энерговампиризме</t>
+  </si>
+  <si>
+    <t>зарядо-высасывании</t>
+  </si>
+  <si>
+    <t>энерговампиризму</t>
+  </si>
+  <si>
+    <t>зарядо-высасыванию</t>
+  </si>
+  <si>
+    <t>энерговампиризмы</t>
+  </si>
+  <si>
+    <t>энерговампиризмом</t>
+  </si>
+  <si>
+    <t>зарядо-высасыванием</t>
+  </si>
+  <si>
+    <t>энерговампиризмов</t>
+  </si>
+  <si>
+    <t>зарядо-высасываний</t>
+  </si>
+  <si>
+    <t>по полной форме</t>
+  </si>
+  <si>
+    <t>по полному состоянию</t>
+  </si>
+  <si>
+    <t>энергоинформационного вируса</t>
+  </si>
+  <si>
+    <t>вездесущной заразы</t>
+  </si>
+  <si>
+    <t>озарившую его «теорию</t>
+  </si>
+  <si>
+    <t>озарившее его «учение</t>
+  </si>
+  <si>
+    <t>космологическая модель</t>
+  </si>
+  <si>
+    <t>вселенско изучаемый прообраз</t>
+  </si>
+  <si>
+    <t>космологическая модель перенесла</t>
+  </si>
+  <si>
+    <t>вселенско изучаемый прообраз перенёс</t>
+  </si>
+  <si>
+    <t>Термин “Информационные Поля” (ИП) стал</t>
+  </si>
+  <si>
+    <t>Понятия “Несущие сведения Поля” (ИП) стало</t>
+  </si>
+  <si>
+    <t>возможны два варианта его возврата</t>
+  </si>
+  <si>
+    <t>возможны два исхода её возврата</t>
   </si>
 </sst>
 </file>
@@ -2051,13 +2181,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="31.90625" customWidth="1"/>
-    <col min="2" max="2" width="42.54296875" customWidth="1"/>
+    <col min="1" max="1" width="31.89453125" customWidth="1"/>
+    <col min="2" max="2" width="42.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>257</v>
       </c>
@@ -2065,7 +2195,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>259</v>
       </c>
@@ -2073,7 +2203,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>261</v>
       </c>
@@ -2081,7 +2211,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>271</v>
       </c>
@@ -2089,7 +2219,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>263</v>
       </c>
@@ -2097,7 +2227,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>269</v>
       </c>
@@ -2105,7 +2235,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>265</v>
       </c>
@@ -2113,7 +2243,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>267</v>
       </c>
@@ -2121,7 +2251,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>285</v>
       </c>
@@ -2129,7 +2259,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>287</v>
       </c>
@@ -2137,7 +2267,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>289</v>
       </c>
@@ -2145,7 +2275,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>291</v>
       </c>
@@ -2153,7 +2283,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>293</v>
       </c>
@@ -2161,7 +2291,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>295</v>
       </c>
@@ -2169,7 +2299,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>248</v>
       </c>
@@ -2177,7 +2307,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>273</v>
       </c>
@@ -2185,11 +2315,11 @@
         <v>274</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>275</v>
       </c>
@@ -2197,7 +2327,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>281</v>
       </c>
@@ -2205,7 +2335,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>277</v>
       </c>
@@ -2213,7 +2343,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>279</v>
       </c>
@@ -2221,7 +2351,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>283</v>
       </c>
@@ -2229,7 +2359,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>215</v>
       </c>
@@ -2237,7 +2367,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>213</v>
       </c>
@@ -2245,7 +2375,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>217</v>
       </c>
@@ -2253,7 +2383,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>219</v>
       </c>
@@ -2261,7 +2391,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>221</v>
       </c>
@@ -2269,7 +2399,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>223</v>
       </c>
@@ -2277,7 +2407,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>231</v>
       </c>
@@ -2285,7 +2415,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>229</v>
       </c>
@@ -2293,7 +2423,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>225</v>
       </c>
@@ -2301,7 +2431,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>227</v>
       </c>
@@ -2309,7 +2439,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>336</v>
       </c>
@@ -2317,7 +2447,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>337</v>
       </c>
@@ -2325,7 +2455,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>339</v>
       </c>
@@ -2333,7 +2463,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>341</v>
       </c>
@@ -2341,7 +2471,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>343</v>
       </c>
@@ -2349,7 +2479,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>345</v>
       </c>
@@ -2357,7 +2487,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>347</v>
       </c>
@@ -2365,7 +2495,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>349</v>
       </c>
@@ -2373,71 +2503,111 @@
         <v>342</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
     </row>
@@ -2451,222 +2621,247 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A3:B50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="38.453125" customWidth="1"/>
+    <col min="2" max="2" width="38.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>352</v>
+      </c>
+      <c r="B13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>434</v>
+      </c>
+      <c r="B14" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>518</v>
+      </c>
+      <c r="B18" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>543</v>
+      </c>
+      <c r="B24" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B26" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>350</v>
-      </c>
-      <c r="B9" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>352</v>
-      </c>
-      <c r="B10" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>559</v>
+      </c>
+      <c r="B27" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
         <v>30</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -2674,174 +2869,231 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B31" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>533</v>
+      </c>
+      <c r="B33" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>539</v>
+      </c>
+      <c r="B36" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>555</v>
+      </c>
+      <c r="B39" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>516</v>
+      </c>
+      <c r="B42" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>211</v>
+      </c>
+      <c r="B43" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
         <v>385</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B44" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>145</v>
-      </c>
-      <c r="B35" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>162</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>208</v>
-      </c>
-      <c r="B37" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>211</v>
-      </c>
-      <c r="B38" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>233</v>
-      </c>
-      <c r="B39" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
         <v>250</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B45" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
         <v>299</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>434</v>
-      </c>
-      <c r="B42" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>516</v>
-      </c>
-      <c r="B43" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>518</v>
-      </c>
-      <c r="B44" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>525</v>
-      </c>
-      <c r="B45" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>529</v>
-      </c>
-      <c r="B46" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>533</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>539</v>
+        <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="B49" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>548</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>583</v>
+      </c>
+      <c r="B50" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>587</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>588</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B42" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}"/>
+  <autoFilter ref="A1:B48" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="может быть осуществлена коррекция"/>
+        <filter val="энергоинформационной коррекции"/>
+        <filter val="энергоинформационную коррекцию"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B50">
+    <sortCondition ref="A1:A50"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629FBABB-5E47-4235-BB5F-3D637E48298E}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="65.36328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="77.36328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="36.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="65.3671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="77.3671875" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2849,7 +3101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>46</v>
       </c>
@@ -2857,7 +3109,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2865,7 +3117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>377</v>
       </c>
@@ -2873,7 +3125,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>131</v>
       </c>
@@ -2881,7 +3133,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>87</v>
       </c>
@@ -2889,7 +3141,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>50</v>
       </c>
@@ -2897,7 +3149,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
@@ -2905,7 +3157,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>106</v>
       </c>
@@ -2913,7 +3165,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>120</v>
       </c>
@@ -2921,7 +3173,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -2929,7 +3181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>133</v>
       </c>
@@ -2940,7 +3192,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>177</v>
       </c>
@@ -2948,7 +3200,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>103</v>
       </c>
@@ -2956,7 +3208,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -2964,7 +3216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>75</v>
       </c>
@@ -2972,7 +3224,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>99</v>
       </c>
@@ -2980,7 +3232,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>147</v>
       </c>
@@ -2988,7 +3240,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>180</v>
       </c>
@@ -2996,7 +3248,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>184</v>
       </c>
@@ -3004,7 +3256,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>190</v>
       </c>
@@ -3012,7 +3264,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>192</v>
       </c>
@@ -3020,7 +3272,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>193</v>
       </c>
@@ -3028,7 +3280,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>194</v>
       </c>
@@ -3036,7 +3288,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
         <v>235</v>
       </c>
@@ -3044,7 +3296,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
         <v>253</v>
       </c>
@@ -3052,7 +3304,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
         <v>237</v>
       </c>
@@ -3060,7 +3312,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
         <v>254</v>
       </c>
@@ -3068,7 +3320,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
         <v>310</v>
       </c>
@@ -3076,7 +3328,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2" t="s">
         <v>312</v>
       </c>
@@ -3084,7 +3336,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
         <v>315</v>
       </c>
@@ -3092,7 +3344,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
         <v>85</v>
       </c>
@@ -3100,7 +3352,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2" t="s">
         <v>370</v>
       </c>
@@ -3108,7 +3360,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
         <v>323</v>
       </c>
@@ -3116,7 +3368,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
         <v>325</v>
       </c>
@@ -3124,7 +3376,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2" t="s">
         <v>329</v>
       </c>
@@ -3132,7 +3384,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2" t="s">
         <v>331</v>
       </c>
@@ -3140,7 +3392,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2" t="s">
         <v>334</v>
       </c>
@@ -3148,7 +3400,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2" t="s">
         <v>379</v>
       </c>
@@ -3156,7 +3408,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
         <v>387</v>
       </c>
@@ -3164,7 +3416,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
         <v>389</v>
       </c>
@@ -3172,7 +3424,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2" t="s">
         <v>391</v>
       </c>
@@ -3180,7 +3432,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2" t="s">
         <v>399</v>
       </c>
@@ -3188,7 +3440,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
         <v>403</v>
       </c>
@@ -3196,7 +3448,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="2" t="s">
         <v>407</v>
       </c>
@@ -3204,7 +3456,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2" t="s">
         <v>413</v>
       </c>
@@ -3212,7 +3464,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
         <v>420</v>
       </c>
@@ -3220,7 +3472,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
         <v>424</v>
       </c>
@@ -3228,12 +3480,20 @@
         <v>425</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2" t="s">
         <v>537</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>538</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -3245,16 +3505,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="32.81640625" customWidth="1"/>
-    <col min="2" max="2" width="28.6328125" customWidth="1"/>
+    <col min="1" max="1" width="32.7890625" customWidth="1"/>
+    <col min="2" max="2" width="28.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>151</v>
       </c>
@@ -3262,7 +3522,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>157</v>
       </c>
@@ -3270,7 +3530,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>368</v>
       </c>
@@ -3278,1082 +3538,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>395</v>
       </c>
       <c r="B4" t="s">
         <v>396</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B133"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="43.1796875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="39.7265625" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="42.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A58" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A78" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A105" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>520</v>
-      </c>
-      <c r="B125" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A128" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A130" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A131" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A132" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A133" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -4362,22 +3552,1114 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C9E41E9-C4FF-4A2E-9387-ABCBB02BFCB3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
+  <dimension ref="A1:B133"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="43.15625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="39.734375" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="28.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" t="s">
+        <v>520</v>
+      </c>
+      <c r="B125" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C9E41E9-C4FF-4A2E-9387-ABCBB02BFCB3}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="42.41796875" customWidth="1"/>
+    <col min="2" max="2" width="38.20703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>333</v>
+        <v>553</v>
+      </c>
+      <c r="B1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>593</v>
+      </c>
+      <c r="B4" t="s">
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -4386,15 +4668,30 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
   <dimension ref="A2:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="40.81640625" customWidth="1"/>
+    <col min="1" max="1" width="40.7890625" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>210</v>
       </c>
@@ -4402,7 +4699,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>360</v>
       </c>
@@ -4410,7 +4707,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>241</v>
       </c>
@@ -4418,7 +4715,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>242</v>
       </c>
@@ -4426,7 +4723,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>243</v>
       </c>
@@ -4434,7 +4731,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>256</v>
       </c>
@@ -4442,7 +4739,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>301</v>
       </c>
@@ -4450,7 +4747,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>314</v>
       </c>
@@ -4458,7 +4755,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>354</v>
       </c>
@@ -4466,7 +4763,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>430</v>
       </c>
@@ -4474,7 +4771,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>432</v>
       </c>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A822E7C-A044-4072-AFEA-ACA6C45BDB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2294FA86-00B2-4817-BF57-2506407CC294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="746" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="746" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
     <sheet name="Сложные слова" sheetId="3" r:id="rId2"/>
-    <sheet name="неизменные" sheetId="10" r:id="rId3"/>
-    <sheet name="составные важные" sheetId="1" r:id="rId4"/>
+    <sheet name="составные важные" sheetId="1" r:id="rId3"/>
+    <sheet name="неизменные" sheetId="10" r:id="rId4"/>
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId5"/>
     <sheet name="Неизменные_длинные" sheetId="6" r:id="rId6"/>
     <sheet name="Неизменные_короткие" sheetId="9" r:id="rId7"/>
@@ -24,8 +24,9 @@
     <sheet name="создателю ошибки" sheetId="7" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сложные слова'!$A$1:$B$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'составные важные'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Неизменные_длинные!$A$1:$B$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сложные слова'!$A$1:$B$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$1:$B$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="738">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -314,21 +315,12 @@
     <t>все мои изъятые возможности</t>
   </si>
   <si>
-    <t>живой разумный организм</t>
-  </si>
-  <si>
-    <t>живое разумное тело</t>
-  </si>
-  <si>
     <t>эксплуатируемый всего</t>
   </si>
   <si>
     <t>используемый всешл</t>
   </si>
   <si>
-    <t>создаваемый мыслеобраз должен быть полноценным и для его входа</t>
-  </si>
-  <si>
     <t>генерируемая мыслеформа должна быть полноценна и для ее входа</t>
   </si>
   <si>
@@ -461,9 +453,6 @@
     <t>Принцип действия подобных мыслеформ вполне понятен</t>
   </si>
   <si>
-    <t>Правило действия подобных мыслеобразов вполне понятно</t>
-  </si>
-  <si>
     <t>Этот книгопечатный “произведение искусства” В. Приваловой сразу же привлек</t>
   </si>
   <si>
@@ -503,9 +492,6 @@
     <t>Этот эффект был великолепно экспериментально доказан</t>
   </si>
   <si>
-    <t>это последствие было великолепноопытно доказано академиком</t>
-  </si>
-  <si>
     <t>большой «скрытой массы»</t>
   </si>
   <si>
@@ -569,9 +555,6 @@
     <t>началось непостижимое судебное разбирательство</t>
   </si>
   <si>
-    <t>международной медицинской мафиозной структурой</t>
-  </si>
-  <si>
     <t>Одесский филиал</t>
   </si>
   <si>
@@ -659,9 +642,6 @@
     <t>мыслеформа и мыслеобраз являются категориями</t>
   </si>
   <si>
-    <t>мыслеобраз является понятием</t>
-  </si>
-  <si>
     <t>в некий энергоинформационный «банк»</t>
   </si>
   <si>
@@ -767,9 +747,6 @@
     <t>Мыслеобраз преобразуется в мыслеформу</t>
   </si>
   <si>
-    <t>Мыслеобраз преобразуется</t>
-  </si>
-  <si>
     <t>тот магический эгрегор, который в данном «спектакле» принимал</t>
   </si>
   <si>
@@ -1025,9 +1002,6 @@
     <t>ваша мыслеформа вышла</t>
   </si>
   <si>
-    <t>ваш мыслеобраз вышел</t>
-  </si>
-  <si>
     <t>целому магическому клану</t>
   </si>
   <si>
@@ -1037,9 +1011,6 @@
     <t>была создана следующая мыслеформа</t>
   </si>
   <si>
-    <t>был создан следующий мыслеобраз</t>
-  </si>
-  <si>
     <t>дистанционной и при индивидуальной коррекции</t>
   </si>
   <si>
@@ -1310,9 +1281,6 @@
     <t xml:space="preserve"> само врачевание по уши погрязло</t>
   </si>
   <si>
-    <t>международным врачебным преступным сообществом</t>
-  </si>
-  <si>
     <t>Этот астральный адрес</t>
   </si>
   <si>
@@ -1631,21 +1599,12 @@
     <t>астральную мыслеформу</t>
   </si>
   <si>
-    <t>потусторонний мыслеобраз</t>
-  </si>
-  <si>
     <t>чем конкретнее создана мыслеформа, тем конкретнее пройдет ее материализация</t>
   </si>
   <si>
-    <t>чем чётче создан мыслеобраз, тем чётче пройдет его воплощение</t>
-  </si>
-  <si>
     <t>создана мыслеформа</t>
   </si>
   <si>
-    <t>создан мыслеобраз</t>
-  </si>
-  <si>
     <t>на информационную структуру воды</t>
   </si>
   <si>
@@ -1836,6 +1795,477 @@
   </si>
   <si>
     <t>возможны два исхода её возврата</t>
+  </si>
+  <si>
+    <t>«возбудившего» электрон</t>
+  </si>
+  <si>
+    <t>«возбудившего» отрицательную частицу</t>
+  </si>
+  <si>
+    <t>«неприличный» жест</t>
+  </si>
+  <si>
+    <t>«неприличное» движение рук</t>
+  </si>
+  <si>
+    <t>предыдущей реинкарнации</t>
+  </si>
+  <si>
+    <t>предыдущем перерождении</t>
+  </si>
+  <si>
+    <t>неизвестный пока землянам принцип</t>
+  </si>
+  <si>
+    <t>неизвестное пока землянам правило</t>
+  </si>
+  <si>
+    <t>черной или белой магии</t>
+  </si>
+  <si>
+    <t>чёрного или белого колдовства</t>
+  </si>
+  <si>
+    <t>магии белой или черной</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> колдовства чёрного или белого</t>
+  </si>
+  <si>
+    <t>магами и колдунами</t>
+  </si>
+  <si>
+    <t>чудотворцами и колдунами</t>
+  </si>
+  <si>
+    <t>магическим кланом</t>
+  </si>
+  <si>
+    <t>колдовской семьёй</t>
+  </si>
+  <si>
+    <t>колдуном или магом</t>
+  </si>
+  <si>
+    <t>чудотворцем или колдуном</t>
+  </si>
+  <si>
+    <t>потустороннее мыслетело</t>
+  </si>
+  <si>
+    <t>создано мыслетело</t>
+  </si>
+  <si>
+    <t>Мыслетело преобразуется</t>
+  </si>
+  <si>
+    <t>ваше мыслетело вышел</t>
+  </si>
+  <si>
+    <t>быол создано следующее мыслетело</t>
+  </si>
+  <si>
+    <t>создаваемое мыслетело должно быть полноценным и для его входа</t>
+  </si>
+  <si>
+    <t>мыслетело является понятием</t>
+  </si>
+  <si>
+    <t>Правило действия подобных мыслетел вполне понятно</t>
+  </si>
+  <si>
+    <t>чем чётче создано мыслетело, тем чётче пройдет его воплощение</t>
+  </si>
+  <si>
+    <t>во время коррекции позволил</t>
+  </si>
+  <si>
+    <t>во время изменения позволило</t>
+  </si>
+  <si>
+    <t>составленной мыслеформы</t>
+  </si>
+  <si>
+    <t>составленного мыслетела</t>
+  </si>
+  <si>
+    <t>могла за считанные минуты пройти коррекция</t>
+  </si>
+  <si>
+    <t>могло за считанные минуты пройти изменение</t>
+  </si>
+  <si>
+    <t>коррекцию, которая в те годы длилась</t>
+  </si>
+  <si>
+    <t>изменение, которое в те годы длилось</t>
+  </si>
+  <si>
+    <t>Вся коррекция прошла</t>
+  </si>
+  <si>
+    <t>Всё изменение прошло</t>
+  </si>
+  <si>
+    <t>вся коррекция прошла</t>
+  </si>
+  <si>
+    <t>всё изменение прошло</t>
+  </si>
+  <si>
+    <t>послужила смоделированная по ПС конфликтная ситуация</t>
+  </si>
+  <si>
+    <t>послужил воссозданый по ПС спорный случай</t>
+  </si>
+  <si>
+    <t>Есть какая-то клика</t>
+  </si>
+  <si>
+    <t>сруктурирует</t>
+  </si>
+  <si>
+    <t>структурирует</t>
+  </si>
+  <si>
+    <t>Инстинктивно это используется</t>
+  </si>
+  <si>
+    <t>В среде животных это используется</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При составление эниологического прогноза </t>
+  </si>
+  <si>
+    <t xml:space="preserve">При составлении эниологического прогноза </t>
+  </si>
+  <si>
+    <t>программировал данную негативную ситуацию</t>
+  </si>
+  <si>
+    <t>задавал данную отрицательную обстановку</t>
+  </si>
+  <si>
+    <t>таким-то магическим кланом</t>
+  </si>
+  <si>
+    <t>такой-то колдовской семьёй</t>
+  </si>
+  <si>
+    <t>нотную грамоту</t>
+  </si>
+  <si>
+    <t>нотные правила</t>
+  </si>
+  <si>
+    <t>магам и колдунам</t>
+  </si>
+  <si>
+    <t>чудотворцам и колдунам</t>
+  </si>
+  <si>
+    <t>эниологической техники безопасности</t>
+  </si>
+  <si>
+    <t>вездесущих мер безопасности</t>
+  </si>
+  <si>
+    <t>следующую мыслеформу</t>
+  </si>
+  <si>
+    <t>следующее мыслетело</t>
+  </si>
+  <si>
+    <t>В Центре индивидуальная работа</t>
+  </si>
+  <si>
+    <t>В Учреждении личная работа</t>
+  </si>
+  <si>
+    <t>эниокорректоры Центра</t>
+  </si>
+  <si>
+    <t>вездесущие изменители Учреждения</t>
+  </si>
+  <si>
+    <t>не устают энергетически</t>
+  </si>
+  <si>
+    <t>не устают и не теряют бодрость</t>
+  </si>
+  <si>
+    <t>медицинская астрология</t>
+  </si>
+  <si>
+    <t>врачебный раздел науки о звёздах</t>
+  </si>
+  <si>
+    <t>в измерительный комплекс</t>
+  </si>
+  <si>
+    <t>в измерительное помещение</t>
+  </si>
+  <si>
+    <t>«стирается» вся информация</t>
+  </si>
+  <si>
+    <t>«стираются» все сведения</t>
+  </si>
+  <si>
+    <t>проводниками основной идеологии</t>
+  </si>
+  <si>
+    <t>проводниками основного мировоззрения</t>
+  </si>
+  <si>
+    <t>в прямой телепатической форме</t>
+  </si>
+  <si>
+    <t>в прямом мыслечитательном образе</t>
+  </si>
+  <si>
+    <t>Социум к этому еще не готов</t>
+  </si>
+  <si>
+    <t>Общество к этому еще не готово</t>
+  </si>
+  <si>
+    <t>идентичность мыслеформе</t>
+  </si>
+  <si>
+    <t>соответствие мыслетелу</t>
+  </si>
+  <si>
+    <t>полная идентичность мыслеформе, приведенной</t>
+  </si>
+  <si>
+    <t>полное соответствие мыслетелу, приведенному</t>
+  </si>
+  <si>
+    <t>энергоинформационной нейтрализации</t>
+  </si>
+  <si>
+    <t>вездесущного устранения</t>
+  </si>
+  <si>
+    <t>коррекция будет просто бессмысленна</t>
+  </si>
+  <si>
+    <t>изменение будет просто бессмысленно</t>
+  </si>
+  <si>
+    <t>три эниокорректора</t>
+  </si>
+  <si>
+    <t>три вездесущих изменителя</t>
+  </si>
+  <si>
+    <t>«заряд» возможностей женщины</t>
+  </si>
+  <si>
+    <t>«энергетический» потенциал женщины</t>
+  </si>
+  <si>
+    <t>знали астрологию</t>
+  </si>
+  <si>
+    <t>знали звёздоведение</t>
+  </si>
+  <si>
+    <t>Коррекция прошла нормально</t>
+  </si>
+  <si>
+    <t>Изменение прошло успешно</t>
+  </si>
+  <si>
+    <t>общий сеанс коррекции</t>
+  </si>
+  <si>
+    <t>общий приём при проведении изменения</t>
+  </si>
+  <si>
+    <t>эту группу ученых, собиравшуюся</t>
+  </si>
+  <si>
+    <t>это подразделение ученых, собиравшееся</t>
+  </si>
+  <si>
+    <t>утомили мужнины</t>
+  </si>
+  <si>
+    <t>утомили мужнину</t>
+  </si>
+  <si>
+    <t>почему ампула с противоядием на синезеленый африканский грипп была доставлена</t>
+  </si>
+  <si>
+    <t>почем сосуд с противоядием на синезеленый африканский грипп был доставлен</t>
+  </si>
+  <si>
+    <t>предлагался препарат, приготовленный</t>
+  </si>
+  <si>
+    <t>предлагалось средство, приготовленное</t>
+  </si>
+  <si>
+    <t>«елочной» онкологии</t>
+  </si>
+  <si>
+    <t>«елочной» злокачественной опухли</t>
+  </si>
+  <si>
+    <t>необходимой критической массы оперированных</t>
+  </si>
+  <si>
+    <t>необходимого достаточного количества прошедших врачебные вмешательства</t>
+  </si>
+  <si>
+    <t>Эту «группу», замаскированную</t>
+  </si>
+  <si>
+    <t>Это «подразделение», скрытое</t>
+  </si>
+  <si>
+    <t>Эта ситуация в последние годы развилась</t>
+  </si>
+  <si>
+    <t>Этот случай в последние годы развился</t>
+  </si>
+  <si>
+    <t>это последствие было великолепно опытно доказано академиком</t>
+  </si>
+  <si>
+    <t>постоянная рубрика газеты нашего центра</t>
+  </si>
+  <si>
+    <t>посвящена постоянный заголовок бумажного издания нашего Учреждения</t>
+  </si>
+  <si>
+    <t>Этот каталог можно получить спектрограмму этого объекта</t>
+  </si>
+  <si>
+    <t>Этим каталогом можно получить спектрограмму этого объекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этим набором можно получить многомерный чертёж-рисунок этого предмета </t>
+  </si>
+  <si>
+    <t>Это особа программа</t>
+  </si>
+  <si>
+    <t>Это особая программа</t>
+  </si>
+  <si>
+    <t>наращивала критическую массу</t>
+  </si>
+  <si>
+    <t>наращивало необходимое количество людей</t>
+  </si>
+  <si>
+    <t>предусмотрена эта естественная ситуация</t>
+  </si>
+  <si>
+    <t>предусмотрен этот естественный случай</t>
+  </si>
+  <si>
+    <t>резком ухудшении природных условиях</t>
+  </si>
+  <si>
+    <t>резком ухудшении природных условий</t>
+  </si>
+  <si>
+    <t>был набран этот текст</t>
+  </si>
+  <si>
+    <t>была готова эта письменность</t>
+  </si>
+  <si>
+    <t>просматривался сильнейший стресс</t>
+  </si>
+  <si>
+    <t>просматривалось сильнейшее перенапряжение</t>
+  </si>
+  <si>
+    <t>при эниокоррекции</t>
+  </si>
+  <si>
+    <t>при вездесущем изменении</t>
+  </si>
+  <si>
+    <t>над международной медицинской мафиозной структурой, торговавшей</t>
+  </si>
+  <si>
+    <t>международным врачебным преступным сообществом, торговавшим</t>
+  </si>
+  <si>
+    <t>теоретической эзотерики</t>
+  </si>
+  <si>
+    <t>учебного тайноведения</t>
+  </si>
+  <si>
+    <t>Такое правило работы просто вынуждало</t>
+  </si>
+  <si>
+    <t>Предметом торговли в последние годы стал и так называемый абортный материал</t>
+  </si>
+  <si>
+    <t>Предметами торговли в последние годы стали и так называемые останки плода от прерывания беременности</t>
+  </si>
+  <si>
+    <t>просматривалось сильнейшее перенапряжение, связанное</t>
+  </si>
+  <si>
+    <t>просматривался сильнейший стресс, связанный</t>
+  </si>
+  <si>
+    <t>своя, заранее определенная роль</t>
+  </si>
+  <si>
+    <t>своё, заранее определённое значение</t>
+  </si>
+  <si>
+    <t>жевательных рефлексов</t>
+  </si>
+  <si>
+    <t>жевательных животных позывов</t>
+  </si>
+  <si>
+    <t>Самая типичная контактная ситуация, с которой</t>
+  </si>
+  <si>
+    <t>Самый обычный связующий случай, с которым</t>
+  </si>
+  <si>
+    <t>линий излучения</t>
+  </si>
+  <si>
+    <t>путей излучения</t>
+  </si>
+  <si>
+    <t>потенциала всей цивилизации</t>
+  </si>
+  <si>
+    <t>возможностей всего человечества</t>
+  </si>
+  <si>
+    <t>творческого потенциала, а взамен его</t>
+  </si>
+  <si>
+    <t>творческих возмножностей, а взамен их</t>
+  </si>
+  <si>
+    <t>объемная структура, напоминающая</t>
+  </si>
+  <si>
+    <t>объемный образ, напоминающий</t>
+  </si>
+  <si>
+    <t>энергоинформационный диссонанс</t>
+  </si>
+  <si>
+    <t>вездесущное разногласие</t>
   </si>
 </sst>
 </file>
@@ -2189,130 +2619,130 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B6" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B7" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B8" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B15" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B16" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -2321,266 +2751,266 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B18" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B19" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B20" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B21" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B22" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B23" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B25" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B29" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B30" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -2621,8 +3051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -2631,13 +3060,13 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="B1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -2645,7 +3074,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2653,7 +3082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -2661,7 +3090,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -2669,7 +3098,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2677,15 +3106,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2693,7 +3122,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -2701,7 +3130,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -2709,7 +3138,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -2717,7 +3146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -2725,23 +3154,23 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B13" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="B14" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -2749,31 +3178,31 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="B18" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -2781,7 +3210,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -2789,7 +3218,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -2797,12 +3226,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -2813,15 +3242,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="B24" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2829,7 +3258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -2837,15 +3266,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="B27" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2853,7 +3282,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2861,7 +3290,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -2869,15 +3298,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="B31" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -2885,23 +3314,23 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="B33" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B34" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -2909,15 +3338,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="B36" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -2925,7 +3354,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2933,79 +3362,79 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="B39" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="B42" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B45" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B47" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -3015,38 +3444,134 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="B49" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="B50" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>588</v>
+        <v>574</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>585</v>
+      </c>
+      <c r="B52" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>595</v>
+      </c>
+      <c r="B53" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>610</v>
+      </c>
+      <c r="B54" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>633</v>
+      </c>
+      <c r="B55" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>639</v>
+      </c>
+      <c r="B56" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>647</v>
+      </c>
+      <c r="B57" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>659</v>
+      </c>
+      <c r="B58" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>663</v>
+      </c>
+      <c r="B59" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>671</v>
+      </c>
+      <c r="B60" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>673</v>
+      </c>
+      <c r="B61" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>711</v>
+      </c>
+      <c r="B62" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>715</v>
+      </c>
+      <c r="B63" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>736</v>
+      </c>
+      <c r="B64" t="s">
+        <v>737</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B48" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="может быть осуществлена коррекция"/>
-        <filter val="энергоинформационной коррекции"/>
-        <filter val="энергоинформационную коррекцию"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:B63" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B50">
     <sortCondition ref="A1:A50"/>
   </sortState>
@@ -3055,38 +3580,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629FBABB-5E47-4235-BB5F-3D637E48298E}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="36.62890625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>585</v>
-      </c>
-      <c r="B1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>589</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="65.3671875" style="2" customWidth="1"/>
@@ -3119,26 +3614,18 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -3159,18 +3646,18 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -3183,29 +3670,29 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -3226,122 +3713,122 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>238</v>
+        <v>601</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3354,153 +3841,495 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>324</v>
+        <v>602</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="2" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>582</v>
+        <v>568</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>731</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B28" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B28">
     <sortCondition ref="A1:A28"/>
   </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629FBABB-5E47-4235-BB5F-3D637E48298E}">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="36.62890625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>587</v>
+      </c>
+      <c r="B5" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>608</v>
+      </c>
+      <c r="B6" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>643</v>
+      </c>
+      <c r="B7" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>645</v>
+      </c>
+      <c r="B8" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>651</v>
+      </c>
+      <c r="B9" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>655</v>
+      </c>
+      <c r="B10" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B11" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>667</v>
+      </c>
+      <c r="B12" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>677</v>
+      </c>
+      <c r="B13" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>683</v>
+      </c>
+      <c r="B14" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>685</v>
+      </c>
+      <c r="B15" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>689</v>
+      </c>
+      <c r="B16" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>694</v>
+      </c>
+      <c r="B17" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>703</v>
+      </c>
+      <c r="B18" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>705</v>
+      </c>
+      <c r="B19" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>707</v>
+      </c>
+      <c r="B20" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>345</v>
+      </c>
+      <c r="B21" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>722</v>
+      </c>
+      <c r="B22" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>728</v>
+      </c>
+      <c r="B23" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>732</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3516,34 +4345,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="B4" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -3553,1113 +4382,1245 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="43.15625" style="3" customWidth="1"/>
     <col min="2" max="2" width="39.734375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>373</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
-        <v>71</v>
+        <v>455</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
-        <v>73</v>
+        <v>309</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>74</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>427</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
-        <v>116</v>
+        <v>721</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>117</v>
+        <v>720</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
-        <v>118</v>
+        <v>311</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
-        <v>124</v>
+        <v>318</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>125</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>467</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>399</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>429</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>431</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
-        <v>141</v>
+        <v>196</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>142</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3" t="s">
-        <v>144</v>
+        <v>433</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>143</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3" t="s">
-        <v>153</v>
+        <v>497</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3" t="s">
-        <v>155</v>
+        <v>450</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
-        <v>160</v>
+        <v>479</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>159</v>
+        <v>480</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3" t="s">
-        <v>161</v>
+        <v>481</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>418</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3" t="s">
-        <v>164</v>
+        <v>415</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>167</v>
+        <v>463</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3" t="s">
-        <v>168</v>
+        <v>485</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3" t="s">
-        <v>170</v>
+        <v>453</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3" t="s">
-        <v>172</v>
+        <v>471</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3" t="s">
-        <v>173</v>
+        <v>461</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3" t="s">
-        <v>175</v>
+        <v>493</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3" t="s">
-        <v>149</v>
+        <v>483</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="3" t="s">
-        <v>114</v>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="6" t="s">
+        <v>300</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>391</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3" t="s">
-        <v>110</v>
+        <v>465</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>111</v>
+        <v>466</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3" t="s">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>448</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>552</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>54</v>
+        <v>604</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3" t="s">
-        <v>57</v>
+        <v>387</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3" t="s">
-        <v>101</v>
+        <v>501</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3" t="s">
-        <v>178</v>
+        <v>411</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="3" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3" t="s">
-        <v>186</v>
+        <v>434</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>187</v>
+        <v>435</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="3" t="s">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3" t="s">
-        <v>195</v>
+        <v>289</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="28.5" x14ac:dyDescent="0.55000000000000004">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>371</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>200</v>
+        <v>161</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="3" t="s">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>202</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3" t="s">
-        <v>203</v>
+        <v>148</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>204</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3" t="s">
-        <v>206</v>
+        <v>40</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>207</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>240</v>
+        <v>52</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3" t="s">
-        <v>244</v>
+        <v>459</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3" t="s">
-        <v>246</v>
+        <v>489</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>247</v>
+        <v>490</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3" t="s">
-        <v>297</v>
+        <v>364</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>298</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3" t="s">
-        <v>302</v>
+        <v>444</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>303</v>
+        <v>445</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3" t="s">
-        <v>304</v>
+        <v>403</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>305</v>
+        <v>513</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3" t="s">
-        <v>306</v>
+        <v>440</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>307</v>
+        <v>441</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>509</v>
+      </c>
+      <c r="B63" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3" t="s">
-        <v>317</v>
+        <v>111</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>318</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3" t="s">
-        <v>321</v>
+        <v>125</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>322</v>
+        <v>537</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3" t="s">
-        <v>327</v>
+        <v>193</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3" t="s">
-        <v>319</v>
+        <v>713</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>320</v>
+        <v>714</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3" t="s">
-        <v>355</v>
+        <v>475</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>356</v>
+        <v>476</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3" t="s">
-        <v>357</v>
+        <v>195</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>358</v>
+        <v>605</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3" t="s">
-        <v>372</v>
+        <v>517</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3" t="s">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>375</v>
+        <v>418</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3" t="s">
-        <v>376</v>
+        <v>159</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3" t="s">
-        <v>381</v>
+        <v>294</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>382</v>
+        <v>295</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3" t="s">
-        <v>383</v>
+        <v>176</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>384</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3" t="s">
-        <v>393</v>
+        <v>119</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>394</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3" t="s">
-        <v>397</v>
+        <v>126</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>398</v>
+        <v>127</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3" t="s">
-        <v>401</v>
+        <v>236</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3" t="s">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3" t="s">
-        <v>409</v>
+        <v>469</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>410</v>
+        <v>470</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>412</v>
+        <v>384</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3" t="s">
-        <v>422</v>
+        <v>107</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3" t="s">
-        <v>426</v>
+        <v>98</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>427</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3" t="s">
-        <v>438</v>
+        <v>137</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="28.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>191</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3" t="s">
-        <v>442</v>
+        <v>135</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>443</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3" t="s">
-        <v>445</v>
+        <v>531</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3" t="s">
-        <v>447</v>
+        <v>527</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>448</v>
+        <v>528</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3" t="s">
-        <v>449</v>
+        <v>491</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>450</v>
+        <v>492</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3" t="s">
-        <v>451</v>
+        <v>366</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>452</v>
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="3" t="s">
-        <v>455</v>
+        <v>535</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3" t="s">
-        <v>457</v>
+        <v>169</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3" t="s">
-        <v>459</v>
+        <v>132</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>460</v>
+        <v>606</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3" t="s">
-        <v>444</v>
+        <v>487</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3" t="s">
-        <v>464</v>
+        <v>499</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>465</v>
+        <v>500</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3" t="s">
-        <v>466</v>
+        <v>156</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3" t="s">
-        <v>468</v>
+        <v>182</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>469</v>
+        <v>183</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3" t="s">
-        <v>470</v>
+        <v>69</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>471</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>473</v>
+      <c r="A103" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="3" t="s">
-        <v>474</v>
+        <v>140</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>477</v>
+        <v>105</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="3" t="s">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3" t="s">
-        <v>480</v>
+        <v>115</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="3" t="s">
-        <v>514</v>
+        <v>77</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>515</v>
+        <v>78</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="3" t="s">
-        <v>484</v>
+        <v>395</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>485</v>
+        <v>396</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="3" t="s">
-        <v>486</v>
+        <v>345</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="3" t="s">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>489</v>
+        <v>84</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="3" t="s">
-        <v>490</v>
+        <v>296</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>491</v>
+        <v>297</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="3" t="s">
-        <v>492</v>
+        <v>123</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="3" t="s">
-        <v>494</v>
+        <v>313</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>231</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="3" t="s">
-        <v>498</v>
+        <v>401</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>499</v>
+        <v>402</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="3" t="s">
-        <v>500</v>
+        <v>121</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="3" t="s">
-        <v>502</v>
+        <v>155</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>503</v>
+        <v>154</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="3" t="s">
-        <v>504</v>
+        <v>298</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>505</v>
+        <v>299</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="3" t="s">
-        <v>506</v>
+        <v>457</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>507</v>
+        <v>458</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="3" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="3" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125" t="s">
-        <v>520</v>
-      </c>
-      <c r="B125" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="3" t="s">
-        <v>413</v>
+        <v>53</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="3" t="s">
-        <v>527</v>
+        <v>473</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>528</v>
+        <v>474</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="3" t="s">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="3" t="s">
-        <v>535</v>
+        <v>81</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>536</v>
+        <v>82</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="3" t="s">
-        <v>541</v>
+        <v>133</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>542</v>
+        <v>134</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="3" t="s">
-        <v>545</v>
+        <v>163</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="3" t="s">
-        <v>549</v>
+        <v>145</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>550</v>
+        <v>693</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>719</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B137" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B134">
+    <sortCondition ref="A1:A134"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C9E41E9-C4FF-4A2E-9387-ABCBB02BFCB3}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="42.41796875" customWidth="1"/>
-    <col min="2" max="2" width="38.20703125" customWidth="1"/>
+    <col min="1" max="1" width="68.1015625" customWidth="1"/>
+    <col min="2" max="2" width="45.578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="B1" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="B2" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="B3" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="B4" t="s">
-        <v>594</v>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>612</v>
+      </c>
+      <c r="B5" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>614</v>
+      </c>
+      <c r="B6" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>616</v>
+      </c>
+      <c r="B7" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>618</v>
+      </c>
+      <c r="B8" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>620</v>
+      </c>
+      <c r="B9" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>641</v>
+      </c>
+      <c r="B10" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>661</v>
+      </c>
+      <c r="B11" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>665</v>
+      </c>
+      <c r="B12" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>670</v>
+      </c>
+      <c r="B13" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>687</v>
+      </c>
+      <c r="B14" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>691</v>
+      </c>
+      <c r="B15" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="B16" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>726</v>
+      </c>
+      <c r="B17" t="s">
+        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -4674,7 +5635,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -4684,7 +5645,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
-  <dimension ref="A2:B12"/>
+  <dimension ref="A2:B18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="40.7890625" customWidth="1"/>
@@ -4693,90 +5654,135 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B3" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B6" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B7" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B8" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B9" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="B10" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="B11" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B12" t="s">
-        <v>433</v>
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>623</v>
+      </c>
+      <c r="B14" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>627</v>
+      </c>
+      <c r="B15" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>679</v>
+      </c>
+      <c r="B16" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="B17" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>699</v>
+      </c>
+      <c r="B18" t="s">
+        <v>700</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2294FA86-00B2-4817-BF57-2506407CC294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF608DA-082E-43AE-BC44-0F86B5AE88EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="746" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="746" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="735">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -87,9 +87,6 @@
     <t>этой энергоинформационной трансформации</t>
   </si>
   <si>
-    <t>этого энергоинформационного преобразования</t>
-  </si>
-  <si>
     <t>норма жизни</t>
   </si>
   <si>
@@ -135,9 +132,6 @@
     <t>весь эгрегориальный этнос</t>
   </si>
   <si>
-    <t>вся эгрегориальная народность</t>
-  </si>
-  <si>
     <t>деструктивной магии</t>
   </si>
   <si>
@@ -216,9 +210,6 @@
     <t xml:space="preserve">эзотерический и физический аспект так называемой </t>
   </si>
   <si>
-    <t>тайную и физическую особенность,так называемую</t>
-  </si>
-  <si>
     <t>информационная составляющая через воду оказывает</t>
   </si>
   <si>
@@ -327,9 +318,6 @@
     <t>брежневской эпохи</t>
   </si>
   <si>
-    <t>периода Брежнева</t>
-  </si>
-  <si>
     <t>клиент-искуситель</t>
   </si>
   <si>
@@ -354,12 +342,6 @@
     <t>наше общество является пока лишь лжеразумным</t>
   </si>
   <si>
-    <t>серьезнейшим нарушением</t>
-  </si>
-  <si>
-    <t>серьезнейшим нарушениям</t>
-  </si>
-  <si>
     <t>отправить писателю</t>
   </si>
   <si>
@@ -402,15 +384,9 @@
     <t>Создание единой планетарной цивилизации</t>
   </si>
   <si>
-    <t>Создание единого планетарного общества</t>
-  </si>
-  <si>
     <t>нашей планетарной цивилизации</t>
   </si>
   <si>
-    <t>нашего планетарного общества</t>
-  </si>
-  <si>
     <t>нанесший российскому генофонду сильнейшую деформацию</t>
   </si>
   <si>
@@ -1152,9 +1128,6 @@
     <t>Каким бы прекрасным ни был расчётный прообраз</t>
   </si>
   <si>
-    <t>попадают в русло.</t>
-  </si>
-  <si>
     <t>мой энергоинформационный банк</t>
   </si>
   <si>
@@ -1326,9 +1299,6 @@
     <t>кагальницкой катастрофы</t>
   </si>
   <si>
-    <t>кагальницкого стихийного бедствия</t>
-  </si>
-  <si>
     <t>астрологом Центра</t>
   </si>
   <si>
@@ -1512,9 +1482,6 @@
     <t>В Центре индивидуальная</t>
   </si>
   <si>
-    <t>В Центре личная</t>
-  </si>
-  <si>
     <t>работу в Центре</t>
   </si>
   <si>
@@ -1530,9 +1497,6 @@
     <t>по телефону в Центр</t>
   </si>
   <si>
-    <t>по телефону в Учреждение</t>
-  </si>
-  <si>
     <t>В Центре приходилось</t>
   </si>
   <si>
@@ -1626,9 +1590,6 @@
     <t>проектируется в ментальный план</t>
   </si>
   <si>
-    <t>вкладывается в ментальный план</t>
-  </si>
-  <si>
     <t>увлечение деталировкой</t>
   </si>
   <si>
@@ -1668,9 +1629,6 @@
     <t>любой объёмный образ неким способом создаёт вокруг себя пространство</t>
   </si>
   <si>
-    <t>сведения, записанные на объёмном образе молекулы, способны перезаписываться</t>
-  </si>
-  <si>
     <t>Космического Донорства</t>
   </si>
   <si>
@@ -2133,9 +2091,6 @@
     <t>Этот случай в последние годы развился</t>
   </si>
   <si>
-    <t>это последствие было великолепно опытно доказано академиком</t>
-  </si>
-  <si>
     <t>постоянная рубрика газеты нашего центра</t>
   </si>
   <si>
@@ -2266,6 +2221,42 @@
   </si>
   <si>
     <t>вездесущное разногласие</t>
+  </si>
+  <si>
+    <t>нашего мирового общества</t>
+  </si>
+  <si>
+    <t>Создание единого вселенского общества</t>
+  </si>
+  <si>
+    <t>по числителю для связи в само Учреждение</t>
+  </si>
+  <si>
+    <t>кагальницкого природного бедствия</t>
+  </si>
+  <si>
+    <t>вкладывается в мыслительный замысел</t>
+  </si>
+  <si>
+    <t>В Учреждении личная</t>
+  </si>
+  <si>
+    <t>времени Брежнева</t>
+  </si>
+  <si>
+    <t>вся совместносвязанная сознанием народность</t>
+  </si>
+  <si>
+    <t>этого вездесущего преобразования</t>
+  </si>
+  <si>
+    <t>это последствие было великолепно опытно доказано учёным</t>
+  </si>
+  <si>
+    <t>тайную и плотскую особенность,так называемую</t>
+  </si>
+  <si>
+    <t>сведения, записанные на объёмном образе частицы, способны перезаписываться</t>
   </si>
 </sst>
 </file>
@@ -2618,400 +2609,400 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" t="s">
-        <v>250</v>
+      <c r="A1" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>252</v>
+      <c r="A2" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B3" t="s">
-        <v>254</v>
+      <c r="A3" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B4" t="s">
-        <v>264</v>
+      <c r="A4" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B5" t="s">
-        <v>256</v>
+      <c r="A5" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" t="s">
-        <v>262</v>
+      <c r="A6" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" t="s">
-        <v>258</v>
+      <c r="A7" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" t="s">
-        <v>260</v>
+      <c r="A8" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>277</v>
+        <v>546</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>278</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>279</v>
+        <v>548</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>280</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>282</v>
+      <c r="A11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>284</v>
+      <c r="A12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B12" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>286</v>
+      <c r="A13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B13" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>288</v>
+      <c r="A14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B15" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B16" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B17" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="B18" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B21" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>269</v>
-      </c>
-      <c r="B20" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>271</v>
-      </c>
-      <c r="B21" t="s">
-        <v>272</v>
-      </c>
-    </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>208</v>
-      </c>
-      <c r="B23" t="s">
-        <v>209</v>
+      <c r="A23" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" t="s">
-        <v>206</v>
-      </c>
-      <c r="B24" t="s">
-        <v>207</v>
+      <c r="A24" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>216</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s">
-        <v>219</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B32" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>326</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
+      </c>
+      <c r="B33" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>327</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>328</v>
+        <v>202</v>
+      </c>
+      <c r="B34" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>329</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>330</v>
+        <v>204</v>
+      </c>
+      <c r="B35" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>331</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>332</v>
+        <v>206</v>
+      </c>
+      <c r="B36" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>333</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>334</v>
+        <v>208</v>
+      </c>
+      <c r="B37" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>335</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>336</v>
+        <v>216</v>
+      </c>
+      <c r="B38" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>337</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>338</v>
+        <v>214</v>
+      </c>
+      <c r="B39" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>339</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>332</v>
+        <v>210</v>
+      </c>
+      <c r="B40" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>553</v>
+      <c r="A41" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="1" t="s">
-        <v>549</v>
+      <c r="A42" t="s">
+        <v>321</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>554</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="1" t="s">
-        <v>550</v>
+      <c r="A43" t="s">
+        <v>318</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>555</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="1" t="s">
-        <v>551</v>
+      <c r="A44" t="s">
+        <v>319</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>556</v>
+        <v>320</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="1" t="s">
-        <v>552</v>
+      <c r="A45" t="s">
+        <v>331</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>557</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="1" t="s">
-        <v>558</v>
+      <c r="A46" t="s">
+        <v>323</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>559</v>
+        <v>324</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="1" t="s">
-        <v>560</v>
+      <c r="A47" t="s">
+        <v>325</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>561</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="1" t="s">
-        <v>562</v>
+      <c r="A48" t="s">
+        <v>327</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>554</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="1" t="s">
-        <v>563</v>
+      <c r="A49" t="s">
+        <v>329</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>564</v>
+        <v>330</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>566</v>
-      </c>
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1"/>
@@ -3060,18 +3051,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="B1" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3084,170 +3075,170 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
         <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B13" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B14" t="s">
-        <v>424</v>
+        <v>726</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="B18" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
         <v>16</v>
-      </c>
-      <c r="B21" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="B24" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3260,178 +3251,178 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
         <v>12</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="B27" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="B31" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="B33" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="B36" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="B39" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B42" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B43" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B45" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3439,135 +3430,135 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>731</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="B49" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="B50" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="B52" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B53" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="B54" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="B55" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="B56" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="B57" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="B58" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="B59" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="B60" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="B61" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>711</v>
+        <v>696</v>
       </c>
       <c r="B62" t="s">
-        <v>712</v>
+        <v>697</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="B63" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="B64" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -3581,7 +3572,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="65.3671875" style="2" customWidth="1"/>
@@ -3590,523 +3581,519 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>368</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
-        <v>367</v>
+        <v>166</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>368</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
-        <v>128</v>
+        <v>635</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>129</v>
+        <v>636</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>307</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
-        <v>117</v>
+        <v>299</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>118</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
-        <v>130</v>
+        <v>313</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>314</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>198</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>101</v>
+      <c r="A14" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>21</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>76</v>
+        <v>361</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
-        <v>96</v>
+        <v>709</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>97</v>
+        <v>710</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
-        <v>143</v>
+        <v>611</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>612</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
-        <v>174</v>
+        <v>380</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>175</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
-        <v>178</v>
+        <v>394</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>179</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
-        <v>184</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>185</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
-        <v>186</v>
+        <v>583</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>405</v>
+        <v>584</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
-        <v>187</v>
+        <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>406</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>407</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
-        <v>228</v>
+        <v>621</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>229</v>
+        <v>622</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
-        <v>245</v>
+        <v>579</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>244</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2" t="s">
-        <v>230</v>
+        <v>577</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
-        <v>246</v>
+        <v>170</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>247</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>303</v>
+        <v>358</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2" t="s">
-        <v>304</v>
+        <v>388</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>305</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
-        <v>307</v>
+        <v>222</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>308</v>
+        <v>587</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
-        <v>85</v>
+        <v>686</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>86</v>
+        <v>687</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>361</v>
+        <v>97</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
-        <v>315</v>
+        <v>110</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>602</v>
+        <v>723</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>317</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2" t="s">
-        <v>319</v>
+        <v>404</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>320</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2" t="s">
-        <v>321</v>
+        <v>372</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2" t="s">
-        <v>324</v>
+        <v>661</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>325</v>
+        <v>662</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2" t="s">
-        <v>369</v>
+        <v>296</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>370</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>378</v>
+        <v>352</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
-        <v>379</v>
+        <v>553</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>380</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2" t="s">
-        <v>381</v>
+        <v>715</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>382</v>
+        <v>716</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2" t="s">
-        <v>389</v>
+        <v>122</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>390</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
-        <v>393</v>
+        <v>639</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>394</v>
+        <v>640</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="2" t="s">
-        <v>397</v>
+        <v>511</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>398</v>
+        <v>727</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2" t="s">
-        <v>403</v>
+        <v>694</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>404</v>
+        <v>695</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
-        <v>413</v>
+        <v>163</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>414</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2" t="s">
-        <v>523</v>
+        <v>238</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>524</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="2" t="s">
-        <v>567</v>
+        <v>179</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>397</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="2" t="s">
-        <v>589</v>
+        <v>19</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>590</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="2" t="s">
-        <v>591</v>
+        <v>72</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>592</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="2" t="s">
-        <v>593</v>
+        <v>178</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>594</v>
+        <v>396</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="2" t="s">
-        <v>597</v>
+        <v>617</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="2" t="s">
-        <v>625</v>
+        <v>237</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>626</v>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="2" t="s">
-        <v>631</v>
+        <v>308</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>632</v>
+        <v>309</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="2" t="s">
-        <v>635</v>
+        <v>575</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>636</v>
+        <v>576</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>638</v>
+        <v>294</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="2" t="s">
-        <v>649</v>
+        <v>370</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>650</v>
+        <v>371</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="2" t="s">
-        <v>653</v>
+        <v>623</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>654</v>
+        <v>624</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="2" t="s">
-        <v>675</v>
+        <v>400</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>676</v>
+        <v>401</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="2" t="s">
-        <v>701</v>
+        <v>135</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>702</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>731</v>
-      </c>
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B28">
-    <sortCondition ref="A1:A28"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B64">
+    <sortCondition ref="A1:A64"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4123,210 +4110,210 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="B1" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B3" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="B4" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="B5" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="B6" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="B7" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="B8" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="B9" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="B10" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="B11" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="B12" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="B13" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B14" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="B15" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="B16" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="B17" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="B18" t="s">
-        <v>704</v>
+        <v>689</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>705</v>
+        <v>690</v>
       </c>
       <c r="B19" t="s">
-        <v>706</v>
+        <v>691</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="B20" t="s">
-        <v>708</v>
+        <v>693</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B21" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="B22" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>728</v>
+        <v>713</v>
       </c>
       <c r="B23" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>732</v>
+        <v>717</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -4345,34 +4332,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B3" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B4" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4382,7 +4369,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B137"/>
+  <dimension ref="A1:B134"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="43.15625" style="3" customWidth="1"/>
@@ -4391,1088 +4378,1080 @@
   <sheetData>
     <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
-        <v>721</v>
+        <v>303</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>720</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
-        <v>311</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>312</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>310</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
-        <v>318</v>
+        <v>457</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>603</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
-        <v>467</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
-        <v>57</v>
+        <v>390</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
-        <v>431</v>
+        <v>172</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
-        <v>196</v>
+        <v>423</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>197</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3" t="s">
-        <v>433</v>
+        <v>485</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3" t="s">
-        <v>497</v>
+        <v>440</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>498</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3" t="s">
-        <v>481</v>
+        <v>406</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>482</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3" t="s">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>416</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>464</v>
+        <v>728</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3" t="s">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>486</v>
+        <v>444</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>494</v>
+        <v>474</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="3" t="s">
-        <v>483</v>
+      <c r="A36" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>484</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="6" t="s">
-        <v>300</v>
+      <c r="A37" s="3" t="s">
+        <v>382</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3" t="s">
-        <v>391</v>
+        <v>455</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3" t="s">
-        <v>238</v>
+        <v>438</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="3" t="s">
-        <v>448</v>
+        <v>86</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3" t="s">
-        <v>89</v>
+        <v>378</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>604</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3" t="s">
-        <v>387</v>
+        <v>76</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>388</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="3" t="s">
-        <v>79</v>
+        <v>489</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>80</v>
+        <v>490</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3" t="s">
-        <v>501</v>
+        <v>402</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="3" t="s">
-        <v>411</v>
+        <v>181</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="3" t="s">
-        <v>189</v>
+        <v>424</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3" t="s">
-        <v>434</v>
+        <v>103</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>435</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="3" t="s">
-        <v>109</v>
+        <v>281</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>110</v>
+        <v>282</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3" t="s">
-        <v>289</v>
+        <v>362</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>290</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>372</v>
+        <v>153</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>52</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="3" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3" t="s">
-        <v>148</v>
+        <v>38</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3" t="s">
-        <v>52</v>
+        <v>449</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>538</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3" t="s">
-        <v>489</v>
+        <v>356</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="3" t="s">
-        <v>364</v>
+        <v>434</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>365</v>
+        <v>435</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="3" t="s">
-        <v>444</v>
+        <v>394</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>445</v>
+        <v>501</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>513</v>
+        <v>431</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
-        <v>509</v>
-      </c>
-      <c r="B63" t="s">
-        <v>510</v>
+      <c r="A62" t="s">
+        <v>497</v>
+      </c>
+      <c r="B62" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="3" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>537</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="3" t="s">
-        <v>193</v>
+        <v>465</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>194</v>
+        <v>466</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="3" t="s">
-        <v>713</v>
+        <v>187</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>714</v>
+        <v>591</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="3" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="3" t="s">
-        <v>195</v>
+        <v>408</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>605</v>
+        <v>409</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="3" t="s">
-        <v>517</v>
+        <v>151</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>518</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="3" t="s">
-        <v>417</v>
+        <v>286</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="3" t="s">
-        <v>159</v>
+        <v>698</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>160</v>
+        <v>699</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="3" t="s">
-        <v>294</v>
+        <v>168</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="3" t="s">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="3" t="s">
-        <v>126</v>
+        <v>228</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="3" t="s">
-        <v>236</v>
+        <v>157</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="3" t="s">
-        <v>165</v>
+        <v>459</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="3" t="s">
-        <v>469</v>
+        <v>374</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="3" t="s">
-        <v>383</v>
+        <v>101</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="3" t="s">
-        <v>98</v>
+        <v>436</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>99</v>
+        <v>437</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="3" t="s">
-        <v>446</v>
+        <v>17</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>447</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="3" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="28.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="28.5" x14ac:dyDescent="0.55000000000000004">
+        <v>183</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>127</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="3" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="3" t="s">
-        <v>167</v>
+        <v>518</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="3" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="3" t="s">
-        <v>527</v>
+        <v>480</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>528</v>
+        <v>725</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="3" t="s">
-        <v>491</v>
+        <v>426</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>492</v>
+        <v>427</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="3" t="s">
-        <v>366</v>
+        <v>522</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="3" t="s">
-        <v>436</v>
+        <v>667</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>536</v>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="3" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="3" t="s">
-        <v>487</v>
+        <v>706</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>488</v>
+        <v>705</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="3" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="3" t="s">
-        <v>156</v>
+        <v>487</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="3" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="3" t="s">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>70</v>
+        <v>175</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>511</v>
+      <c r="A103" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>132</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>443</v>
+        <v>99</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="3" t="s">
-        <v>115</v>
+        <v>432</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="3" t="s">
-        <v>521</v>
+        <v>109</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="3" t="s">
-        <v>77</v>
+        <v>509</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>78</v>
+        <v>510</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="3" t="s">
-        <v>395</v>
+        <v>74</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>396</v>
+        <v>75</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="3" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="3" t="s">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="3" t="s">
-        <v>296</v>
+        <v>80</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>297</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="3" t="s">
-        <v>123</v>
+        <v>288</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="3" t="s">
-        <v>313</v>
+        <v>115</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>314</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>232</v>
+        <v>305</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>223</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="3" t="s">
-        <v>121</v>
+        <v>392</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="3" t="s">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="3" t="s">
-        <v>298</v>
+        <v>147</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>299</v>
+        <v>146</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="3" t="s">
-        <v>457</v>
+        <v>290</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>458</v>
+        <v>291</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="3" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="3" t="s">
-        <v>495</v>
+        <v>467</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>496</v>
+        <v>468</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="3" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>607</v>
+        <v>492</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="3" t="s">
-        <v>347</v>
+        <v>503</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>348</v>
+        <v>593</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="3" t="s">
-        <v>53</v>
+        <v>339</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="3" t="s">
-        <v>473</v>
+        <v>51</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>474</v>
+        <v>733</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="3" t="s">
-        <v>73</v>
+        <v>463</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>74</v>
+        <v>464</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="3" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="3" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A136" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A137" s="7" t="s">
-        <v>718</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>719</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>732</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B137" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B134">
-    <sortCondition ref="A1:A134"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B137">
+    <sortCondition ref="A1:A137"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5489,138 +5468,138 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="B1" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="B2" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="B3" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="B4" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="B5" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="B6" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="B7" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="B8" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="B9" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="B10" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="B11" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="B12" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="B13" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="B14" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="B15" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="7" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="B16" t="s">
-        <v>698</v>
+        <v>683</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>726</v>
+        <v>711</v>
       </c>
       <c r="B17" t="s">
-        <v>727</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -5635,7 +5614,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -5654,135 +5633,135 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B2" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B4" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B6" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B7" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B8" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B9" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B10" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B11" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B12" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="B14" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="B15" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="B16" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="B17" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="B18" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>
